--- a/s2.xlsx
+++ b/s2.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17509" uniqueCount="4215">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17509" uniqueCount="4218">
   <si>
     <t>list_name</t>
   </si>
@@ -12669,6 +12669,15 @@
   </si>
   <si>
     <t>table25e_note6</t>
+  </si>
+  <si>
+    <t>table26a_note6</t>
+  </si>
+  <si>
+    <t>table26b_note6</t>
+  </si>
+  <si>
+    <t>table26c_note6</t>
   </si>
 </sst>
 </file>
@@ -20964,7 +20973,7 @@
       <c r="Q204" s="33"/>
       <c r="R204" s="33"/>
     </row>
-    <row r="205" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A205" s="35" t="s">
         <v>382</v>
       </c>
@@ -20981,7 +20990,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="206" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A206" s="28" t="s">
         <v>268</v>
       </c>
@@ -20998,7 +21007,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="207" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A207" s="28" t="s">
         <v>268</v>
       </c>
@@ -21018,7 +21027,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="208" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A208" s="28" t="s">
         <v>268</v>
       </c>
@@ -21038,7 +21047,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="209" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A209" s="28" t="s">
         <v>268</v>
       </c>
@@ -21058,7 +21067,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="210" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A210" s="24" t="s">
         <v>273</v>
       </c>
@@ -21070,7 +21079,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="211" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A211" s="24" t="s">
         <v>268</v>
       </c>
@@ -21087,7 +21096,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="212" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A212" s="24" t="s">
         <v>296</v>
       </c>
@@ -21113,7 +21122,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="213" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:15" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A213" s="24" t="s">
         <v>296</v>
       </c>
@@ -21139,7 +21148,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="214" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:15" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A214" s="24" t="s">
         <v>296</v>
       </c>
@@ -21166,13 +21175,13 @@
         <v>603</v>
       </c>
     </row>
-    <row r="215" spans="1:15" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A215" s="24" t="s">
         <v>374</v>
       </c>
       <c r="H215" s="24"/>
     </row>
-    <row r="216" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A216" s="24" t="s">
         <v>273</v>
       </c>
@@ -21184,7 +21193,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="217" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A217" s="24" t="s">
         <v>268</v>
       </c>
@@ -21201,7 +21210,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="218" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A218" s="24" t="s">
         <v>296</v>
       </c>
@@ -21227,7 +21236,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="219" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A219" s="24" t="s">
         <v>296</v>
       </c>
@@ -21253,7 +21262,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="220" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:15" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A220" s="24" t="s">
         <v>296</v>
       </c>
@@ -21280,13 +21289,13 @@
         <v>609</v>
       </c>
     </row>
-    <row r="221" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A221" s="24" t="s">
         <v>374</v>
       </c>
       <c r="H221" s="24"/>
     </row>
-    <row r="222" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A222" s="24" t="s">
         <v>273</v>
       </c>
@@ -21298,7 +21307,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="223" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A223" s="24" t="s">
         <v>268</v>
       </c>
@@ -21315,7 +21324,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="224" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A224" s="24" t="s">
         <v>296</v>
       </c>
@@ -21341,7 +21350,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="225" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A225" s="24" t="s">
         <v>296</v>
       </c>
@@ -21367,7 +21376,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="226" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:18" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A226" s="24" t="s">
         <v>296</v>
       </c>
@@ -21394,13 +21403,13 @@
         <v>615</v>
       </c>
     </row>
-    <row r="227" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A227" s="24" t="s">
         <v>374</v>
       </c>
       <c r="H227" s="24"/>
     </row>
-    <row r="228" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A228" s="24" t="s">
         <v>273</v>
       </c>
@@ -21412,7 +21421,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="229" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A229" s="24" t="s">
         <v>268</v>
       </c>
@@ -21429,7 +21438,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="230" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A230" s="24" t="s">
         <v>296</v>
       </c>
@@ -21455,7 +21464,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="231" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A231" s="24" t="s">
         <v>296</v>
       </c>
@@ -21481,7 +21490,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="232" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:18" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A232" s="24" t="s">
         <v>296</v>
       </c>
@@ -21508,13 +21517,13 @@
         <v>621</v>
       </c>
     </row>
-    <row r="233" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A233" s="24" t="s">
         <v>374</v>
       </c>
       <c r="H233" s="24"/>
     </row>
-    <row r="234" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A234" s="24" t="s">
         <v>273</v>
       </c>
@@ -21526,7 +21535,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="235" spans="1:18" s="33" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:18" s="33" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A235" s="24" t="s">
         <v>268</v>
       </c>
@@ -21556,7 +21565,7 @@
       <c r="Q235" s="24"/>
       <c r="R235" s="24"/>
     </row>
-    <row r="236" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A236" s="24" t="s">
         <v>296</v>
       </c>
@@ -21582,7 +21591,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="237" spans="1:18" s="31" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:18" s="31" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A237" s="24" t="s">
         <v>296</v>
       </c>
@@ -21618,7 +21627,7 @@
       <c r="Q237" s="24"/>
       <c r="R237" s="24"/>
     </row>
-    <row r="238" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:18" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A238" s="24" t="s">
         <v>296</v>
       </c>
@@ -21645,7 +21654,7 @@
         <v>627</v>
       </c>
     </row>
-    <row r="239" spans="1:18" s="31" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:18" s="31" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A239" s="24" t="s">
         <v>374</v>
       </c>
@@ -21667,7 +21676,7 @@
       <c r="Q239" s="24"/>
       <c r="R239" s="24"/>
     </row>
-    <row r="240" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A240" s="24" t="s">
         <v>268</v>
       </c>
@@ -21684,7 +21693,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="241" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A241" s="38" t="s">
         <v>296</v>
       </c>
@@ -21711,7 +21720,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="242" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A242" s="38" t="s">
         <v>296</v>
       </c>
@@ -21738,7 +21747,7 @@
         <v>631</v>
       </c>
     </row>
-    <row r="243" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:18" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A243" s="24" t="s">
         <v>296</v>
       </c>
@@ -22621,7 +22630,7 @@
         <v>268</v>
       </c>
       <c r="B285" s="24" t="s">
-        <v>443</v>
+        <v>4215</v>
       </c>
       <c r="H285" s="24" t="s">
         <v>394</v>
@@ -23454,7 +23463,7 @@
         <v>268</v>
       </c>
       <c r="B327" s="24" t="s">
-        <v>443</v>
+        <v>4216</v>
       </c>
       <c r="H327" s="24" t="s">
         <v>394</v>
@@ -23606,7 +23615,7 @@
       <c r="Q333" s="33"/>
       <c r="R333" s="33"/>
     </row>
-    <row r="334" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A334" s="35" t="s">
         <v>382</v>
       </c>
@@ -23623,7 +23632,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="335" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A335" s="28" t="s">
         <v>268</v>
       </c>
@@ -23640,7 +23649,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="336" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A336" s="28" t="s">
         <v>268</v>
       </c>
@@ -23660,7 +23669,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="337" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A337" s="28" t="s">
         <v>268</v>
       </c>
@@ -23680,7 +23689,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="338" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A338" s="28" t="s">
         <v>268</v>
       </c>
@@ -23700,7 +23709,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="339" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A339" s="24" t="s">
         <v>273</v>
       </c>
@@ -23712,7 +23721,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="340" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A340" s="24" t="s">
         <v>268</v>
       </c>
@@ -23729,7 +23738,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="341" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A341" s="24" t="s">
         <v>296</v>
       </c>
@@ -23755,7 +23764,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="342" spans="1:15" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A342" s="24" t="s">
         <v>296</v>
       </c>
@@ -23781,7 +23790,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="343" spans="1:15" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A343" s="24" t="s">
         <v>296</v>
       </c>
@@ -23808,13 +23817,13 @@
         <v>746</v>
       </c>
     </row>
-    <row r="344" spans="1:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:15" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A344" s="24" t="s">
         <v>374</v>
       </c>
       <c r="H344" s="24"/>
     </row>
-    <row r="345" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A345" s="24" t="s">
         <v>273</v>
       </c>
@@ -23826,7 +23835,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="346" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A346" s="24" t="s">
         <v>268</v>
       </c>
@@ -23843,7 +23852,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="347" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A347" s="24" t="s">
         <v>296</v>
       </c>
@@ -23869,7 +23878,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="348" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A348" s="24" t="s">
         <v>296</v>
       </c>
@@ -23895,7 +23904,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="349" spans="1:15" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A349" s="24" t="s">
         <v>296</v>
       </c>
@@ -23922,13 +23931,13 @@
         <v>752</v>
       </c>
     </row>
-    <row r="350" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A350" s="24" t="s">
         <v>374</v>
       </c>
       <c r="H350" s="24"/>
     </row>
-    <row r="351" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A351" s="24" t="s">
         <v>273</v>
       </c>
@@ -23940,7 +23949,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="352" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A352" s="24" t="s">
         <v>268</v>
       </c>
@@ -23957,7 +23966,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="353" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A353" s="24" t="s">
         <v>296</v>
       </c>
@@ -23983,7 +23992,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="354" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A354" s="24" t="s">
         <v>296</v>
       </c>
@@ -24009,7 +24018,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="355" spans="1:18" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A355" s="24" t="s">
         <v>296</v>
       </c>
@@ -24036,13 +24045,13 @@
         <v>758</v>
       </c>
     </row>
-    <row r="356" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A356" s="24" t="s">
         <v>374</v>
       </c>
       <c r="H356" s="24"/>
     </row>
-    <row r="357" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A357" s="24" t="s">
         <v>273</v>
       </c>
@@ -24054,7 +24063,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="358" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A358" s="24" t="s">
         <v>268</v>
       </c>
@@ -24071,7 +24080,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="359" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A359" s="24" t="s">
         <v>296</v>
       </c>
@@ -24097,7 +24106,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="360" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A360" s="24" t="s">
         <v>296</v>
       </c>
@@ -24123,7 +24132,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="361" spans="1:18" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A361" s="24" t="s">
         <v>296</v>
       </c>
@@ -24150,13 +24159,13 @@
         <v>764</v>
       </c>
     </row>
-    <row r="362" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A362" s="24" t="s">
         <v>374</v>
       </c>
       <c r="H362" s="24"/>
     </row>
-    <row r="363" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A363" s="24" t="s">
         <v>273</v>
       </c>
@@ -24168,7 +24177,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="364" spans="1:18" s="33" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:18" s="33" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A364" s="24" t="s">
         <v>268</v>
       </c>
@@ -24198,7 +24207,7 @@
       <c r="Q364" s="24"/>
       <c r="R364" s="24"/>
     </row>
-    <row r="365" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A365" s="24" t="s">
         <v>296</v>
       </c>
@@ -24224,7 +24233,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="366" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A366" s="24" t="s">
         <v>296</v>
       </c>
@@ -24250,7 +24259,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="367" spans="1:18" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A367" s="24" t="s">
         <v>296</v>
       </c>
@@ -24277,18 +24286,18 @@
         <v>770</v>
       </c>
     </row>
-    <row r="368" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A368" s="24" t="s">
         <v>374</v>
       </c>
       <c r="H368" s="24"/>
     </row>
-    <row r="369" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A369" s="24" t="s">
         <v>268</v>
       </c>
       <c r="B369" s="24" t="s">
-        <v>443</v>
+        <v>4217</v>
       </c>
       <c r="H369" s="24" t="s">
         <v>394</v>
@@ -24300,7 +24309,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="370" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A370" s="38" t="s">
         <v>296</v>
       </c>
@@ -24327,7 +24336,7 @@
         <v>772</v>
       </c>
     </row>
-    <row r="371" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A371" s="38" t="s">
         <v>296</v>
       </c>
@@ -24354,7 +24363,7 @@
         <v>774</v>
       </c>
     </row>
-    <row r="372" spans="1:18" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A372" s="24" t="s">
         <v>296</v>
       </c>

--- a/s2.xlsx
+++ b/s2.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17509" uniqueCount="4218">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17509" uniqueCount="4219">
   <si>
     <t>list_name</t>
   </si>
@@ -12678,6 +12678,9 @@
   </si>
   <si>
     <t>table26c_note6</t>
+  </si>
+  <si>
+    <t>table27a_note6</t>
   </si>
 </sst>
 </file>
@@ -23615,7 +23618,7 @@
       <c r="Q333" s="33"/>
       <c r="R333" s="33"/>
     </row>
-    <row r="334" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A334" s="35" t="s">
         <v>382</v>
       </c>
@@ -23632,7 +23635,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="335" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A335" s="28" t="s">
         <v>268</v>
       </c>
@@ -23649,7 +23652,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="336" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A336" s="28" t="s">
         <v>268</v>
       </c>
@@ -23669,7 +23672,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="337" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A337" s="28" t="s">
         <v>268</v>
       </c>
@@ -23689,7 +23692,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="338" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A338" s="28" t="s">
         <v>268</v>
       </c>
@@ -23709,7 +23712,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="339" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A339" s="24" t="s">
         <v>273</v>
       </c>
@@ -23721,7 +23724,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="340" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A340" s="24" t="s">
         <v>268</v>
       </c>
@@ -23738,7 +23741,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="341" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A341" s="24" t="s">
         <v>296</v>
       </c>
@@ -23764,7 +23767,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="342" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:15" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A342" s="24" t="s">
         <v>296</v>
       </c>
@@ -23790,7 +23793,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="343" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:15" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A343" s="24" t="s">
         <v>296</v>
       </c>
@@ -23817,13 +23820,13 @@
         <v>746</v>
       </c>
     </row>
-    <row r="344" spans="1:15" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A344" s="24" t="s">
         <v>374</v>
       </c>
       <c r="H344" s="24"/>
     </row>
-    <row r="345" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A345" s="24" t="s">
         <v>273</v>
       </c>
@@ -23835,7 +23838,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="346" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A346" s="24" t="s">
         <v>268</v>
       </c>
@@ -23852,7 +23855,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="347" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A347" s="24" t="s">
         <v>296</v>
       </c>
@@ -23878,7 +23881,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="348" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A348" s="24" t="s">
         <v>296</v>
       </c>
@@ -23904,7 +23907,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="349" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:15" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A349" s="24" t="s">
         <v>296</v>
       </c>
@@ -23931,13 +23934,13 @@
         <v>752</v>
       </c>
     </row>
-    <row r="350" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A350" s="24" t="s">
         <v>374</v>
       </c>
       <c r="H350" s="24"/>
     </row>
-    <row r="351" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A351" s="24" t="s">
         <v>273</v>
       </c>
@@ -23949,7 +23952,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="352" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A352" s="24" t="s">
         <v>268</v>
       </c>
@@ -23966,7 +23969,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="353" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A353" s="24" t="s">
         <v>296</v>
       </c>
@@ -23992,7 +23995,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="354" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A354" s="24" t="s">
         <v>296</v>
       </c>
@@ -24018,7 +24021,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="355" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:18" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A355" s="24" t="s">
         <v>296</v>
       </c>
@@ -24045,13 +24048,13 @@
         <v>758</v>
       </c>
     </row>
-    <row r="356" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A356" s="24" t="s">
         <v>374</v>
       </c>
       <c r="H356" s="24"/>
     </row>
-    <row r="357" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A357" s="24" t="s">
         <v>273</v>
       </c>
@@ -24063,7 +24066,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="358" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A358" s="24" t="s">
         <v>268</v>
       </c>
@@ -24080,7 +24083,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="359" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A359" s="24" t="s">
         <v>296</v>
       </c>
@@ -24106,7 +24109,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="360" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A360" s="24" t="s">
         <v>296</v>
       </c>
@@ -24132,7 +24135,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="361" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:18" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A361" s="24" t="s">
         <v>296</v>
       </c>
@@ -24159,13 +24162,13 @@
         <v>764</v>
       </c>
     </row>
-    <row r="362" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A362" s="24" t="s">
         <v>374</v>
       </c>
       <c r="H362" s="24"/>
     </row>
-    <row r="363" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A363" s="24" t="s">
         <v>273</v>
       </c>
@@ -24177,7 +24180,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="364" spans="1:18" s="33" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:18" s="33" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A364" s="24" t="s">
         <v>268</v>
       </c>
@@ -24207,7 +24210,7 @@
       <c r="Q364" s="24"/>
       <c r="R364" s="24"/>
     </row>
-    <row r="365" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A365" s="24" t="s">
         <v>296</v>
       </c>
@@ -24233,7 +24236,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="366" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A366" s="24" t="s">
         <v>296</v>
       </c>
@@ -24259,7 +24262,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="367" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:18" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A367" s="24" t="s">
         <v>296</v>
       </c>
@@ -24286,13 +24289,13 @@
         <v>770</v>
       </c>
     </row>
-    <row r="368" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A368" s="24" t="s">
         <v>374</v>
       </c>
       <c r="H368" s="24"/>
     </row>
-    <row r="369" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A369" s="24" t="s">
         <v>268</v>
       </c>
@@ -24309,7 +24312,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="370" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A370" s="38" t="s">
         <v>296</v>
       </c>
@@ -24336,7 +24339,7 @@
         <v>772</v>
       </c>
     </row>
-    <row r="371" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A371" s="38" t="s">
         <v>296</v>
       </c>
@@ -24363,7 +24366,7 @@
         <v>774</v>
       </c>
     </row>
-    <row r="372" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:18" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A372" s="24" t="s">
         <v>296</v>
       </c>
@@ -25523,7 +25526,7 @@
       <c r="Q429" s="33"/>
       <c r="R429" s="33"/>
     </row>
-    <row r="430" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A430" s="35" t="s">
         <v>382</v>
       </c>
@@ -25540,7 +25543,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="431" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A431" s="28" t="s">
         <v>268</v>
       </c>
@@ -25557,7 +25560,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="432" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A432" s="28" t="s">
         <v>268</v>
       </c>
@@ -25577,7 +25580,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="433" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A433" s="28" t="s">
         <v>268</v>
       </c>
@@ -25597,7 +25600,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="434" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A434" s="28" t="s">
         <v>268</v>
       </c>
@@ -25617,7 +25620,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="435" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A435" s="24" t="s">
         <v>273</v>
       </c>
@@ -25629,7 +25632,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="436" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A436" s="24" t="s">
         <v>268</v>
       </c>
@@ -25646,7 +25649,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="437" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A437" s="24" t="s">
         <v>296</v>
       </c>
@@ -25678,7 +25681,7 @@
         <v>648</v>
       </c>
     </row>
-    <row r="438" spans="1:18" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A438" s="24" t="s">
         <v>296</v>
       </c>
@@ -25710,7 +25713,7 @@
         <v>648</v>
       </c>
     </row>
-    <row r="439" spans="1:18" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A439" s="24" t="s">
         <v>296</v>
       </c>
@@ -25737,13 +25740,13 @@
         <v>858</v>
       </c>
     </row>
-    <row r="440" spans="1:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A440" s="24" t="s">
         <v>374</v>
       </c>
       <c r="H440" s="24"/>
     </row>
-    <row r="441" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A441" s="24" t="s">
         <v>273</v>
       </c>
@@ -25755,7 +25758,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="442" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A442" s="24" t="s">
         <v>268</v>
       </c>
@@ -25772,7 +25775,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="443" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A443" s="24" t="s">
         <v>296</v>
       </c>
@@ -25804,7 +25807,7 @@
         <v>648</v>
       </c>
     </row>
-    <row r="444" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A444" s="24" t="s">
         <v>296</v>
       </c>
@@ -25836,7 +25839,7 @@
         <v>648</v>
       </c>
     </row>
-    <row r="445" spans="1:18" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A445" s="24" t="s">
         <v>296</v>
       </c>
@@ -25863,13 +25866,13 @@
         <v>866</v>
       </c>
     </row>
-    <row r="446" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A446" s="24" t="s">
         <v>374</v>
       </c>
       <c r="H446" s="24"/>
     </row>
-    <row r="447" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A447" s="24" t="s">
         <v>273</v>
       </c>
@@ -25881,7 +25884,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="448" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A448" s="24" t="s">
         <v>268</v>
       </c>
@@ -25898,7 +25901,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="449" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A449" s="24" t="s">
         <v>296</v>
       </c>
@@ -25930,7 +25933,7 @@
         <v>648</v>
       </c>
     </row>
-    <row r="450" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A450" s="24" t="s">
         <v>296</v>
       </c>
@@ -25962,7 +25965,7 @@
         <v>648</v>
       </c>
     </row>
-    <row r="451" spans="1:18" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A451" s="24" t="s">
         <v>296</v>
       </c>
@@ -25989,13 +25992,13 @@
         <v>874</v>
       </c>
     </row>
-    <row r="452" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A452" s="24" t="s">
         <v>374</v>
       </c>
       <c r="H452" s="24"/>
     </row>
-    <row r="453" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A453" s="24" t="s">
         <v>273</v>
       </c>
@@ -26007,7 +26010,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="454" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A454" s="24" t="s">
         <v>268</v>
       </c>
@@ -26024,7 +26027,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="455" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A455" s="24" t="s">
         <v>296</v>
       </c>
@@ -26056,7 +26059,7 @@
         <v>648</v>
       </c>
     </row>
-    <row r="456" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A456" s="24" t="s">
         <v>296</v>
       </c>
@@ -26088,7 +26091,7 @@
         <v>648</v>
       </c>
     </row>
-    <row r="457" spans="1:18" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A457" s="24" t="s">
         <v>296</v>
       </c>
@@ -26115,13 +26118,13 @@
         <v>882</v>
       </c>
     </row>
-    <row r="458" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A458" s="24" t="s">
         <v>374</v>
       </c>
       <c r="H458" s="24"/>
     </row>
-    <row r="459" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A459" s="24" t="s">
         <v>273</v>
       </c>
@@ -26133,7 +26136,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="460" spans="1:18" s="33" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:18" s="33" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A460" s="24" t="s">
         <v>268</v>
       </c>
@@ -26163,7 +26166,7 @@
       <c r="Q460" s="24"/>
       <c r="R460" s="24"/>
     </row>
-    <row r="461" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A461" s="24" t="s">
         <v>296</v>
       </c>
@@ -26195,7 +26198,7 @@
         <v>648</v>
       </c>
     </row>
-    <row r="462" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A462" s="24" t="s">
         <v>296</v>
       </c>
@@ -26227,7 +26230,7 @@
         <v>648</v>
       </c>
     </row>
-    <row r="463" spans="1:18" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="463" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A463" s="24" t="s">
         <v>296</v>
       </c>
@@ -26254,18 +26257,18 @@
         <v>890</v>
       </c>
     </row>
-    <row r="464" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A464" s="24" t="s">
         <v>374</v>
       </c>
       <c r="H464" s="24"/>
     </row>
-    <row r="465" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A465" s="24" t="s">
         <v>268</v>
       </c>
       <c r="B465" s="24" t="s">
-        <v>443</v>
+        <v>4218</v>
       </c>
       <c r="H465" s="24" t="s">
         <v>394</v>
@@ -26277,7 +26280,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="466" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A466" s="38" t="s">
         <v>296</v>
       </c>
@@ -26304,7 +26307,7 @@
         <v>892</v>
       </c>
     </row>
-    <row r="467" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="467" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A467" s="38" t="s">
         <v>296</v>
       </c>
@@ -26331,7 +26334,7 @@
         <v>894</v>
       </c>
     </row>
-    <row r="468" spans="1:18" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="468" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A468" s="24" t="s">
         <v>296</v>
       </c>

--- a/s2.xlsx
+++ b/s2.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17509" uniqueCount="4219">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17509" uniqueCount="4222">
   <si>
     <t>list_name</t>
   </si>
@@ -12681,6 +12681,15 @@
   </si>
   <si>
     <t>table27a_note6</t>
+  </si>
+  <si>
+    <t>table27b_note6</t>
+  </si>
+  <si>
+    <t>table27c_note6</t>
+  </si>
+  <si>
+    <t>table27d_note6</t>
   </si>
 </sst>
 </file>
@@ -25526,7 +25535,7 @@
       <c r="Q429" s="33"/>
       <c r="R429" s="33"/>
     </row>
-    <row r="430" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A430" s="35" t="s">
         <v>382</v>
       </c>
@@ -25543,7 +25552,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="431" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A431" s="28" t="s">
         <v>268</v>
       </c>
@@ -25560,7 +25569,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="432" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A432" s="28" t="s">
         <v>268</v>
       </c>
@@ -25580,7 +25589,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="433" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A433" s="28" t="s">
         <v>268</v>
       </c>
@@ -25600,7 +25609,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="434" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A434" s="28" t="s">
         <v>268</v>
       </c>
@@ -25620,7 +25629,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="435" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A435" s="24" t="s">
         <v>273</v>
       </c>
@@ -25632,7 +25641,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="436" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A436" s="24" t="s">
         <v>268</v>
       </c>
@@ -25649,7 +25658,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="437" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A437" s="24" t="s">
         <v>296</v>
       </c>
@@ -25681,7 +25690,7 @@
         <v>648</v>
       </c>
     </row>
-    <row r="438" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:18" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A438" s="24" t="s">
         <v>296</v>
       </c>
@@ -25713,7 +25722,7 @@
         <v>648</v>
       </c>
     </row>
-    <row r="439" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:18" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A439" s="24" t="s">
         <v>296</v>
       </c>
@@ -25740,13 +25749,13 @@
         <v>858</v>
       </c>
     </row>
-    <row r="440" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A440" s="24" t="s">
         <v>374</v>
       </c>
       <c r="H440" s="24"/>
     </row>
-    <row r="441" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A441" s="24" t="s">
         <v>273</v>
       </c>
@@ -25758,7 +25767,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="442" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A442" s="24" t="s">
         <v>268</v>
       </c>
@@ -25775,7 +25784,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="443" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A443" s="24" t="s">
         <v>296</v>
       </c>
@@ -25807,7 +25816,7 @@
         <v>648</v>
       </c>
     </row>
-    <row r="444" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A444" s="24" t="s">
         <v>296</v>
       </c>
@@ -25839,7 +25848,7 @@
         <v>648</v>
       </c>
     </row>
-    <row r="445" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:18" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A445" s="24" t="s">
         <v>296</v>
       </c>
@@ -25866,13 +25875,13 @@
         <v>866</v>
       </c>
     </row>
-    <row r="446" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A446" s="24" t="s">
         <v>374</v>
       </c>
       <c r="H446" s="24"/>
     </row>
-    <row r="447" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A447" s="24" t="s">
         <v>273</v>
       </c>
@@ -25884,7 +25893,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="448" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A448" s="24" t="s">
         <v>268</v>
       </c>
@@ -25901,7 +25910,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="449" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A449" s="24" t="s">
         <v>296</v>
       </c>
@@ -25933,7 +25942,7 @@
         <v>648</v>
       </c>
     </row>
-    <row r="450" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A450" s="24" t="s">
         <v>296</v>
       </c>
@@ -25965,7 +25974,7 @@
         <v>648</v>
       </c>
     </row>
-    <row r="451" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:18" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A451" s="24" t="s">
         <v>296</v>
       </c>
@@ -25992,13 +26001,13 @@
         <v>874</v>
       </c>
     </row>
-    <row r="452" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A452" s="24" t="s">
         <v>374</v>
       </c>
       <c r="H452" s="24"/>
     </row>
-    <row r="453" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A453" s="24" t="s">
         <v>273</v>
       </c>
@@ -26010,7 +26019,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="454" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A454" s="24" t="s">
         <v>268</v>
       </c>
@@ -26027,7 +26036,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="455" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A455" s="24" t="s">
         <v>296</v>
       </c>
@@ -26059,7 +26068,7 @@
         <v>648</v>
       </c>
     </row>
-    <row r="456" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A456" s="24" t="s">
         <v>296</v>
       </c>
@@ -26091,7 +26100,7 @@
         <v>648</v>
       </c>
     </row>
-    <row r="457" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:18" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A457" s="24" t="s">
         <v>296</v>
       </c>
@@ -26118,13 +26127,13 @@
         <v>882</v>
       </c>
     </row>
-    <row r="458" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A458" s="24" t="s">
         <v>374</v>
       </c>
       <c r="H458" s="24"/>
     </row>
-    <row r="459" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A459" s="24" t="s">
         <v>273</v>
       </c>
@@ -26136,7 +26145,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="460" spans="1:18" s="33" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:18" s="33" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A460" s="24" t="s">
         <v>268</v>
       </c>
@@ -26166,7 +26175,7 @@
       <c r="Q460" s="24"/>
       <c r="R460" s="24"/>
     </row>
-    <row r="461" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A461" s="24" t="s">
         <v>296</v>
       </c>
@@ -26198,7 +26207,7 @@
         <v>648</v>
       </c>
     </row>
-    <row r="462" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A462" s="24" t="s">
         <v>296</v>
       </c>
@@ -26230,7 +26239,7 @@
         <v>648</v>
       </c>
     </row>
-    <row r="463" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="463" spans="1:18" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A463" s="24" t="s">
         <v>296</v>
       </c>
@@ -26257,13 +26266,13 @@
         <v>890</v>
       </c>
     </row>
-    <row r="464" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A464" s="24" t="s">
         <v>374</v>
       </c>
       <c r="H464" s="24"/>
     </row>
-    <row r="465" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A465" s="24" t="s">
         <v>268</v>
       </c>
@@ -26280,7 +26289,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="466" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A466" s="38" t="s">
         <v>296</v>
       </c>
@@ -26307,7 +26316,7 @@
         <v>892</v>
       </c>
     </row>
-    <row r="467" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="467" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A467" s="38" t="s">
         <v>296</v>
       </c>
@@ -26334,7 +26343,7 @@
         <v>894</v>
       </c>
     </row>
-    <row r="468" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="468" spans="1:18" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A468" s="24" t="s">
         <v>296</v>
       </c>
@@ -26418,7 +26427,7 @@
       <c r="Q471" s="33"/>
       <c r="R471" s="33"/>
     </row>
-    <row r="472" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="472" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A472" s="35" t="s">
         <v>382</v>
       </c>
@@ -26435,7 +26444,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="473" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="473" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A473" s="28" t="s">
         <v>268</v>
       </c>
@@ -26452,7 +26461,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="474" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="474" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A474" s="28" t="s">
         <v>268</v>
       </c>
@@ -26472,7 +26481,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="475" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="475" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A475" s="28" t="s">
         <v>268</v>
       </c>
@@ -26492,7 +26501,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="476" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="476" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A476" s="28" t="s">
         <v>268</v>
       </c>
@@ -26512,7 +26521,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="477" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="477" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A477" s="24" t="s">
         <v>273</v>
       </c>
@@ -26524,7 +26533,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="478" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="478" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A478" s="24" t="s">
         <v>268</v>
       </c>
@@ -26541,7 +26550,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="479" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="479" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A479" s="24" t="s">
         <v>296</v>
       </c>
@@ -26573,7 +26582,7 @@
         <v>648</v>
       </c>
     </row>
-    <row r="480" spans="1:18" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="480" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A480" s="24" t="s">
         <v>296</v>
       </c>
@@ -26605,7 +26614,7 @@
         <v>648</v>
       </c>
     </row>
-    <row r="481" spans="1:18" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A481" s="24" t="s">
         <v>296</v>
       </c>
@@ -26632,13 +26641,13 @@
         <v>911</v>
       </c>
     </row>
-    <row r="482" spans="1:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="482" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A482" s="24" t="s">
         <v>374</v>
       </c>
       <c r="H482" s="24"/>
     </row>
-    <row r="483" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="483" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A483" s="24" t="s">
         <v>273</v>
       </c>
@@ -26650,7 +26659,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="484" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="484" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A484" s="24" t="s">
         <v>268</v>
       </c>
@@ -26667,7 +26676,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="485" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="485" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A485" s="24" t="s">
         <v>296</v>
       </c>
@@ -26699,7 +26708,7 @@
         <v>648</v>
       </c>
     </row>
-    <row r="486" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="486" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A486" s="24" t="s">
         <v>296</v>
       </c>
@@ -26731,7 +26740,7 @@
         <v>648</v>
       </c>
     </row>
-    <row r="487" spans="1:18" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="487" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A487" s="24" t="s">
         <v>296</v>
       </c>
@@ -26758,13 +26767,13 @@
         <v>919</v>
       </c>
     </row>
-    <row r="488" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="488" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A488" s="24" t="s">
         <v>374</v>
       </c>
       <c r="H488" s="24"/>
     </row>
-    <row r="489" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="489" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A489" s="24" t="s">
         <v>273</v>
       </c>
@@ -26776,7 +26785,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="490" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="490" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A490" s="24" t="s">
         <v>268</v>
       </c>
@@ -26795,7 +26804,7 @@
       <c r="Q490" s="12"/>
       <c r="R490" s="12"/>
     </row>
-    <row r="491" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="491" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A491" s="24" t="s">
         <v>296</v>
       </c>
@@ -26828,7 +26837,7 @@
         <v>648</v>
       </c>
     </row>
-    <row r="492" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="492" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A492" s="24" t="s">
         <v>296</v>
       </c>
@@ -26861,7 +26870,7 @@
         <v>648</v>
       </c>
     </row>
-    <row r="493" spans="1:18" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="493" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A493" s="24" t="s">
         <v>296</v>
       </c>
@@ -26888,13 +26897,13 @@
         <v>927</v>
       </c>
     </row>
-    <row r="494" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="494" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A494" s="24" t="s">
         <v>374</v>
       </c>
       <c r="H494" s="24"/>
     </row>
-    <row r="495" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="495" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A495" s="24" t="s">
         <v>273</v>
       </c>
@@ -26906,7 +26915,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="496" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="496" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A496" s="24" t="s">
         <v>268</v>
       </c>
@@ -26923,7 +26932,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="497" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="497" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A497" s="24" t="s">
         <v>296</v>
       </c>
@@ -26955,7 +26964,7 @@
         <v>648</v>
       </c>
     </row>
-    <row r="498" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="498" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A498" s="24" t="s">
         <v>296</v>
       </c>
@@ -26987,7 +26996,7 @@
         <v>648</v>
       </c>
     </row>
-    <row r="499" spans="1:18" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="499" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A499" s="24" t="s">
         <v>296</v>
       </c>
@@ -27014,13 +27023,13 @@
         <v>935</v>
       </c>
     </row>
-    <row r="500" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="500" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A500" s="24" t="s">
         <v>374</v>
       </c>
       <c r="H500" s="24"/>
     </row>
-    <row r="501" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="501" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A501" s="24" t="s">
         <v>273</v>
       </c>
@@ -27032,7 +27041,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="502" spans="1:18" s="33" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="502" spans="1:18" s="33" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A502" s="24" t="s">
         <v>268</v>
       </c>
@@ -27062,7 +27071,7 @@
       <c r="Q502" s="24"/>
       <c r="R502" s="24"/>
     </row>
-    <row r="503" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="503" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A503" s="24" t="s">
         <v>296</v>
       </c>
@@ -27094,7 +27103,7 @@
         <v>648</v>
       </c>
     </row>
-    <row r="504" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="504" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A504" s="24" t="s">
         <v>296</v>
       </c>
@@ -27126,7 +27135,7 @@
         <v>648</v>
       </c>
     </row>
-    <row r="505" spans="1:18" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="505" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A505" s="24" t="s">
         <v>296</v>
       </c>
@@ -27153,18 +27162,18 @@
         <v>943</v>
       </c>
     </row>
-    <row r="506" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="506" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A506" s="24" t="s">
         <v>374</v>
       </c>
       <c r="H506" s="24"/>
     </row>
-    <row r="507" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="507" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A507" s="24" t="s">
         <v>268</v>
       </c>
       <c r="B507" s="24" t="s">
-        <v>443</v>
+        <v>4219</v>
       </c>
       <c r="H507" s="24" t="s">
         <v>394</v>
@@ -27176,7 +27185,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="508" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="508" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A508" s="38" t="s">
         <v>296</v>
       </c>
@@ -27203,7 +27212,7 @@
         <v>945</v>
       </c>
     </row>
-    <row r="509" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="509" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A509" s="38" t="s">
         <v>296</v>
       </c>
@@ -27230,7 +27239,7 @@
         <v>947</v>
       </c>
     </row>
-    <row r="510" spans="1:18" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="510" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A510" s="24" t="s">
         <v>296</v>
       </c>
@@ -27315,7 +27324,7 @@
       <c r="Q513" s="33"/>
       <c r="R513" s="33"/>
     </row>
-    <row r="514" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="514" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A514" s="35" t="s">
         <v>382</v>
       </c>
@@ -27332,7 +27341,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="515" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="515" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A515" s="28" t="s">
         <v>268</v>
       </c>
@@ -27349,7 +27358,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="516" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="516" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A516" s="28" t="s">
         <v>268</v>
       </c>
@@ -27369,7 +27378,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="517" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="517" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A517" s="28" t="s">
         <v>268</v>
       </c>
@@ -27389,7 +27398,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="518" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="518" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A518" s="28" t="s">
         <v>268</v>
       </c>
@@ -27409,7 +27418,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="519" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="519" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A519" s="24" t="s">
         <v>273</v>
       </c>
@@ -27421,7 +27430,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="520" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="520" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A520" s="24" t="s">
         <v>268</v>
       </c>
@@ -27438,7 +27447,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="521" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="521" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A521" s="24" t="s">
         <v>296</v>
       </c>
@@ -27470,7 +27479,7 @@
         <v>648</v>
       </c>
     </row>
-    <row r="522" spans="1:18" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="522" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A522" s="24" t="s">
         <v>296</v>
       </c>
@@ -27502,7 +27511,7 @@
         <v>648</v>
       </c>
     </row>
-    <row r="523" spans="1:18" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="523" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A523" s="24" t="s">
         <v>296</v>
       </c>
@@ -27529,13 +27538,13 @@
         <v>964</v>
       </c>
     </row>
-    <row r="524" spans="1:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="524" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A524" s="24" t="s">
         <v>374</v>
       </c>
       <c r="H524" s="24"/>
     </row>
-    <row r="525" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="525" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A525" s="24" t="s">
         <v>273</v>
       </c>
@@ -27547,7 +27556,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="526" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="526" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A526" s="24" t="s">
         <v>268</v>
       </c>
@@ -27564,7 +27573,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="527" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="527" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A527" s="24" t="s">
         <v>296</v>
       </c>
@@ -27596,7 +27605,7 @@
         <v>648</v>
       </c>
     </row>
-    <row r="528" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="528" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A528" s="24" t="s">
         <v>296</v>
       </c>
@@ -27628,7 +27637,7 @@
         <v>648</v>
       </c>
     </row>
-    <row r="529" spans="1:18" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="529" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A529" s="24" t="s">
         <v>296</v>
       </c>
@@ -27655,13 +27664,13 @@
         <v>972</v>
       </c>
     </row>
-    <row r="530" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="530" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A530" s="24" t="s">
         <v>374</v>
       </c>
       <c r="H530" s="24"/>
     </row>
-    <row r="531" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="531" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A531" s="24" t="s">
         <v>273</v>
       </c>
@@ -27673,7 +27682,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="532" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="532" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A532" s="24" t="s">
         <v>268</v>
       </c>
@@ -27692,7 +27701,7 @@
       <c r="Q532" s="12"/>
       <c r="R532" s="12"/>
     </row>
-    <row r="533" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="533" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A533" s="24" t="s">
         <v>296</v>
       </c>
@@ -27724,7 +27733,7 @@
         <v>648</v>
       </c>
     </row>
-    <row r="534" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="534" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A534" s="24" t="s">
         <v>296</v>
       </c>
@@ -27756,7 +27765,7 @@
         <v>648</v>
       </c>
     </row>
-    <row r="535" spans="1:18" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="535" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A535" s="24" t="s">
         <v>296</v>
       </c>
@@ -27783,13 +27792,13 @@
         <v>980</v>
       </c>
     </row>
-    <row r="536" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="536" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A536" s="24" t="s">
         <v>374</v>
       </c>
       <c r="H536" s="24"/>
     </row>
-    <row r="537" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="537" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A537" s="24" t="s">
         <v>273</v>
       </c>
@@ -27801,7 +27810,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="538" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="538" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A538" s="24" t="s">
         <v>268</v>
       </c>
@@ -27818,7 +27827,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="539" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="539" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A539" s="24" t="s">
         <v>296</v>
       </c>
@@ -27850,7 +27859,7 @@
         <v>648</v>
       </c>
     </row>
-    <row r="540" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="540" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A540" s="24" t="s">
         <v>296</v>
       </c>
@@ -27882,7 +27891,7 @@
         <v>648</v>
       </c>
     </row>
-    <row r="541" spans="1:18" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="541" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A541" s="24" t="s">
         <v>296</v>
       </c>
@@ -27909,13 +27918,13 @@
         <v>988</v>
       </c>
     </row>
-    <row r="542" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="542" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A542" s="24" t="s">
         <v>374</v>
       </c>
       <c r="H542" s="24"/>
     </row>
-    <row r="543" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="543" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A543" s="24" t="s">
         <v>273</v>
       </c>
@@ -27927,7 +27936,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="544" spans="1:18" s="33" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="544" spans="1:18" s="33" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A544" s="24" t="s">
         <v>268</v>
       </c>
@@ -27957,7 +27966,7 @@
       <c r="Q544" s="24"/>
       <c r="R544" s="24"/>
     </row>
-    <row r="545" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="545" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A545" s="24" t="s">
         <v>296</v>
       </c>
@@ -27989,7 +27998,7 @@
         <v>648</v>
       </c>
     </row>
-    <row r="546" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="546" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A546" s="24" t="s">
         <v>296</v>
       </c>
@@ -28021,7 +28030,7 @@
         <v>648</v>
       </c>
     </row>
-    <row r="547" spans="1:18" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="547" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A547" s="24" t="s">
         <v>296</v>
       </c>
@@ -28048,18 +28057,18 @@
         <v>996</v>
       </c>
     </row>
-    <row r="548" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="548" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A548" s="24" t="s">
         <v>374</v>
       </c>
       <c r="H548" s="24"/>
     </row>
-    <row r="549" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="549" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A549" s="24" t="s">
         <v>268</v>
       </c>
       <c r="B549" s="24" t="s">
-        <v>443</v>
+        <v>4220</v>
       </c>
       <c r="H549" s="24" t="s">
         <v>394</v>
@@ -28071,7 +28080,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="550" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="550" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A550" s="38" t="s">
         <v>296</v>
       </c>
@@ -28098,7 +28107,7 @@
         <v>998</v>
       </c>
     </row>
-    <row r="551" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="551" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A551" s="38" t="s">
         <v>296</v>
       </c>
@@ -28125,7 +28134,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="552" spans="1:18" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="552" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A552" s="24" t="s">
         <v>296</v>
       </c>
@@ -28210,7 +28219,7 @@
       <c r="Q555" s="33"/>
       <c r="R555" s="33"/>
     </row>
-    <row r="556" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="556" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A556" s="35" t="s">
         <v>382</v>
       </c>
@@ -28227,7 +28236,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="557" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="557" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A557" s="28" t="s">
         <v>268</v>
       </c>
@@ -28244,7 +28253,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="558" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="558" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A558" s="28" t="s">
         <v>268</v>
       </c>
@@ -28264,7 +28273,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="559" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="559" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A559" s="28" t="s">
         <v>268</v>
       </c>
@@ -28284,7 +28293,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="560" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="560" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A560" s="28" t="s">
         <v>268</v>
       </c>
@@ -28304,7 +28313,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="561" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="561" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A561" s="24" t="s">
         <v>273</v>
       </c>
@@ -28316,7 +28325,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="562" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="562" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A562" s="24" t="s">
         <v>268</v>
       </c>
@@ -28333,7 +28342,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="563" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="563" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A563" s="24" t="s">
         <v>296</v>
       </c>
@@ -28365,7 +28374,7 @@
         <v>648</v>
       </c>
     </row>
-    <row r="564" spans="1:18" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="564" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A564" s="24" t="s">
         <v>296</v>
       </c>
@@ -28397,7 +28406,7 @@
         <v>648</v>
       </c>
     </row>
-    <row r="565" spans="1:18" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="565" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A565" s="24" t="s">
         <v>296</v>
       </c>
@@ -28424,13 +28433,13 @@
         <v>1017</v>
       </c>
     </row>
-    <row r="566" spans="1:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="566" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A566" s="24" t="s">
         <v>374</v>
       </c>
       <c r="H566" s="24"/>
     </row>
-    <row r="567" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="567" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A567" s="24" t="s">
         <v>273</v>
       </c>
@@ -28442,7 +28451,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="568" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="568" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A568" s="24" t="s">
         <v>268</v>
       </c>
@@ -28459,7 +28468,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="569" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="569" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A569" s="24" t="s">
         <v>296</v>
       </c>
@@ -28491,7 +28500,7 @@
         <v>648</v>
       </c>
     </row>
-    <row r="570" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="570" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A570" s="24" t="s">
         <v>296</v>
       </c>
@@ -28523,7 +28532,7 @@
         <v>648</v>
       </c>
     </row>
-    <row r="571" spans="1:18" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="571" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A571" s="24" t="s">
         <v>296</v>
       </c>
@@ -28550,13 +28559,13 @@
         <v>1025</v>
       </c>
     </row>
-    <row r="572" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="572" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A572" s="24" t="s">
         <v>374</v>
       </c>
       <c r="H572" s="24"/>
     </row>
-    <row r="573" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="573" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A573" s="24" t="s">
         <v>273</v>
       </c>
@@ -28568,7 +28577,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="574" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="574" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A574" s="24" t="s">
         <v>268</v>
       </c>
@@ -28587,7 +28596,7 @@
       <c r="Q574" s="12"/>
       <c r="R574" s="12"/>
     </row>
-    <row r="575" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="575" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A575" s="24" t="s">
         <v>296</v>
       </c>
@@ -28619,7 +28628,7 @@
         <v>648</v>
       </c>
     </row>
-    <row r="576" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="576" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A576" s="24" t="s">
         <v>296</v>
       </c>
@@ -28651,7 +28660,7 @@
         <v>648</v>
       </c>
     </row>
-    <row r="577" spans="1:18" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="577" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A577" s="24" t="s">
         <v>296</v>
       </c>
@@ -28678,13 +28687,13 @@
         <v>1033</v>
       </c>
     </row>
-    <row r="578" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="578" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A578" s="24" t="s">
         <v>374</v>
       </c>
       <c r="H578" s="24"/>
     </row>
-    <row r="579" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="579" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A579" s="24" t="s">
         <v>273</v>
       </c>
@@ -28696,7 +28705,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="580" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="580" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A580" s="24" t="s">
         <v>268</v>
       </c>
@@ -28713,7 +28722,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="581" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="581" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A581" s="24" t="s">
         <v>296</v>
       </c>
@@ -28745,7 +28754,7 @@
         <v>648</v>
       </c>
     </row>
-    <row r="582" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="582" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A582" s="24" t="s">
         <v>296</v>
       </c>
@@ -28777,7 +28786,7 @@
         <v>648</v>
       </c>
     </row>
-    <row r="583" spans="1:18" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="583" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A583" s="24" t="s">
         <v>296</v>
       </c>
@@ -28804,13 +28813,13 @@
         <v>1041</v>
       </c>
     </row>
-    <row r="584" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="584" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A584" s="24" t="s">
         <v>374</v>
       </c>
       <c r="H584" s="24"/>
     </row>
-    <row r="585" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="585" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A585" s="24" t="s">
         <v>273</v>
       </c>
@@ -28822,7 +28831,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="586" spans="1:18" s="33" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="586" spans="1:18" s="33" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A586" s="24" t="s">
         <v>268</v>
       </c>
@@ -28852,7 +28861,7 @@
       <c r="Q586" s="24"/>
       <c r="R586" s="24"/>
     </row>
-    <row r="587" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="587" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A587" s="24" t="s">
         <v>296</v>
       </c>
@@ -28884,7 +28893,7 @@
         <v>648</v>
       </c>
     </row>
-    <row r="588" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="588" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A588" s="24" t="s">
         <v>296</v>
       </c>
@@ -28916,7 +28925,7 @@
         <v>648</v>
       </c>
     </row>
-    <row r="589" spans="1:18" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="589" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A589" s="24" t="s">
         <v>296</v>
       </c>
@@ -28943,18 +28952,18 @@
         <v>1049</v>
       </c>
     </row>
-    <row r="590" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="590" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A590" s="24" t="s">
         <v>374</v>
       </c>
       <c r="H590" s="24"/>
     </row>
-    <row r="591" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="591" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A591" s="24" t="s">
         <v>268</v>
       </c>
       <c r="B591" s="24" t="s">
-        <v>443</v>
+        <v>4221</v>
       </c>
       <c r="H591" s="24" t="s">
         <v>394</v>
@@ -28966,7 +28975,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="592" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="592" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A592" s="38" t="s">
         <v>296</v>
       </c>
@@ -28993,7 +29002,7 @@
         <v>1051</v>
       </c>
     </row>
-    <row r="593" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="593" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A593" s="38" t="s">
         <v>296</v>
       </c>
@@ -29020,7 +29029,7 @@
         <v>1053</v>
       </c>
     </row>
-    <row r="594" spans="1:18" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="594" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A594" s="24" t="s">
         <v>296</v>
       </c>

--- a/s2.xlsx
+++ b/s2.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17509" uniqueCount="4222">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17509" uniqueCount="4226">
   <si>
     <t>list_name</t>
   </si>
@@ -12690,6 +12690,18 @@
   </si>
   <si>
     <t>table27d_note6</t>
+  </si>
+  <si>
+    <t>table27e_note6</t>
+  </si>
+  <si>
+    <t>table27f_note6</t>
+  </si>
+  <si>
+    <t>table27g_note6</t>
+  </si>
+  <si>
+    <t>table27h_note6</t>
   </si>
 </sst>
 </file>
@@ -26427,7 +26439,7 @@
       <c r="Q471" s="33"/>
       <c r="R471" s="33"/>
     </row>
-    <row r="472" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="472" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A472" s="35" t="s">
         <v>382</v>
       </c>
@@ -26444,7 +26456,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="473" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="473" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A473" s="28" t="s">
         <v>268</v>
       </c>
@@ -26461,7 +26473,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="474" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="474" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A474" s="28" t="s">
         <v>268</v>
       </c>
@@ -26481,7 +26493,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="475" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="475" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A475" s="28" t="s">
         <v>268</v>
       </c>
@@ -26501,7 +26513,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="476" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="476" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A476" s="28" t="s">
         <v>268</v>
       </c>
@@ -26521,7 +26533,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="477" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="477" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A477" s="24" t="s">
         <v>273</v>
       </c>
@@ -26533,7 +26545,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="478" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="478" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A478" s="24" t="s">
         <v>268</v>
       </c>
@@ -26550,7 +26562,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="479" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="479" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A479" s="24" t="s">
         <v>296</v>
       </c>
@@ -26582,7 +26594,7 @@
         <v>648</v>
       </c>
     </row>
-    <row r="480" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="480" spans="1:18" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A480" s="24" t="s">
         <v>296</v>
       </c>
@@ -26614,7 +26626,7 @@
         <v>648</v>
       </c>
     </row>
-    <row r="481" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:18" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A481" s="24" t="s">
         <v>296</v>
       </c>
@@ -26641,13 +26653,13 @@
         <v>911</v>
       </c>
     </row>
-    <row r="482" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="482" spans="1:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A482" s="24" t="s">
         <v>374</v>
       </c>
       <c r="H482" s="24"/>
     </row>
-    <row r="483" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="483" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A483" s="24" t="s">
         <v>273</v>
       </c>
@@ -26659,7 +26671,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="484" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="484" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A484" s="24" t="s">
         <v>268</v>
       </c>
@@ -26676,7 +26688,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="485" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="485" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A485" s="24" t="s">
         <v>296</v>
       </c>
@@ -26708,7 +26720,7 @@
         <v>648</v>
       </c>
     </row>
-    <row r="486" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="486" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A486" s="24" t="s">
         <v>296</v>
       </c>
@@ -26740,7 +26752,7 @@
         <v>648</v>
       </c>
     </row>
-    <row r="487" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="487" spans="1:18" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A487" s="24" t="s">
         <v>296</v>
       </c>
@@ -26767,13 +26779,13 @@
         <v>919</v>
       </c>
     </row>
-    <row r="488" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="488" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A488" s="24" t="s">
         <v>374</v>
       </c>
       <c r="H488" s="24"/>
     </row>
-    <row r="489" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="489" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A489" s="24" t="s">
         <v>273</v>
       </c>
@@ -26785,7 +26797,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="490" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="490" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A490" s="24" t="s">
         <v>268</v>
       </c>
@@ -26804,7 +26816,7 @@
       <c r="Q490" s="12"/>
       <c r="R490" s="12"/>
     </row>
-    <row r="491" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="491" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A491" s="24" t="s">
         <v>296</v>
       </c>
@@ -26837,7 +26849,7 @@
         <v>648</v>
       </c>
     </row>
-    <row r="492" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="492" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A492" s="24" t="s">
         <v>296</v>
       </c>
@@ -26870,7 +26882,7 @@
         <v>648</v>
       </c>
     </row>
-    <row r="493" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="493" spans="1:18" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A493" s="24" t="s">
         <v>296</v>
       </c>
@@ -26897,13 +26909,13 @@
         <v>927</v>
       </c>
     </row>
-    <row r="494" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="494" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A494" s="24" t="s">
         <v>374</v>
       </c>
       <c r="H494" s="24"/>
     </row>
-    <row r="495" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="495" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A495" s="24" t="s">
         <v>273</v>
       </c>
@@ -26915,7 +26927,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="496" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="496" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A496" s="24" t="s">
         <v>268</v>
       </c>
@@ -26932,7 +26944,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="497" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="497" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A497" s="24" t="s">
         <v>296</v>
       </c>
@@ -26964,7 +26976,7 @@
         <v>648</v>
       </c>
     </row>
-    <row r="498" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="498" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A498" s="24" t="s">
         <v>296</v>
       </c>
@@ -26996,7 +27008,7 @@
         <v>648</v>
       </c>
     </row>
-    <row r="499" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="499" spans="1:18" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A499" s="24" t="s">
         <v>296</v>
       </c>
@@ -27023,13 +27035,13 @@
         <v>935</v>
       </c>
     </row>
-    <row r="500" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="500" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A500" s="24" t="s">
         <v>374</v>
       </c>
       <c r="H500" s="24"/>
     </row>
-    <row r="501" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="501" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A501" s="24" t="s">
         <v>273</v>
       </c>
@@ -27041,7 +27053,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="502" spans="1:18" s="33" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="502" spans="1:18" s="33" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A502" s="24" t="s">
         <v>268</v>
       </c>
@@ -27071,7 +27083,7 @@
       <c r="Q502" s="24"/>
       <c r="R502" s="24"/>
     </row>
-    <row r="503" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="503" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A503" s="24" t="s">
         <v>296</v>
       </c>
@@ -27103,7 +27115,7 @@
         <v>648</v>
       </c>
     </row>
-    <row r="504" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="504" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A504" s="24" t="s">
         <v>296</v>
       </c>
@@ -27135,7 +27147,7 @@
         <v>648</v>
       </c>
     </row>
-    <row r="505" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="505" spans="1:18" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A505" s="24" t="s">
         <v>296</v>
       </c>
@@ -27162,13 +27174,13 @@
         <v>943</v>
       </c>
     </row>
-    <row r="506" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="506" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A506" s="24" t="s">
         <v>374</v>
       </c>
       <c r="H506" s="24"/>
     </row>
-    <row r="507" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="507" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A507" s="24" t="s">
         <v>268</v>
       </c>
@@ -27185,7 +27197,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="508" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="508" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A508" s="38" t="s">
         <v>296</v>
       </c>
@@ -27212,7 +27224,7 @@
         <v>945</v>
       </c>
     </row>
-    <row r="509" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="509" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A509" s="38" t="s">
         <v>296</v>
       </c>
@@ -27239,7 +27251,7 @@
         <v>947</v>
       </c>
     </row>
-    <row r="510" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="510" spans="1:18" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A510" s="24" t="s">
         <v>296</v>
       </c>
@@ -27324,7 +27336,7 @@
       <c r="Q513" s="33"/>
       <c r="R513" s="33"/>
     </row>
-    <row r="514" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="514" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A514" s="35" t="s">
         <v>382</v>
       </c>
@@ -27341,7 +27353,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="515" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="515" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A515" s="28" t="s">
         <v>268</v>
       </c>
@@ -27358,7 +27370,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="516" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="516" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A516" s="28" t="s">
         <v>268</v>
       </c>
@@ -27378,7 +27390,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="517" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="517" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A517" s="28" t="s">
         <v>268</v>
       </c>
@@ -27398,7 +27410,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="518" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="518" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A518" s="28" t="s">
         <v>268</v>
       </c>
@@ -27418,7 +27430,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="519" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="519" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A519" s="24" t="s">
         <v>273</v>
       </c>
@@ -27430,7 +27442,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="520" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="520" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A520" s="24" t="s">
         <v>268</v>
       </c>
@@ -27447,7 +27459,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="521" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="521" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A521" s="24" t="s">
         <v>296</v>
       </c>
@@ -27479,7 +27491,7 @@
         <v>648</v>
       </c>
     </row>
-    <row r="522" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="522" spans="1:18" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A522" s="24" t="s">
         <v>296</v>
       </c>
@@ -27511,7 +27523,7 @@
         <v>648</v>
       </c>
     </row>
-    <row r="523" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="523" spans="1:18" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A523" s="24" t="s">
         <v>296</v>
       </c>
@@ -27538,13 +27550,13 @@
         <v>964</v>
       </c>
     </row>
-    <row r="524" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="524" spans="1:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A524" s="24" t="s">
         <v>374</v>
       </c>
       <c r="H524" s="24"/>
     </row>
-    <row r="525" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="525" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A525" s="24" t="s">
         <v>273</v>
       </c>
@@ -27556,7 +27568,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="526" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="526" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A526" s="24" t="s">
         <v>268</v>
       </c>
@@ -27573,7 +27585,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="527" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="527" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A527" s="24" t="s">
         <v>296</v>
       </c>
@@ -27605,7 +27617,7 @@
         <v>648</v>
       </c>
     </row>
-    <row r="528" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="528" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A528" s="24" t="s">
         <v>296</v>
       </c>
@@ -27637,7 +27649,7 @@
         <v>648</v>
       </c>
     </row>
-    <row r="529" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="529" spans="1:18" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A529" s="24" t="s">
         <v>296</v>
       </c>
@@ -27664,13 +27676,13 @@
         <v>972</v>
       </c>
     </row>
-    <row r="530" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="530" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A530" s="24" t="s">
         <v>374</v>
       </c>
       <c r="H530" s="24"/>
     </row>
-    <row r="531" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="531" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A531" s="24" t="s">
         <v>273</v>
       </c>
@@ -27682,7 +27694,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="532" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="532" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A532" s="24" t="s">
         <v>268</v>
       </c>
@@ -27701,7 +27713,7 @@
       <c r="Q532" s="12"/>
       <c r="R532" s="12"/>
     </row>
-    <row r="533" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="533" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A533" s="24" t="s">
         <v>296</v>
       </c>
@@ -27733,7 +27745,7 @@
         <v>648</v>
       </c>
     </row>
-    <row r="534" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="534" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A534" s="24" t="s">
         <v>296</v>
       </c>
@@ -27765,7 +27777,7 @@
         <v>648</v>
       </c>
     </row>
-    <row r="535" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="535" spans="1:18" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A535" s="24" t="s">
         <v>296</v>
       </c>
@@ -27792,13 +27804,13 @@
         <v>980</v>
       </c>
     </row>
-    <row r="536" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="536" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A536" s="24" t="s">
         <v>374</v>
       </c>
       <c r="H536" s="24"/>
     </row>
-    <row r="537" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="537" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A537" s="24" t="s">
         <v>273</v>
       </c>
@@ -27810,7 +27822,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="538" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="538" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A538" s="24" t="s">
         <v>268</v>
       </c>
@@ -27827,7 +27839,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="539" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="539" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A539" s="24" t="s">
         <v>296</v>
       </c>
@@ -27859,7 +27871,7 @@
         <v>648</v>
       </c>
     </row>
-    <row r="540" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="540" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A540" s="24" t="s">
         <v>296</v>
       </c>
@@ -27891,7 +27903,7 @@
         <v>648</v>
       </c>
     </row>
-    <row r="541" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="541" spans="1:18" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A541" s="24" t="s">
         <v>296</v>
       </c>
@@ -27918,13 +27930,13 @@
         <v>988</v>
       </c>
     </row>
-    <row r="542" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="542" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A542" s="24" t="s">
         <v>374</v>
       </c>
       <c r="H542" s="24"/>
     </row>
-    <row r="543" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="543" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A543" s="24" t="s">
         <v>273</v>
       </c>
@@ -27936,7 +27948,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="544" spans="1:18" s="33" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="544" spans="1:18" s="33" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A544" s="24" t="s">
         <v>268</v>
       </c>
@@ -27966,7 +27978,7 @@
       <c r="Q544" s="24"/>
       <c r="R544" s="24"/>
     </row>
-    <row r="545" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="545" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A545" s="24" t="s">
         <v>296</v>
       </c>
@@ -27998,7 +28010,7 @@
         <v>648</v>
       </c>
     </row>
-    <row r="546" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="546" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A546" s="24" t="s">
         <v>296</v>
       </c>
@@ -28030,7 +28042,7 @@
         <v>648</v>
       </c>
     </row>
-    <row r="547" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="547" spans="1:18" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A547" s="24" t="s">
         <v>296</v>
       </c>
@@ -28057,13 +28069,13 @@
         <v>996</v>
       </c>
     </row>
-    <row r="548" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="548" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A548" s="24" t="s">
         <v>374</v>
       </c>
       <c r="H548" s="24"/>
     </row>
-    <row r="549" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="549" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A549" s="24" t="s">
         <v>268</v>
       </c>
@@ -28080,7 +28092,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="550" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="550" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A550" s="38" t="s">
         <v>296</v>
       </c>
@@ -28107,7 +28119,7 @@
         <v>998</v>
       </c>
     </row>
-    <row r="551" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="551" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A551" s="38" t="s">
         <v>296</v>
       </c>
@@ -28134,7 +28146,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="552" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="552" spans="1:18" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A552" s="24" t="s">
         <v>296</v>
       </c>
@@ -28219,7 +28231,7 @@
       <c r="Q555" s="33"/>
       <c r="R555" s="33"/>
     </row>
-    <row r="556" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="556" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A556" s="35" t="s">
         <v>382</v>
       </c>
@@ -28236,7 +28248,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="557" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="557" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A557" s="28" t="s">
         <v>268</v>
       </c>
@@ -28253,7 +28265,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="558" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="558" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A558" s="28" t="s">
         <v>268</v>
       </c>
@@ -28273,7 +28285,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="559" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="559" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A559" s="28" t="s">
         <v>268</v>
       </c>
@@ -28293,7 +28305,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="560" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="560" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A560" s="28" t="s">
         <v>268</v>
       </c>
@@ -28313,7 +28325,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="561" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="561" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A561" s="24" t="s">
         <v>273</v>
       </c>
@@ -28325,7 +28337,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="562" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="562" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A562" s="24" t="s">
         <v>268</v>
       </c>
@@ -28342,7 +28354,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="563" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="563" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A563" s="24" t="s">
         <v>296</v>
       </c>
@@ -28374,7 +28386,7 @@
         <v>648</v>
       </c>
     </row>
-    <row r="564" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="564" spans="1:18" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A564" s="24" t="s">
         <v>296</v>
       </c>
@@ -28406,7 +28418,7 @@
         <v>648</v>
       </c>
     </row>
-    <row r="565" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="565" spans="1:18" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A565" s="24" t="s">
         <v>296</v>
       </c>
@@ -28433,13 +28445,13 @@
         <v>1017</v>
       </c>
     </row>
-    <row r="566" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="566" spans="1:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A566" s="24" t="s">
         <v>374</v>
       </c>
       <c r="H566" s="24"/>
     </row>
-    <row r="567" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="567" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A567" s="24" t="s">
         <v>273</v>
       </c>
@@ -28451,7 +28463,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="568" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="568" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A568" s="24" t="s">
         <v>268</v>
       </c>
@@ -28468,7 +28480,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="569" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="569" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A569" s="24" t="s">
         <v>296</v>
       </c>
@@ -28500,7 +28512,7 @@
         <v>648</v>
       </c>
     </row>
-    <row r="570" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="570" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A570" s="24" t="s">
         <v>296</v>
       </c>
@@ -28532,7 +28544,7 @@
         <v>648</v>
       </c>
     </row>
-    <row r="571" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="571" spans="1:18" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A571" s="24" t="s">
         <v>296</v>
       </c>
@@ -28559,13 +28571,13 @@
         <v>1025</v>
       </c>
     </row>
-    <row r="572" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="572" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A572" s="24" t="s">
         <v>374</v>
       </c>
       <c r="H572" s="24"/>
     </row>
-    <row r="573" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="573" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A573" s="24" t="s">
         <v>273</v>
       </c>
@@ -28577,7 +28589,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="574" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="574" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A574" s="24" t="s">
         <v>268</v>
       </c>
@@ -28596,7 +28608,7 @@
       <c r="Q574" s="12"/>
       <c r="R574" s="12"/>
     </row>
-    <row r="575" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="575" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A575" s="24" t="s">
         <v>296</v>
       </c>
@@ -28628,7 +28640,7 @@
         <v>648</v>
       </c>
     </row>
-    <row r="576" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="576" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A576" s="24" t="s">
         <v>296</v>
       </c>
@@ -28660,7 +28672,7 @@
         <v>648</v>
       </c>
     </row>
-    <row r="577" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="577" spans="1:18" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A577" s="24" t="s">
         <v>296</v>
       </c>
@@ -28687,13 +28699,13 @@
         <v>1033</v>
       </c>
     </row>
-    <row r="578" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="578" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A578" s="24" t="s">
         <v>374</v>
       </c>
       <c r="H578" s="24"/>
     </row>
-    <row r="579" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="579" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A579" s="24" t="s">
         <v>273</v>
       </c>
@@ -28705,7 +28717,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="580" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="580" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A580" s="24" t="s">
         <v>268</v>
       </c>
@@ -28722,7 +28734,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="581" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="581" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A581" s="24" t="s">
         <v>296</v>
       </c>
@@ -28754,7 +28766,7 @@
         <v>648</v>
       </c>
     </row>
-    <row r="582" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="582" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A582" s="24" t="s">
         <v>296</v>
       </c>
@@ -28786,7 +28798,7 @@
         <v>648</v>
       </c>
     </row>
-    <row r="583" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="583" spans="1:18" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A583" s="24" t="s">
         <v>296</v>
       </c>
@@ -28813,13 +28825,13 @@
         <v>1041</v>
       </c>
     </row>
-    <row r="584" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="584" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A584" s="24" t="s">
         <v>374</v>
       </c>
       <c r="H584" s="24"/>
     </row>
-    <row r="585" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="585" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A585" s="24" t="s">
         <v>273</v>
       </c>
@@ -28831,7 +28843,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="586" spans="1:18" s="33" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="586" spans="1:18" s="33" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A586" s="24" t="s">
         <v>268</v>
       </c>
@@ -28861,7 +28873,7 @@
       <c r="Q586" s="24"/>
       <c r="R586" s="24"/>
     </row>
-    <row r="587" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="587" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A587" s="24" t="s">
         <v>296</v>
       </c>
@@ -28893,7 +28905,7 @@
         <v>648</v>
       </c>
     </row>
-    <row r="588" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="588" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A588" s="24" t="s">
         <v>296</v>
       </c>
@@ -28925,7 +28937,7 @@
         <v>648</v>
       </c>
     </row>
-    <row r="589" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="589" spans="1:18" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A589" s="24" t="s">
         <v>296</v>
       </c>
@@ -28952,13 +28964,13 @@
         <v>1049</v>
       </c>
     </row>
-    <row r="590" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="590" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A590" s="24" t="s">
         <v>374</v>
       </c>
       <c r="H590" s="24"/>
     </row>
-    <row r="591" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="591" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A591" s="24" t="s">
         <v>268</v>
       </c>
@@ -28975,7 +28987,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="592" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="592" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A592" s="38" t="s">
         <v>296</v>
       </c>
@@ -29002,7 +29014,7 @@
         <v>1051</v>
       </c>
     </row>
-    <row r="593" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="593" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A593" s="38" t="s">
         <v>296</v>
       </c>
@@ -29029,7 +29041,7 @@
         <v>1053</v>
       </c>
     </row>
-    <row r="594" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="594" spans="1:18" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A594" s="24" t="s">
         <v>296</v>
       </c>
@@ -29114,7 +29126,7 @@
       <c r="Q597" s="33"/>
       <c r="R597" s="33"/>
     </row>
-    <row r="598" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="598" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A598" s="35" t="s">
         <v>382</v>
       </c>
@@ -29131,7 +29143,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="599" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="599" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A599" s="28" t="s">
         <v>268</v>
       </c>
@@ -29148,7 +29160,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="600" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="600" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A600" s="28" t="s">
         <v>268</v>
       </c>
@@ -29168,7 +29180,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="601" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="601" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A601" s="28" t="s">
         <v>268</v>
       </c>
@@ -29188,7 +29200,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="602" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="602" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A602" s="28" t="s">
         <v>268</v>
       </c>
@@ -29208,7 +29220,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="603" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="603" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A603" s="24" t="s">
         <v>273</v>
       </c>
@@ -29220,7 +29232,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="604" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="604" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A604" s="24" t="s">
         <v>268</v>
       </c>
@@ -29237,7 +29249,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="605" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="605" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A605" s="24" t="s">
         <v>296</v>
       </c>
@@ -29263,7 +29275,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="606" spans="1:18" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="606" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A606" s="24" t="s">
         <v>296</v>
       </c>
@@ -29289,7 +29301,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="607" spans="1:18" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="607" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A607" s="24" t="s">
         <v>296</v>
       </c>
@@ -29316,13 +29328,13 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="608" spans="1:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="608" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A608" s="24" t="s">
         <v>374</v>
       </c>
       <c r="H608" s="24"/>
     </row>
-    <row r="609" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="609" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A609" s="24" t="s">
         <v>273</v>
       </c>
@@ -29334,7 +29346,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="610" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="610" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A610" s="24" t="s">
         <v>268</v>
       </c>
@@ -29351,7 +29363,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="611" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="611" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A611" s="24" t="s">
         <v>296</v>
       </c>
@@ -29377,7 +29389,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="612" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="612" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A612" s="24" t="s">
         <v>296</v>
       </c>
@@ -29403,7 +29415,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="613" spans="1:15" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="613" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A613" s="24" t="s">
         <v>296</v>
       </c>
@@ -29430,13 +29442,13 @@
         <v>1074</v>
       </c>
     </row>
-    <row r="614" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="614" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A614" s="24" t="s">
         <v>374</v>
       </c>
       <c r="H614" s="24"/>
     </row>
-    <row r="615" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="615" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A615" s="24" t="s">
         <v>273</v>
       </c>
@@ -29448,7 +29460,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="616" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="616" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A616" s="24" t="s">
         <v>268</v>
       </c>
@@ -29465,7 +29477,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="617" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="617" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A617" s="24" t="s">
         <v>296</v>
       </c>
@@ -29491,7 +29503,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="618" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="618" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A618" s="24" t="s">
         <v>296</v>
       </c>
@@ -29517,7 +29529,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="619" spans="1:15" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="619" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A619" s="24" t="s">
         <v>296</v>
       </c>
@@ -29544,13 +29556,13 @@
         <v>1080</v>
       </c>
     </row>
-    <row r="620" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="620" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A620" s="24" t="s">
         <v>374</v>
       </c>
       <c r="H620" s="24"/>
     </row>
-    <row r="621" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="621" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A621" s="24" t="s">
         <v>273</v>
       </c>
@@ -29562,7 +29574,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="622" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="622" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A622" s="24" t="s">
         <v>268</v>
       </c>
@@ -29579,7 +29591,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="623" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="623" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A623" s="24" t="s">
         <v>296</v>
       </c>
@@ -29605,7 +29617,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="624" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="624" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A624" s="24" t="s">
         <v>296</v>
       </c>
@@ -29631,7 +29643,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="625" spans="1:18" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="625" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A625" s="24" t="s">
         <v>296</v>
       </c>
@@ -29658,13 +29670,13 @@
         <v>1086</v>
       </c>
     </row>
-    <row r="626" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="626" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A626" s="24" t="s">
         <v>374</v>
       </c>
       <c r="H626" s="24"/>
     </row>
-    <row r="627" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="627" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A627" s="24" t="s">
         <v>273</v>
       </c>
@@ -29676,7 +29688,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="628" spans="1:18" s="33" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="628" spans="1:18" s="33" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A628" s="24" t="s">
         <v>268</v>
       </c>
@@ -29706,7 +29718,7 @@
       <c r="Q628" s="24"/>
       <c r="R628" s="24"/>
     </row>
-    <row r="629" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="629" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A629" s="24" t="s">
         <v>296</v>
       </c>
@@ -29732,7 +29744,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="630" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="630" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A630" s="24" t="s">
         <v>296</v>
       </c>
@@ -29758,7 +29770,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="631" spans="1:18" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="631" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A631" s="24" t="s">
         <v>296</v>
       </c>
@@ -29785,18 +29797,18 @@
         <v>1094</v>
       </c>
     </row>
-    <row r="632" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="632" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A632" s="24" t="s">
         <v>374</v>
       </c>
       <c r="H632" s="24"/>
     </row>
-    <row r="633" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="633" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A633" s="24" t="s">
         <v>268</v>
       </c>
       <c r="B633" s="24" t="s">
-        <v>443</v>
+        <v>4222</v>
       </c>
       <c r="H633" s="24" t="s">
         <v>394</v>
@@ -29808,7 +29820,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="634" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="634" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A634" s="38" t="s">
         <v>296</v>
       </c>
@@ -29835,7 +29847,7 @@
         <v>1096</v>
       </c>
     </row>
-    <row r="635" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="635" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A635" s="38" t="s">
         <v>296</v>
       </c>
@@ -29862,7 +29874,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="636" spans="1:18" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="636" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A636" s="24" t="s">
         <v>296</v>
       </c>
@@ -29947,7 +29959,7 @@
       <c r="Q639" s="33"/>
       <c r="R639" s="33"/>
     </row>
-    <row r="640" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="640" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A640" s="35" t="s">
         <v>382</v>
       </c>
@@ -29964,7 +29976,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="641" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="641" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A641" s="28" t="s">
         <v>268</v>
       </c>
@@ -29981,7 +29993,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="642" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="642" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A642" s="28" t="s">
         <v>268</v>
       </c>
@@ -30001,7 +30013,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="643" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="643" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A643" s="28" t="s">
         <v>268</v>
       </c>
@@ -30021,7 +30033,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="644" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="644" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A644" s="28" t="s">
         <v>268</v>
       </c>
@@ -30041,7 +30053,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="645" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="645" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A645" s="24" t="s">
         <v>273</v>
       </c>
@@ -30053,7 +30065,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="646" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="646" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A646" s="24" t="s">
         <v>268</v>
       </c>
@@ -30070,7 +30082,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="647" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="647" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A647" s="24" t="s">
         <v>296</v>
       </c>
@@ -30096,7 +30108,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="648" spans="1:15" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="648" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A648" s="24" t="s">
         <v>296</v>
       </c>
@@ -30122,7 +30134,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="649" spans="1:15" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="649" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A649" s="24" t="s">
         <v>296</v>
       </c>
@@ -30149,13 +30161,13 @@
         <v>1113</v>
       </c>
     </row>
-    <row r="650" spans="1:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="650" spans="1:15" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A650" s="24" t="s">
         <v>374</v>
       </c>
       <c r="H650" s="24"/>
     </row>
-    <row r="651" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="651" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A651" s="24" t="s">
         <v>273</v>
       </c>
@@ -30167,7 +30179,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="652" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="652" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A652" s="24" t="s">
         <v>268</v>
       </c>
@@ -30184,7 +30196,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="653" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="653" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A653" s="24" t="s">
         <v>296</v>
       </c>
@@ -30210,7 +30222,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="654" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="654" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A654" s="24" t="s">
         <v>296</v>
       </c>
@@ -30236,7 +30248,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="655" spans="1:15" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="655" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A655" s="24" t="s">
         <v>296</v>
       </c>
@@ -30263,13 +30275,13 @@
         <v>1119</v>
       </c>
     </row>
-    <row r="656" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="656" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A656" s="24" t="s">
         <v>374</v>
       </c>
       <c r="H656" s="24"/>
     </row>
-    <row r="657" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="657" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A657" s="24" t="s">
         <v>273</v>
       </c>
@@ -30281,7 +30293,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="658" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="658" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A658" s="24" t="s">
         <v>268</v>
       </c>
@@ -30298,7 +30310,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="659" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="659" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A659" s="24" t="s">
         <v>296</v>
       </c>
@@ -30324,7 +30336,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="660" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="660" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A660" s="24" t="s">
         <v>296</v>
       </c>
@@ -30350,7 +30362,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="661" spans="1:18" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="661" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A661" s="24" t="s">
         <v>296</v>
       </c>
@@ -30377,13 +30389,13 @@
         <v>1125</v>
       </c>
     </row>
-    <row r="662" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="662" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A662" s="24" t="s">
         <v>374</v>
       </c>
       <c r="H662" s="24"/>
     </row>
-    <row r="663" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="663" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A663" s="24" t="s">
         <v>273</v>
       </c>
@@ -30395,7 +30407,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="664" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="664" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A664" s="24" t="s">
         <v>268</v>
       </c>
@@ -30412,7 +30424,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="665" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="665" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A665" s="24" t="s">
         <v>296</v>
       </c>
@@ -30438,7 +30450,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="666" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="666" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A666" s="24" t="s">
         <v>296</v>
       </c>
@@ -30464,7 +30476,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="667" spans="1:18" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="667" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A667" s="24" t="s">
         <v>296</v>
       </c>
@@ -30491,13 +30503,13 @@
         <v>1131</v>
       </c>
     </row>
-    <row r="668" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="668" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A668" s="24" t="s">
         <v>374</v>
       </c>
       <c r="H668" s="24"/>
     </row>
-    <row r="669" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="669" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A669" s="24" t="s">
         <v>273</v>
       </c>
@@ -30509,7 +30521,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="670" spans="1:18" s="33" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="670" spans="1:18" s="33" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A670" s="24" t="s">
         <v>268</v>
       </c>
@@ -30539,7 +30551,7 @@
       <c r="Q670" s="24"/>
       <c r="R670" s="24"/>
     </row>
-    <row r="671" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="671" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A671" s="24" t="s">
         <v>296</v>
       </c>
@@ -30565,7 +30577,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="672" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="672" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A672" s="24" t="s">
         <v>296</v>
       </c>
@@ -30591,7 +30603,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="673" spans="1:18" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="673" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A673" s="24" t="s">
         <v>296</v>
       </c>
@@ -30618,18 +30630,18 @@
         <v>1137</v>
       </c>
     </row>
-    <row r="674" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="674" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A674" s="24" t="s">
         <v>374</v>
       </c>
       <c r="H674" s="24"/>
     </row>
-    <row r="675" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="675" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A675" s="24" t="s">
         <v>268</v>
       </c>
       <c r="B675" s="24" t="s">
-        <v>443</v>
+        <v>4223</v>
       </c>
       <c r="H675" s="24" t="s">
         <v>394</v>
@@ -30641,7 +30653,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="676" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="676" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A676" s="38" t="s">
         <v>296</v>
       </c>
@@ -30668,7 +30680,7 @@
         <v>1139</v>
       </c>
     </row>
-    <row r="677" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="677" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A677" s="38" t="s">
         <v>296</v>
       </c>
@@ -30695,7 +30707,7 @@
         <v>1141</v>
       </c>
     </row>
-    <row r="678" spans="1:18" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="678" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A678" s="24" t="s">
         <v>296</v>
       </c>
@@ -30780,7 +30792,7 @@
       <c r="Q681" s="33"/>
       <c r="R681" s="33"/>
     </row>
-    <row r="682" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="682" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A682" s="35" t="s">
         <v>382</v>
       </c>
@@ -30797,7 +30809,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="683" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="683" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A683" s="28" t="s">
         <v>268</v>
       </c>
@@ -30814,7 +30826,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="684" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="684" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A684" s="28" t="s">
         <v>268</v>
       </c>
@@ -30834,7 +30846,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="685" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="685" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A685" s="28" t="s">
         <v>268</v>
       </c>
@@ -30854,7 +30866,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="686" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="686" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A686" s="28" t="s">
         <v>268</v>
       </c>
@@ -30874,7 +30886,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="687" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="687" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A687" s="24" t="s">
         <v>273</v>
       </c>
@@ -30886,7 +30898,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="688" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="688" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A688" s="24" t="s">
         <v>268</v>
       </c>
@@ -30903,7 +30915,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="689" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="689" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A689" s="24" t="s">
         <v>296</v>
       </c>
@@ -30929,7 +30941,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="690" spans="1:15" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="690" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A690" s="24" t="s">
         <v>296</v>
       </c>
@@ -30955,7 +30967,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="691" spans="1:15" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="691" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A691" s="24" t="s">
         <v>296</v>
       </c>
@@ -30982,13 +30994,13 @@
         <v>1156</v>
       </c>
     </row>
-    <row r="692" spans="1:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="692" spans="1:15" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A692" s="24" t="s">
         <v>374</v>
       </c>
       <c r="H692" s="24"/>
     </row>
-    <row r="693" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="693" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A693" s="24" t="s">
         <v>273</v>
       </c>
@@ -31000,7 +31012,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="694" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="694" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A694" s="24" t="s">
         <v>268</v>
       </c>
@@ -31017,7 +31029,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="695" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="695" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A695" s="24" t="s">
         <v>296</v>
       </c>
@@ -31043,7 +31055,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="696" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="696" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A696" s="24" t="s">
         <v>296</v>
       </c>
@@ -31069,7 +31081,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="697" spans="1:15" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="697" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A697" s="24" t="s">
         <v>296</v>
       </c>
@@ -31096,13 +31108,13 @@
         <v>1162</v>
       </c>
     </row>
-    <row r="698" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="698" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A698" s="24" t="s">
         <v>374</v>
       </c>
       <c r="H698" s="24"/>
     </row>
-    <row r="699" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="699" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A699" s="24" t="s">
         <v>273</v>
       </c>
@@ -31114,7 +31126,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="700" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="700" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A700" s="24" t="s">
         <v>268</v>
       </c>
@@ -31131,7 +31143,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="701" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="701" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A701" s="24" t="s">
         <v>296</v>
       </c>
@@ -31157,7 +31169,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="702" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="702" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A702" s="24" t="s">
         <v>296</v>
       </c>
@@ -31183,7 +31195,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="703" spans="1:15" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="703" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A703" s="24" t="s">
         <v>296</v>
       </c>
@@ -31210,13 +31222,13 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="704" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="704" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A704" s="24" t="s">
         <v>374</v>
       </c>
       <c r="H704" s="24"/>
     </row>
-    <row r="705" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="705" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A705" s="24" t="s">
         <v>273</v>
       </c>
@@ -31228,7 +31240,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="706" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="706" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A706" s="24" t="s">
         <v>268</v>
       </c>
@@ -31245,7 +31257,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="707" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="707" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A707" s="24" t="s">
         <v>296</v>
       </c>
@@ -31271,7 +31283,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="708" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="708" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A708" s="24" t="s">
         <v>296</v>
       </c>
@@ -31297,7 +31309,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="709" spans="1:18" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="709" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A709" s="24" t="s">
         <v>296</v>
       </c>
@@ -31324,13 +31336,13 @@
         <v>1174</v>
       </c>
     </row>
-    <row r="710" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="710" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A710" s="24" t="s">
         <v>374</v>
       </c>
       <c r="H710" s="24"/>
     </row>
-    <row r="711" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="711" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A711" s="24" t="s">
         <v>273</v>
       </c>
@@ -31342,7 +31354,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="712" spans="1:18" s="33" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="712" spans="1:18" s="33" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A712" s="24" t="s">
         <v>268</v>
       </c>
@@ -31372,7 +31384,7 @@
       <c r="Q712" s="24"/>
       <c r="R712" s="24"/>
     </row>
-    <row r="713" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="713" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A713" s="24" t="s">
         <v>296</v>
       </c>
@@ -31398,7 +31410,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="714" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="714" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A714" s="24" t="s">
         <v>296</v>
       </c>
@@ -31424,7 +31436,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="715" spans="1:18" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="715" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A715" s="24" t="s">
         <v>296</v>
       </c>
@@ -31451,18 +31463,18 @@
         <v>1180</v>
       </c>
     </row>
-    <row r="716" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="716" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A716" s="24" t="s">
         <v>374</v>
       </c>
       <c r="H716" s="24"/>
     </row>
-    <row r="717" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="717" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A717" s="24" t="s">
         <v>268</v>
       </c>
       <c r="B717" s="24" t="s">
-        <v>443</v>
+        <v>4224</v>
       </c>
       <c r="H717" s="24" t="s">
         <v>394</v>
@@ -31474,7 +31486,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="718" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="718" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A718" s="38" t="s">
         <v>296</v>
       </c>
@@ -31501,7 +31513,7 @@
         <v>1182</v>
       </c>
     </row>
-    <row r="719" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="719" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A719" s="38" t="s">
         <v>296</v>
       </c>
@@ -31528,7 +31540,7 @@
         <v>1184</v>
       </c>
     </row>
-    <row r="720" spans="1:18" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="720" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A720" s="24" t="s">
         <v>296</v>
       </c>
@@ -31613,7 +31625,7 @@
       <c r="Q723" s="33"/>
       <c r="R723" s="33"/>
     </row>
-    <row r="724" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="724" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A724" s="35" t="s">
         <v>382</v>
       </c>
@@ -31630,7 +31642,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="725" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="725" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A725" s="28" t="s">
         <v>268</v>
       </c>
@@ -31647,7 +31659,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="726" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="726" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A726" s="28" t="s">
         <v>268</v>
       </c>
@@ -31667,7 +31679,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="727" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="727" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A727" s="28" t="s">
         <v>268</v>
       </c>
@@ -31687,7 +31699,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="728" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="728" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A728" s="28" t="s">
         <v>268</v>
       </c>
@@ -31707,7 +31719,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="729" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="729" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A729" s="24" t="s">
         <v>273</v>
       </c>
@@ -31719,7 +31731,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="730" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="730" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A730" s="24" t="s">
         <v>268</v>
       </c>
@@ -31736,7 +31748,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="731" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="731" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A731" s="24" t="s">
         <v>296</v>
       </c>
@@ -31762,7 +31774,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="732" spans="1:18" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="732" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A732" s="24" t="s">
         <v>296</v>
       </c>
@@ -31788,7 +31800,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="733" spans="1:18" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="733" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A733" s="24" t="s">
         <v>296</v>
       </c>
@@ -31815,13 +31827,13 @@
         <v>1199</v>
       </c>
     </row>
-    <row r="734" spans="1:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="734" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A734" s="24" t="s">
         <v>374</v>
       </c>
       <c r="H734" s="24"/>
     </row>
-    <row r="735" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="735" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A735" s="24" t="s">
         <v>273</v>
       </c>
@@ -31833,7 +31845,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="736" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="736" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A736" s="24" t="s">
         <v>268</v>
       </c>
@@ -31850,7 +31862,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="737" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="737" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A737" s="24" t="s">
         <v>296</v>
       </c>
@@ -31876,7 +31888,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="738" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="738" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A738" s="24" t="s">
         <v>296</v>
       </c>
@@ -31902,7 +31914,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="739" spans="1:15" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="739" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A739" s="24" t="s">
         <v>296</v>
       </c>
@@ -31929,13 +31941,13 @@
         <v>1205</v>
       </c>
     </row>
-    <row r="740" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="740" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A740" s="24" t="s">
         <v>374</v>
       </c>
       <c r="H740" s="24"/>
     </row>
-    <row r="741" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="741" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A741" s="24" t="s">
         <v>273</v>
       </c>
@@ -31947,7 +31959,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="742" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="742" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A742" s="24" t="s">
         <v>268</v>
       </c>
@@ -31964,7 +31976,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="743" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="743" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A743" s="24" t="s">
         <v>296</v>
       </c>
@@ -31990,7 +32002,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="744" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="744" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A744" s="24" t="s">
         <v>296</v>
       </c>
@@ -32016,7 +32028,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="745" spans="1:15" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="745" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A745" s="24" t="s">
         <v>296</v>
       </c>
@@ -32043,13 +32055,13 @@
         <v>1211</v>
       </c>
     </row>
-    <row r="746" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="746" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A746" s="24" t="s">
         <v>374</v>
       </c>
       <c r="H746" s="24"/>
     </row>
-    <row r="747" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="747" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A747" s="24" t="s">
         <v>273</v>
       </c>
@@ -32061,7 +32073,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="748" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="748" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A748" s="24" t="s">
         <v>268</v>
       </c>
@@ -32078,7 +32090,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="749" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="749" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A749" s="24" t="s">
         <v>296</v>
       </c>
@@ -32104,7 +32116,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="750" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="750" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A750" s="24" t="s">
         <v>296</v>
       </c>
@@ -32130,7 +32142,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="751" spans="1:15" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="751" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A751" s="24" t="s">
         <v>296</v>
       </c>
@@ -32157,13 +32169,13 @@
         <v>1217</v>
       </c>
     </row>
-    <row r="752" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="752" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A752" s="24" t="s">
         <v>374</v>
       </c>
       <c r="H752" s="24"/>
     </row>
-    <row r="753" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="753" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A753" s="24" t="s">
         <v>273</v>
       </c>
@@ -32175,7 +32187,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="754" spans="1:18" s="33" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="754" spans="1:18" s="33" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A754" s="24" t="s">
         <v>268</v>
       </c>
@@ -32205,7 +32217,7 @@
       <c r="Q754" s="24"/>
       <c r="R754" s="24"/>
     </row>
-    <row r="755" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="755" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A755" s="24" t="s">
         <v>296</v>
       </c>
@@ -32231,7 +32243,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="756" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="756" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A756" s="24" t="s">
         <v>296</v>
       </c>
@@ -32257,7 +32269,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="757" spans="1:18" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="757" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A757" s="24" t="s">
         <v>296</v>
       </c>
@@ -32284,18 +32296,18 @@
         <v>1223</v>
       </c>
     </row>
-    <row r="758" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="758" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A758" s="24" t="s">
         <v>374</v>
       </c>
       <c r="H758" s="24"/>
     </row>
-    <row r="759" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="759" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A759" s="24" t="s">
         <v>268</v>
       </c>
       <c r="B759" s="24" t="s">
-        <v>443</v>
+        <v>4225</v>
       </c>
       <c r="H759" s="24" t="s">
         <v>394</v>
@@ -32307,7 +32319,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="760" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="760" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A760" s="38" t="s">
         <v>296</v>
       </c>
@@ -32334,7 +32346,7 @@
         <v>1225</v>
       </c>
     </row>
-    <row r="761" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="761" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A761" s="38" t="s">
         <v>296</v>
       </c>
@@ -32361,7 +32373,7 @@
         <v>1227</v>
       </c>
     </row>
-    <row r="762" spans="1:18" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="762" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A762" s="24" t="s">
         <v>296</v>
       </c>

--- a/s2.xlsx
+++ b/s2.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17509" uniqueCount="4226">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17509" uniqueCount="4230">
   <si>
     <t>list_name</t>
   </si>
@@ -12702,6 +12702,18 @@
   </si>
   <si>
     <t>table27h_note6</t>
+  </si>
+  <si>
+    <t>table27i_note6</t>
+  </si>
+  <si>
+    <t>table27j_note6</t>
+  </si>
+  <si>
+    <t>table27k_note6</t>
+  </si>
+  <si>
+    <t>table27l_note6</t>
   </si>
 </sst>
 </file>
@@ -29126,7 +29138,7 @@
       <c r="Q597" s="33"/>
       <c r="R597" s="33"/>
     </row>
-    <row r="598" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="598" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A598" s="35" t="s">
         <v>382</v>
       </c>
@@ -29143,7 +29155,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="599" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="599" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A599" s="28" t="s">
         <v>268</v>
       </c>
@@ -29160,7 +29172,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="600" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="600" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A600" s="28" t="s">
         <v>268</v>
       </c>
@@ -29180,7 +29192,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="601" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="601" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A601" s="28" t="s">
         <v>268</v>
       </c>
@@ -29200,7 +29212,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="602" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="602" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A602" s="28" t="s">
         <v>268</v>
       </c>
@@ -29220,7 +29232,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="603" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="603" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A603" s="24" t="s">
         <v>273</v>
       </c>
@@ -29232,7 +29244,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="604" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="604" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A604" s="24" t="s">
         <v>268</v>
       </c>
@@ -29249,7 +29261,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="605" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="605" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A605" s="24" t="s">
         <v>296</v>
       </c>
@@ -29275,7 +29287,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="606" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="606" spans="1:18" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A606" s="24" t="s">
         <v>296</v>
       </c>
@@ -29301,7 +29313,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="607" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="607" spans="1:18" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A607" s="24" t="s">
         <v>296</v>
       </c>
@@ -29328,13 +29340,13 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="608" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="608" spans="1:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A608" s="24" t="s">
         <v>374</v>
       </c>
       <c r="H608" s="24"/>
     </row>
-    <row r="609" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="609" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A609" s="24" t="s">
         <v>273</v>
       </c>
@@ -29346,7 +29358,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="610" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="610" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A610" s="24" t="s">
         <v>268</v>
       </c>
@@ -29363,7 +29375,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="611" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="611" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A611" s="24" t="s">
         <v>296</v>
       </c>
@@ -29389,7 +29401,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="612" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="612" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A612" s="24" t="s">
         <v>296</v>
       </c>
@@ -29415,7 +29427,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="613" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="613" spans="1:15" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A613" s="24" t="s">
         <v>296</v>
       </c>
@@ -29442,13 +29454,13 @@
         <v>1074</v>
       </c>
     </row>
-    <row r="614" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="614" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A614" s="24" t="s">
         <v>374</v>
       </c>
       <c r="H614" s="24"/>
     </row>
-    <row r="615" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="615" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A615" s="24" t="s">
         <v>273</v>
       </c>
@@ -29460,7 +29472,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="616" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="616" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A616" s="24" t="s">
         <v>268</v>
       </c>
@@ -29477,7 +29489,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="617" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="617" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A617" s="24" t="s">
         <v>296</v>
       </c>
@@ -29503,7 +29515,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="618" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="618" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A618" s="24" t="s">
         <v>296</v>
       </c>
@@ -29529,7 +29541,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="619" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="619" spans="1:15" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A619" s="24" t="s">
         <v>296</v>
       </c>
@@ -29556,13 +29568,13 @@
         <v>1080</v>
       </c>
     </row>
-    <row r="620" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="620" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A620" s="24" t="s">
         <v>374</v>
       </c>
       <c r="H620" s="24"/>
     </row>
-    <row r="621" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="621" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A621" s="24" t="s">
         <v>273</v>
       </c>
@@ -29574,7 +29586,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="622" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="622" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A622" s="24" t="s">
         <v>268</v>
       </c>
@@ -29591,7 +29603,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="623" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="623" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A623" s="24" t="s">
         <v>296</v>
       </c>
@@ -29617,7 +29629,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="624" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="624" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A624" s="24" t="s">
         <v>296</v>
       </c>
@@ -29643,7 +29655,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="625" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="625" spans="1:18" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A625" s="24" t="s">
         <v>296</v>
       </c>
@@ -29670,13 +29682,13 @@
         <v>1086</v>
       </c>
     </row>
-    <row r="626" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="626" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A626" s="24" t="s">
         <v>374</v>
       </c>
       <c r="H626" s="24"/>
     </row>
-    <row r="627" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="627" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A627" s="24" t="s">
         <v>273</v>
       </c>
@@ -29688,7 +29700,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="628" spans="1:18" s="33" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="628" spans="1:18" s="33" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A628" s="24" t="s">
         <v>268</v>
       </c>
@@ -29718,7 +29730,7 @@
       <c r="Q628" s="24"/>
       <c r="R628" s="24"/>
     </row>
-    <row r="629" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="629" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A629" s="24" t="s">
         <v>296</v>
       </c>
@@ -29744,7 +29756,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="630" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="630" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A630" s="24" t="s">
         <v>296</v>
       </c>
@@ -29770,7 +29782,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="631" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="631" spans="1:18" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A631" s="24" t="s">
         <v>296</v>
       </c>
@@ -29797,13 +29809,13 @@
         <v>1094</v>
       </c>
     </row>
-    <row r="632" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="632" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A632" s="24" t="s">
         <v>374</v>
       </c>
       <c r="H632" s="24"/>
     </row>
-    <row r="633" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="633" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A633" s="24" t="s">
         <v>268</v>
       </c>
@@ -29820,7 +29832,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="634" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="634" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A634" s="38" t="s">
         <v>296</v>
       </c>
@@ -29847,7 +29859,7 @@
         <v>1096</v>
       </c>
     </row>
-    <row r="635" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="635" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A635" s="38" t="s">
         <v>296</v>
       </c>
@@ -29874,7 +29886,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="636" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="636" spans="1:18" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A636" s="24" t="s">
         <v>296</v>
       </c>
@@ -29959,7 +29971,7 @@
       <c r="Q639" s="33"/>
       <c r="R639" s="33"/>
     </row>
-    <row r="640" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="640" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A640" s="35" t="s">
         <v>382</v>
       </c>
@@ -29976,7 +29988,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="641" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="641" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A641" s="28" t="s">
         <v>268</v>
       </c>
@@ -29993,7 +30005,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="642" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="642" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A642" s="28" t="s">
         <v>268</v>
       </c>
@@ -30013,7 +30025,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="643" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="643" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A643" s="28" t="s">
         <v>268</v>
       </c>
@@ -30033,7 +30045,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="644" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="644" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A644" s="28" t="s">
         <v>268</v>
       </c>
@@ -30053,7 +30065,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="645" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="645" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A645" s="24" t="s">
         <v>273</v>
       </c>
@@ -30065,7 +30077,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="646" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="646" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A646" s="24" t="s">
         <v>268</v>
       </c>
@@ -30082,7 +30094,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="647" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="647" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A647" s="24" t="s">
         <v>296</v>
       </c>
@@ -30108,7 +30120,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="648" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="648" spans="1:15" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A648" s="24" t="s">
         <v>296</v>
       </c>
@@ -30134,7 +30146,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="649" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="649" spans="1:15" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A649" s="24" t="s">
         <v>296</v>
       </c>
@@ -30161,13 +30173,13 @@
         <v>1113</v>
       </c>
     </row>
-    <row r="650" spans="1:15" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="650" spans="1:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A650" s="24" t="s">
         <v>374</v>
       </c>
       <c r="H650" s="24"/>
     </row>
-    <row r="651" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="651" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A651" s="24" t="s">
         <v>273</v>
       </c>
@@ -30179,7 +30191,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="652" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="652" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A652" s="24" t="s">
         <v>268</v>
       </c>
@@ -30196,7 +30208,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="653" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="653" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A653" s="24" t="s">
         <v>296</v>
       </c>
@@ -30222,7 +30234,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="654" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="654" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A654" s="24" t="s">
         <v>296</v>
       </c>
@@ -30248,7 +30260,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="655" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="655" spans="1:15" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A655" s="24" t="s">
         <v>296</v>
       </c>
@@ -30275,13 +30287,13 @@
         <v>1119</v>
       </c>
     </row>
-    <row r="656" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="656" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A656" s="24" t="s">
         <v>374</v>
       </c>
       <c r="H656" s="24"/>
     </row>
-    <row r="657" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="657" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A657" s="24" t="s">
         <v>273</v>
       </c>
@@ -30293,7 +30305,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="658" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="658" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A658" s="24" t="s">
         <v>268</v>
       </c>
@@ -30310,7 +30322,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="659" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="659" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A659" s="24" t="s">
         <v>296</v>
       </c>
@@ -30336,7 +30348,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="660" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="660" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A660" s="24" t="s">
         <v>296</v>
       </c>
@@ -30362,7 +30374,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="661" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="661" spans="1:18" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A661" s="24" t="s">
         <v>296</v>
       </c>
@@ -30389,13 +30401,13 @@
         <v>1125</v>
       </c>
     </row>
-    <row r="662" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="662" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A662" s="24" t="s">
         <v>374</v>
       </c>
       <c r="H662" s="24"/>
     </row>
-    <row r="663" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="663" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A663" s="24" t="s">
         <v>273</v>
       </c>
@@ -30407,7 +30419,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="664" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="664" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A664" s="24" t="s">
         <v>268</v>
       </c>
@@ -30424,7 +30436,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="665" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="665" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A665" s="24" t="s">
         <v>296</v>
       </c>
@@ -30450,7 +30462,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="666" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="666" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A666" s="24" t="s">
         <v>296</v>
       </c>
@@ -30476,7 +30488,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="667" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="667" spans="1:18" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A667" s="24" t="s">
         <v>296</v>
       </c>
@@ -30503,13 +30515,13 @@
         <v>1131</v>
       </c>
     </row>
-    <row r="668" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="668" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A668" s="24" t="s">
         <v>374</v>
       </c>
       <c r="H668" s="24"/>
     </row>
-    <row r="669" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="669" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A669" s="24" t="s">
         <v>273</v>
       </c>
@@ -30521,7 +30533,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="670" spans="1:18" s="33" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="670" spans="1:18" s="33" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A670" s="24" t="s">
         <v>268</v>
       </c>
@@ -30551,7 +30563,7 @@
       <c r="Q670" s="24"/>
       <c r="R670" s="24"/>
     </row>
-    <row r="671" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="671" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A671" s="24" t="s">
         <v>296</v>
       </c>
@@ -30577,7 +30589,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="672" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="672" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A672" s="24" t="s">
         <v>296</v>
       </c>
@@ -30603,7 +30615,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="673" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="673" spans="1:18" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A673" s="24" t="s">
         <v>296</v>
       </c>
@@ -30630,13 +30642,13 @@
         <v>1137</v>
       </c>
     </row>
-    <row r="674" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="674" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A674" s="24" t="s">
         <v>374</v>
       </c>
       <c r="H674" s="24"/>
     </row>
-    <row r="675" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="675" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A675" s="24" t="s">
         <v>268</v>
       </c>
@@ -30653,7 +30665,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="676" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="676" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A676" s="38" t="s">
         <v>296</v>
       </c>
@@ -30680,7 +30692,7 @@
         <v>1139</v>
       </c>
     </row>
-    <row r="677" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="677" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A677" s="38" t="s">
         <v>296</v>
       </c>
@@ -30707,7 +30719,7 @@
         <v>1141</v>
       </c>
     </row>
-    <row r="678" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="678" spans="1:18" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A678" s="24" t="s">
         <v>296</v>
       </c>
@@ -30792,7 +30804,7 @@
       <c r="Q681" s="33"/>
       <c r="R681" s="33"/>
     </row>
-    <row r="682" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="682" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A682" s="35" t="s">
         <v>382</v>
       </c>
@@ -30809,7 +30821,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="683" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="683" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A683" s="28" t="s">
         <v>268</v>
       </c>
@@ -30826,7 +30838,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="684" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="684" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A684" s="28" t="s">
         <v>268</v>
       </c>
@@ -30846,7 +30858,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="685" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="685" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A685" s="28" t="s">
         <v>268</v>
       </c>
@@ -30866,7 +30878,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="686" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="686" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A686" s="28" t="s">
         <v>268</v>
       </c>
@@ -30886,7 +30898,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="687" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="687" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A687" s="24" t="s">
         <v>273</v>
       </c>
@@ -30898,7 +30910,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="688" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="688" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A688" s="24" t="s">
         <v>268</v>
       </c>
@@ -30915,7 +30927,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="689" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="689" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A689" s="24" t="s">
         <v>296</v>
       </c>
@@ -30941,7 +30953,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="690" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="690" spans="1:15" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A690" s="24" t="s">
         <v>296</v>
       </c>
@@ -30967,7 +30979,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="691" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="691" spans="1:15" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A691" s="24" t="s">
         <v>296</v>
       </c>
@@ -30994,13 +31006,13 @@
         <v>1156</v>
       </c>
     </row>
-    <row r="692" spans="1:15" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="692" spans="1:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A692" s="24" t="s">
         <v>374</v>
       </c>
       <c r="H692" s="24"/>
     </row>
-    <row r="693" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="693" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A693" s="24" t="s">
         <v>273</v>
       </c>
@@ -31012,7 +31024,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="694" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="694" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A694" s="24" t="s">
         <v>268</v>
       </c>
@@ -31029,7 +31041,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="695" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="695" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A695" s="24" t="s">
         <v>296</v>
       </c>
@@ -31055,7 +31067,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="696" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="696" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A696" s="24" t="s">
         <v>296</v>
       </c>
@@ -31081,7 +31093,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="697" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="697" spans="1:15" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A697" s="24" t="s">
         <v>296</v>
       </c>
@@ -31108,13 +31120,13 @@
         <v>1162</v>
       </c>
     </row>
-    <row r="698" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="698" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A698" s="24" t="s">
         <v>374</v>
       </c>
       <c r="H698" s="24"/>
     </row>
-    <row r="699" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="699" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A699" s="24" t="s">
         <v>273</v>
       </c>
@@ -31126,7 +31138,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="700" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="700" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A700" s="24" t="s">
         <v>268</v>
       </c>
@@ -31143,7 +31155,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="701" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="701" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A701" s="24" t="s">
         <v>296</v>
       </c>
@@ -31169,7 +31181,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="702" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="702" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A702" s="24" t="s">
         <v>296</v>
       </c>
@@ -31195,7 +31207,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="703" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="703" spans="1:15" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A703" s="24" t="s">
         <v>296</v>
       </c>
@@ -31222,13 +31234,13 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="704" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="704" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A704" s="24" t="s">
         <v>374</v>
       </c>
       <c r="H704" s="24"/>
     </row>
-    <row r="705" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="705" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A705" s="24" t="s">
         <v>273</v>
       </c>
@@ -31240,7 +31252,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="706" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="706" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A706" s="24" t="s">
         <v>268</v>
       </c>
@@ -31257,7 +31269,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="707" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="707" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A707" s="24" t="s">
         <v>296</v>
       </c>
@@ -31283,7 +31295,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="708" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="708" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A708" s="24" t="s">
         <v>296</v>
       </c>
@@ -31309,7 +31321,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="709" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="709" spans="1:18" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A709" s="24" t="s">
         <v>296</v>
       </c>
@@ -31336,13 +31348,13 @@
         <v>1174</v>
       </c>
     </row>
-    <row r="710" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="710" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A710" s="24" t="s">
         <v>374</v>
       </c>
       <c r="H710" s="24"/>
     </row>
-    <row r="711" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="711" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A711" s="24" t="s">
         <v>273</v>
       </c>
@@ -31354,7 +31366,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="712" spans="1:18" s="33" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="712" spans="1:18" s="33" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A712" s="24" t="s">
         <v>268</v>
       </c>
@@ -31384,7 +31396,7 @@
       <c r="Q712" s="24"/>
       <c r="R712" s="24"/>
     </row>
-    <row r="713" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="713" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A713" s="24" t="s">
         <v>296</v>
       </c>
@@ -31410,7 +31422,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="714" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="714" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A714" s="24" t="s">
         <v>296</v>
       </c>
@@ -31436,7 +31448,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="715" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="715" spans="1:18" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A715" s="24" t="s">
         <v>296</v>
       </c>
@@ -31463,13 +31475,13 @@
         <v>1180</v>
       </c>
     </row>
-    <row r="716" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="716" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A716" s="24" t="s">
         <v>374</v>
       </c>
       <c r="H716" s="24"/>
     </row>
-    <row r="717" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="717" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A717" s="24" t="s">
         <v>268</v>
       </c>
@@ -31486,7 +31498,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="718" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="718" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A718" s="38" t="s">
         <v>296</v>
       </c>
@@ -31513,7 +31525,7 @@
         <v>1182</v>
       </c>
     </row>
-    <row r="719" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="719" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A719" s="38" t="s">
         <v>296</v>
       </c>
@@ -31540,7 +31552,7 @@
         <v>1184</v>
       </c>
     </row>
-    <row r="720" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="720" spans="1:18" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A720" s="24" t="s">
         <v>296</v>
       </c>
@@ -31625,7 +31637,7 @@
       <c r="Q723" s="33"/>
       <c r="R723" s="33"/>
     </row>
-    <row r="724" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="724" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A724" s="35" t="s">
         <v>382</v>
       </c>
@@ -31642,7 +31654,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="725" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="725" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A725" s="28" t="s">
         <v>268</v>
       </c>
@@ -31659,7 +31671,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="726" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="726" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A726" s="28" t="s">
         <v>268</v>
       </c>
@@ -31679,7 +31691,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="727" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="727" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A727" s="28" t="s">
         <v>268</v>
       </c>
@@ -31699,7 +31711,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="728" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="728" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A728" s="28" t="s">
         <v>268</v>
       </c>
@@ -31719,7 +31731,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="729" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="729" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A729" s="24" t="s">
         <v>273</v>
       </c>
@@ -31731,7 +31743,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="730" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="730" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A730" s="24" t="s">
         <v>268</v>
       </c>
@@ -31748,7 +31760,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="731" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="731" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A731" s="24" t="s">
         <v>296</v>
       </c>
@@ -31774,7 +31786,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="732" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="732" spans="1:18" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A732" s="24" t="s">
         <v>296</v>
       </c>
@@ -31800,7 +31812,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="733" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="733" spans="1:18" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A733" s="24" t="s">
         <v>296</v>
       </c>
@@ -31827,13 +31839,13 @@
         <v>1199</v>
       </c>
     </row>
-    <row r="734" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="734" spans="1:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A734" s="24" t="s">
         <v>374</v>
       </c>
       <c r="H734" s="24"/>
     </row>
-    <row r="735" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="735" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A735" s="24" t="s">
         <v>273</v>
       </c>
@@ -31845,7 +31857,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="736" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="736" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A736" s="24" t="s">
         <v>268</v>
       </c>
@@ -31862,7 +31874,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="737" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="737" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A737" s="24" t="s">
         <v>296</v>
       </c>
@@ -31888,7 +31900,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="738" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="738" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A738" s="24" t="s">
         <v>296</v>
       </c>
@@ -31914,7 +31926,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="739" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="739" spans="1:15" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A739" s="24" t="s">
         <v>296</v>
       </c>
@@ -31941,13 +31953,13 @@
         <v>1205</v>
       </c>
     </row>
-    <row r="740" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="740" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A740" s="24" t="s">
         <v>374</v>
       </c>
       <c r="H740" s="24"/>
     </row>
-    <row r="741" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="741" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A741" s="24" t="s">
         <v>273</v>
       </c>
@@ -31959,7 +31971,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="742" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="742" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A742" s="24" t="s">
         <v>268</v>
       </c>
@@ -31976,7 +31988,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="743" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="743" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A743" s="24" t="s">
         <v>296</v>
       </c>
@@ -32002,7 +32014,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="744" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="744" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A744" s="24" t="s">
         <v>296</v>
       </c>
@@ -32028,7 +32040,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="745" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="745" spans="1:15" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A745" s="24" t="s">
         <v>296</v>
       </c>
@@ -32055,13 +32067,13 @@
         <v>1211</v>
       </c>
     </row>
-    <row r="746" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="746" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A746" s="24" t="s">
         <v>374</v>
       </c>
       <c r="H746" s="24"/>
     </row>
-    <row r="747" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="747" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A747" s="24" t="s">
         <v>273</v>
       </c>
@@ -32073,7 +32085,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="748" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="748" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A748" s="24" t="s">
         <v>268</v>
       </c>
@@ -32090,7 +32102,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="749" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="749" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A749" s="24" t="s">
         <v>296</v>
       </c>
@@ -32116,7 +32128,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="750" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="750" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A750" s="24" t="s">
         <v>296</v>
       </c>
@@ -32142,7 +32154,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="751" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="751" spans="1:15" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A751" s="24" t="s">
         <v>296</v>
       </c>
@@ -32169,13 +32181,13 @@
         <v>1217</v>
       </c>
     </row>
-    <row r="752" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="752" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A752" s="24" t="s">
         <v>374</v>
       </c>
       <c r="H752" s="24"/>
     </row>
-    <row r="753" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="753" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A753" s="24" t="s">
         <v>273</v>
       </c>
@@ -32187,7 +32199,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="754" spans="1:18" s="33" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="754" spans="1:18" s="33" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A754" s="24" t="s">
         <v>268</v>
       </c>
@@ -32217,7 +32229,7 @@
       <c r="Q754" s="24"/>
       <c r="R754" s="24"/>
     </row>
-    <row r="755" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="755" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A755" s="24" t="s">
         <v>296</v>
       </c>
@@ -32243,7 +32255,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="756" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="756" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A756" s="24" t="s">
         <v>296</v>
       </c>
@@ -32269,7 +32281,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="757" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="757" spans="1:18" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A757" s="24" t="s">
         <v>296</v>
       </c>
@@ -32296,13 +32308,13 @@
         <v>1223</v>
       </c>
     </row>
-    <row r="758" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="758" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A758" s="24" t="s">
         <v>374</v>
       </c>
       <c r="H758" s="24"/>
     </row>
-    <row r="759" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="759" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A759" s="24" t="s">
         <v>268</v>
       </c>
@@ -32319,7 +32331,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="760" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="760" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A760" s="38" t="s">
         <v>296</v>
       </c>
@@ -32346,7 +32358,7 @@
         <v>1225</v>
       </c>
     </row>
-    <row r="761" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="761" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A761" s="38" t="s">
         <v>296</v>
       </c>
@@ -32373,7 +32385,7 @@
         <v>1227</v>
       </c>
     </row>
-    <row r="762" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="762" spans="1:18" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A762" s="24" t="s">
         <v>296</v>
       </c>
@@ -32458,7 +32470,7 @@
       <c r="Q765" s="33"/>
       <c r="R765" s="33"/>
     </row>
-    <row r="766" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="766" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A766" s="35" t="s">
         <v>382</v>
       </c>
@@ -32475,7 +32487,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="767" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="767" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A767" s="28" t="s">
         <v>268</v>
       </c>
@@ -32492,7 +32504,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="768" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="768" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A768" s="28" t="s">
         <v>268</v>
       </c>
@@ -32512,7 +32524,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="769" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="769" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A769" s="28" t="s">
         <v>268</v>
       </c>
@@ -32532,7 +32544,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="770" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="770" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A770" s="28" t="s">
         <v>268</v>
       </c>
@@ -32552,7 +32564,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="771" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="771" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A771" s="24" t="s">
         <v>273</v>
       </c>
@@ -32564,7 +32576,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="772" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="772" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A772" s="24" t="s">
         <v>268</v>
       </c>
@@ -32581,7 +32593,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="773" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="773" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A773" s="24" t="s">
         <v>296</v>
       </c>
@@ -32607,7 +32619,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="774" spans="1:15" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="774" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A774" s="24" t="s">
         <v>296</v>
       </c>
@@ -32633,7 +32645,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="775" spans="1:15" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="775" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A775" s="24" t="s">
         <v>296</v>
       </c>
@@ -32660,13 +32672,13 @@
         <v>1242</v>
       </c>
     </row>
-    <row r="776" spans="1:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="776" spans="1:15" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A776" s="24" t="s">
         <v>374</v>
       </c>
       <c r="H776" s="24"/>
     </row>
-    <row r="777" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="777" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A777" s="24" t="s">
         <v>273</v>
       </c>
@@ -32678,7 +32690,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="778" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="778" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A778" s="24" t="s">
         <v>268</v>
       </c>
@@ -32695,7 +32707,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="779" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="779" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A779" s="24" t="s">
         <v>296</v>
       </c>
@@ -32721,7 +32733,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="780" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="780" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A780" s="24" t="s">
         <v>296</v>
       </c>
@@ -32747,7 +32759,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="781" spans="1:15" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="781" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A781" s="24" t="s">
         <v>296</v>
       </c>
@@ -32774,13 +32786,13 @@
         <v>1248</v>
       </c>
     </row>
-    <row r="782" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="782" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A782" s="24" t="s">
         <v>374</v>
       </c>
       <c r="H782" s="24"/>
     </row>
-    <row r="783" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="783" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A783" s="24" t="s">
         <v>273</v>
       </c>
@@ -32792,7 +32804,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="784" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="784" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A784" s="24" t="s">
         <v>268</v>
       </c>
@@ -32809,7 +32821,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="785" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="785" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A785" s="24" t="s">
         <v>296</v>
       </c>
@@ -32835,7 +32847,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="786" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="786" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A786" s="24" t="s">
         <v>296</v>
       </c>
@@ -32861,7 +32873,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="787" spans="1:18" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="787" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A787" s="24" t="s">
         <v>296</v>
       </c>
@@ -32888,13 +32900,13 @@
         <v>1254</v>
       </c>
     </row>
-    <row r="788" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="788" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A788" s="24" t="s">
         <v>374</v>
       </c>
       <c r="H788" s="24"/>
     </row>
-    <row r="789" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="789" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A789" s="24" t="s">
         <v>273</v>
       </c>
@@ -32906,7 +32918,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="790" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="790" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A790" s="24" t="s">
         <v>268</v>
       </c>
@@ -32923,7 +32935,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="791" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="791" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A791" s="24" t="s">
         <v>296</v>
       </c>
@@ -32949,7 +32961,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="792" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="792" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A792" s="24" t="s">
         <v>296</v>
       </c>
@@ -32975,7 +32987,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="793" spans="1:18" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="793" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A793" s="24" t="s">
         <v>296</v>
       </c>
@@ -33002,13 +33014,13 @@
         <v>1260</v>
       </c>
     </row>
-    <row r="794" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="794" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A794" s="24" t="s">
         <v>374</v>
       </c>
       <c r="H794" s="24"/>
     </row>
-    <row r="795" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="795" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A795" s="24" t="s">
         <v>273</v>
       </c>
@@ -33020,7 +33032,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="796" spans="1:18" s="33" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="796" spans="1:18" s="33" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A796" s="24" t="s">
         <v>268</v>
       </c>
@@ -33050,7 +33062,7 @@
       <c r="Q796" s="24"/>
       <c r="R796" s="24"/>
     </row>
-    <row r="797" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="797" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A797" s="24" t="s">
         <v>296</v>
       </c>
@@ -33076,7 +33088,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="798" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="798" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A798" s="24" t="s">
         <v>296</v>
       </c>
@@ -33102,7 +33114,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="799" spans="1:18" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="799" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A799" s="24" t="s">
         <v>296</v>
       </c>
@@ -33129,18 +33141,18 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="800" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="800" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A800" s="24" t="s">
         <v>374</v>
       </c>
       <c r="H800" s="24"/>
     </row>
-    <row r="801" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="801" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A801" s="24" t="s">
         <v>268</v>
       </c>
       <c r="B801" s="24" t="s">
-        <v>443</v>
+        <v>4226</v>
       </c>
       <c r="H801" s="24" t="s">
         <v>394</v>
@@ -33152,7 +33164,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="802" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="802" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A802" s="38" t="s">
         <v>296</v>
       </c>
@@ -33179,7 +33191,7 @@
         <v>1270</v>
       </c>
     </row>
-    <row r="803" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="803" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A803" s="38" t="s">
         <v>296</v>
       </c>
@@ -33206,7 +33218,7 @@
         <v>1272</v>
       </c>
     </row>
-    <row r="804" spans="1:18" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="804" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A804" s="24" t="s">
         <v>296</v>
       </c>
@@ -33291,7 +33303,7 @@
       <c r="Q807" s="33"/>
       <c r="R807" s="33"/>
     </row>
-    <row r="808" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="808" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A808" s="35" t="s">
         <v>382</v>
       </c>
@@ -33308,7 +33320,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="809" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="809" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A809" s="28" t="s">
         <v>268</v>
       </c>
@@ -33325,7 +33337,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="810" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="810" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A810" s="28" t="s">
         <v>268</v>
       </c>
@@ -33345,7 +33357,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="811" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="811" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A811" s="28" t="s">
         <v>268</v>
       </c>
@@ -33365,7 +33377,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="812" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="812" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A812" s="28" t="s">
         <v>268</v>
       </c>
@@ -33385,7 +33397,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="813" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="813" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A813" s="24" t="s">
         <v>273</v>
       </c>
@@ -33397,7 +33409,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="814" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="814" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A814" s="24" t="s">
         <v>268</v>
       </c>
@@ -33414,7 +33426,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="815" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="815" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A815" s="24" t="s">
         <v>296</v>
       </c>
@@ -33440,7 +33452,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="816" spans="1:18" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="816" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A816" s="24" t="s">
         <v>296</v>
       </c>
@@ -33466,7 +33478,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="817" spans="1:15" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="817" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A817" s="24" t="s">
         <v>296</v>
       </c>
@@ -33493,13 +33505,13 @@
         <v>1287</v>
       </c>
     </row>
-    <row r="818" spans="1:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="818" spans="1:15" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A818" s="24" t="s">
         <v>374</v>
       </c>
       <c r="H818" s="24"/>
     </row>
-    <row r="819" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="819" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A819" s="24" t="s">
         <v>273</v>
       </c>
@@ -33511,7 +33523,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="820" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="820" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A820" s="24" t="s">
         <v>268</v>
       </c>
@@ -33528,7 +33540,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="821" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="821" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A821" s="24" t="s">
         <v>296</v>
       </c>
@@ -33554,7 +33566,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="822" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="822" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A822" s="24" t="s">
         <v>296</v>
       </c>
@@ -33580,7 +33592,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="823" spans="1:15" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="823" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A823" s="24" t="s">
         <v>296</v>
       </c>
@@ -33607,13 +33619,13 @@
         <v>1293</v>
       </c>
     </row>
-    <row r="824" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="824" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A824" s="24" t="s">
         <v>374</v>
       </c>
       <c r="H824" s="24"/>
     </row>
-    <row r="825" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="825" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A825" s="24" t="s">
         <v>273</v>
       </c>
@@ -33625,7 +33637,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="826" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="826" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A826" s="24" t="s">
         <v>268</v>
       </c>
@@ -33642,7 +33654,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="827" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="827" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A827" s="24" t="s">
         <v>296</v>
       </c>
@@ -33668,7 +33680,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="828" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="828" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A828" s="24" t="s">
         <v>296</v>
       </c>
@@ -33694,7 +33706,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="829" spans="1:15" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="829" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A829" s="24" t="s">
         <v>296</v>
       </c>
@@ -33721,13 +33733,13 @@
         <v>1299</v>
       </c>
     </row>
-    <row r="830" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="830" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A830" s="24" t="s">
         <v>374</v>
       </c>
       <c r="H830" s="24"/>
     </row>
-    <row r="831" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="831" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A831" s="24" t="s">
         <v>273</v>
       </c>
@@ -33739,7 +33751,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="832" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="832" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A832" s="24" t="s">
         <v>268</v>
       </c>
@@ -33756,7 +33768,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="833" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="833" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A833" s="24" t="s">
         <v>296</v>
       </c>
@@ -33782,7 +33794,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="834" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="834" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A834" s="24" t="s">
         <v>296</v>
       </c>
@@ -33808,7 +33820,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="835" spans="1:18" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="835" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A835" s="24" t="s">
         <v>296</v>
       </c>
@@ -33835,13 +33847,13 @@
         <v>1305</v>
       </c>
     </row>
-    <row r="836" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="836" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A836" s="24" t="s">
         <v>374</v>
       </c>
       <c r="H836" s="24"/>
     </row>
-    <row r="837" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="837" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A837" s="24" t="s">
         <v>273</v>
       </c>
@@ -33853,7 +33865,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="838" spans="1:18" s="33" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="838" spans="1:18" s="33" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A838" s="24" t="s">
         <v>268</v>
       </c>
@@ -33883,7 +33895,7 @@
       <c r="Q838" s="24"/>
       <c r="R838" s="24"/>
     </row>
-    <row r="839" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="839" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A839" s="24" t="s">
         <v>296</v>
       </c>
@@ -33909,7 +33921,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="840" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="840" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A840" s="24" t="s">
         <v>296</v>
       </c>
@@ -33935,7 +33947,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="841" spans="1:18" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="841" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A841" s="24" t="s">
         <v>296</v>
       </c>
@@ -33962,18 +33974,18 @@
         <v>1311</v>
       </c>
     </row>
-    <row r="842" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="842" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A842" s="24" t="s">
         <v>374</v>
       </c>
       <c r="H842" s="24"/>
     </row>
-    <row r="843" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="843" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A843" s="24" t="s">
         <v>268</v>
       </c>
       <c r="B843" s="24" t="s">
-        <v>443</v>
+        <v>4227</v>
       </c>
       <c r="H843" s="24" t="s">
         <v>394</v>
@@ -33985,7 +33997,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="844" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="844" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A844" s="38" t="s">
         <v>296</v>
       </c>
@@ -34012,7 +34024,7 @@
         <v>1313</v>
       </c>
     </row>
-    <row r="845" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="845" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A845" s="38" t="s">
         <v>296</v>
       </c>
@@ -34039,7 +34051,7 @@
         <v>1315</v>
       </c>
     </row>
-    <row r="846" spans="1:18" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="846" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A846" s="24" t="s">
         <v>296</v>
       </c>
@@ -34124,7 +34136,7 @@
       <c r="Q849" s="33"/>
       <c r="R849" s="33"/>
     </row>
-    <row r="850" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="850" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A850" s="35" t="s">
         <v>382</v>
       </c>
@@ -34141,7 +34153,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="851" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="851" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A851" s="28" t="s">
         <v>268</v>
       </c>
@@ -34158,7 +34170,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="852" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="852" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A852" s="28" t="s">
         <v>268</v>
       </c>
@@ -34178,7 +34190,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="853" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="853" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A853" s="28" t="s">
         <v>268</v>
       </c>
@@ -34198,7 +34210,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="854" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="854" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A854" s="28" t="s">
         <v>268</v>
       </c>
@@ -34218,7 +34230,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="855" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="855" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A855" s="24" t="s">
         <v>273</v>
       </c>
@@ -34230,7 +34242,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="856" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="856" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A856" s="24" t="s">
         <v>268</v>
       </c>
@@ -34247,7 +34259,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="857" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="857" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A857" s="24" t="s">
         <v>296</v>
       </c>
@@ -34273,7 +34285,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="858" spans="1:18" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="858" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A858" s="24" t="s">
         <v>296</v>
       </c>
@@ -34299,7 +34311,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="859" spans="1:18" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="859" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A859" s="24" t="s">
         <v>296</v>
       </c>
@@ -34326,13 +34338,13 @@
         <v>1330</v>
       </c>
     </row>
-    <row r="860" spans="1:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="860" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A860" s="24" t="s">
         <v>374</v>
       </c>
       <c r="H860" s="24"/>
     </row>
-    <row r="861" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="861" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A861" s="24" t="s">
         <v>273</v>
       </c>
@@ -34344,7 +34356,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="862" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="862" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A862" s="24" t="s">
         <v>268</v>
       </c>
@@ -34361,7 +34373,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="863" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="863" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A863" s="24" t="s">
         <v>296</v>
       </c>
@@ -34387,7 +34399,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="864" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="864" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A864" s="24" t="s">
         <v>296</v>
       </c>
@@ -34413,7 +34425,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="865" spans="1:18" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="865" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A865" s="24" t="s">
         <v>296</v>
       </c>
@@ -34440,13 +34452,13 @@
         <v>1336</v>
       </c>
     </row>
-    <row r="866" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="866" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A866" s="24" t="s">
         <v>374</v>
       </c>
       <c r="H866" s="24"/>
     </row>
-    <row r="867" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="867" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A867" s="24" t="s">
         <v>273</v>
       </c>
@@ -34458,7 +34470,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="868" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="868" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A868" s="24" t="s">
         <v>268</v>
       </c>
@@ -34475,7 +34487,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="869" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="869" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A869" s="24" t="s">
         <v>296</v>
       </c>
@@ -34501,7 +34513,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="870" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="870" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A870" s="24" t="s">
         <v>296</v>
       </c>
@@ -34527,7 +34539,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="871" spans="1:18" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="871" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A871" s="24" t="s">
         <v>296</v>
       </c>
@@ -34554,13 +34566,13 @@
         <v>1342</v>
       </c>
     </row>
-    <row r="872" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="872" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A872" s="24" t="s">
         <v>374</v>
       </c>
       <c r="H872" s="24"/>
     </row>
-    <row r="873" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="873" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A873" s="24" t="s">
         <v>273</v>
       </c>
@@ -34572,7 +34584,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="874" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="874" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A874" s="24" t="s">
         <v>268</v>
       </c>
@@ -34589,7 +34601,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="875" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="875" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A875" s="24" t="s">
         <v>296</v>
       </c>
@@ -34615,7 +34627,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="876" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="876" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A876" s="24" t="s">
         <v>296</v>
       </c>
@@ -34641,7 +34653,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="877" spans="1:18" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="877" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A877" s="24" t="s">
         <v>296</v>
       </c>
@@ -34668,13 +34680,13 @@
         <v>1348</v>
       </c>
     </row>
-    <row r="878" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="878" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A878" s="24" t="s">
         <v>374</v>
       </c>
       <c r="H878" s="24"/>
     </row>
-    <row r="879" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="879" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A879" s="24" t="s">
         <v>273</v>
       </c>
@@ -34686,7 +34698,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="880" spans="1:18" s="33" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="880" spans="1:18" s="33" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A880" s="24" t="s">
         <v>268</v>
       </c>
@@ -34716,7 +34728,7 @@
       <c r="Q880" s="24"/>
       <c r="R880" s="24"/>
     </row>
-    <row r="881" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="881" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A881" s="24" t="s">
         <v>296</v>
       </c>
@@ -34742,7 +34754,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="882" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="882" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A882" s="24" t="s">
         <v>296</v>
       </c>
@@ -34768,7 +34780,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="883" spans="1:18" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="883" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A883" s="24" t="s">
         <v>296</v>
       </c>
@@ -34795,18 +34807,18 @@
         <v>1354</v>
       </c>
     </row>
-    <row r="884" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="884" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A884" s="24" t="s">
         <v>374</v>
       </c>
       <c r="H884" s="24"/>
     </row>
-    <row r="885" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="885" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A885" s="24" t="s">
         <v>268</v>
       </c>
       <c r="B885" s="24" t="s">
-        <v>443</v>
+        <v>4228</v>
       </c>
       <c r="H885" s="24" t="s">
         <v>394</v>
@@ -34818,7 +34830,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="886" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="886" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A886" s="38" t="s">
         <v>296</v>
       </c>
@@ -34845,7 +34857,7 @@
         <v>1356</v>
       </c>
     </row>
-    <row r="887" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="887" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A887" s="38" t="s">
         <v>296</v>
       </c>
@@ -34872,7 +34884,7 @@
         <v>1358</v>
       </c>
     </row>
-    <row r="888" spans="1:18" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="888" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A888" s="24" t="s">
         <v>296</v>
       </c>
@@ -34957,7 +34969,7 @@
       <c r="Q891" s="33"/>
       <c r="R891" s="33"/>
     </row>
-    <row r="892" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="892" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A892" s="35" t="s">
         <v>382</v>
       </c>
@@ -34974,7 +34986,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="893" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="893" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A893" s="28" t="s">
         <v>268</v>
       </c>
@@ -34991,7 +35003,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="894" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="894" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A894" s="28" t="s">
         <v>268</v>
       </c>
@@ -35011,7 +35023,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="895" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="895" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A895" s="28" t="s">
         <v>268</v>
       </c>
@@ -35031,7 +35043,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="896" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="896" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A896" s="28" t="s">
         <v>268</v>
       </c>
@@ -35051,7 +35063,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="897" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="897" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A897" s="24" t="s">
         <v>273</v>
       </c>
@@ -35063,7 +35075,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="898" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="898" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A898" s="24" t="s">
         <v>268</v>
       </c>
@@ -35080,7 +35092,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="899" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="899" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A899" s="24" t="s">
         <v>296</v>
       </c>
@@ -35106,7 +35118,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="900" spans="1:15" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="900" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A900" s="24" t="s">
         <v>296</v>
       </c>
@@ -35132,7 +35144,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="901" spans="1:15" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="901" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A901" s="24" t="s">
         <v>296</v>
       </c>
@@ -35159,13 +35171,13 @@
         <v>1373</v>
       </c>
     </row>
-    <row r="902" spans="1:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="902" spans="1:15" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A902" s="24" t="s">
         <v>374</v>
       </c>
       <c r="H902" s="24"/>
     </row>
-    <row r="903" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="903" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A903" s="24" t="s">
         <v>273</v>
       </c>
@@ -35177,7 +35189,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="904" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="904" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A904" s="24" t="s">
         <v>268</v>
       </c>
@@ -35194,7 +35206,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="905" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="905" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A905" s="24" t="s">
         <v>296</v>
       </c>
@@ -35220,7 +35232,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="906" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="906" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A906" s="24" t="s">
         <v>296</v>
       </c>
@@ -35246,7 +35258,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="907" spans="1:15" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="907" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A907" s="24" t="s">
         <v>296</v>
       </c>
@@ -35273,13 +35285,13 @@
         <v>1379</v>
       </c>
     </row>
-    <row r="908" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="908" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A908" s="24" t="s">
         <v>374</v>
       </c>
       <c r="H908" s="24"/>
     </row>
-    <row r="909" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="909" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A909" s="24" t="s">
         <v>273</v>
       </c>
@@ -35291,7 +35303,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="910" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="910" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A910" s="24" t="s">
         <v>268</v>
       </c>
@@ -35308,7 +35320,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="911" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="911" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A911" s="24" t="s">
         <v>296</v>
       </c>
@@ -35334,7 +35346,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="912" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="912" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A912" s="24" t="s">
         <v>296</v>
       </c>
@@ -35360,7 +35372,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="913" spans="1:18" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="913" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A913" s="24" t="s">
         <v>296</v>
       </c>
@@ -35387,13 +35399,13 @@
         <v>1385</v>
       </c>
     </row>
-    <row r="914" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="914" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A914" s="24" t="s">
         <v>374</v>
       </c>
       <c r="H914" s="24"/>
     </row>
-    <row r="915" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="915" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A915" s="24" t="s">
         <v>273</v>
       </c>
@@ -35405,7 +35417,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="916" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="916" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A916" s="24" t="s">
         <v>268</v>
       </c>
@@ -35422,7 +35434,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="917" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="917" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A917" s="24" t="s">
         <v>296</v>
       </c>
@@ -35448,7 +35460,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="918" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="918" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A918" s="24" t="s">
         <v>296</v>
       </c>
@@ -35474,7 +35486,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="919" spans="1:18" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="919" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A919" s="24" t="s">
         <v>296</v>
       </c>
@@ -35501,13 +35513,13 @@
         <v>1391</v>
       </c>
     </row>
-    <row r="920" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="920" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A920" s="24" t="s">
         <v>374</v>
       </c>
       <c r="H920" s="24"/>
     </row>
-    <row r="921" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="921" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A921" s="24" t="s">
         <v>273</v>
       </c>
@@ -35519,7 +35531,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="922" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="922" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A922" s="24" t="s">
         <v>268</v>
       </c>
@@ -35536,7 +35548,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="923" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="923" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A923" s="24" t="s">
         <v>296</v>
       </c>
@@ -35562,7 +35574,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="924" spans="1:18" s="31" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="924" spans="1:18" s="31" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A924" s="24" t="s">
         <v>296</v>
       </c>
@@ -35598,7 +35610,7 @@
       <c r="Q924" s="24"/>
       <c r="R924" s="24"/>
     </row>
-    <row r="925" spans="1:18" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="925" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A925" s="24" t="s">
         <v>296</v>
       </c>
@@ -35625,7 +35637,7 @@
         <v>1397</v>
       </c>
     </row>
-    <row r="926" spans="1:18" s="31" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="926" spans="1:18" s="31" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A926" s="24" t="s">
         <v>374</v>
       </c>
@@ -35647,12 +35659,12 @@
       <c r="Q926" s="24"/>
       <c r="R926" s="24"/>
     </row>
-    <row r="927" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="927" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A927" s="24" t="s">
         <v>268</v>
       </c>
       <c r="B927" s="24" t="s">
-        <v>443</v>
+        <v>4229</v>
       </c>
       <c r="H927" s="24" t="s">
         <v>394</v>
@@ -35664,7 +35676,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="928" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="928" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A928" s="38" t="s">
         <v>296</v>
       </c>
@@ -35691,7 +35703,7 @@
         <v>1399</v>
       </c>
     </row>
-    <row r="929" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="929" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A929" s="38" t="s">
         <v>296</v>
       </c>
@@ -35718,7 +35730,7 @@
         <v>1401</v>
       </c>
     </row>
-    <row r="930" spans="1:18" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="930" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A930" s="24" t="s">
         <v>296</v>
       </c>

--- a/s2.xlsx
+++ b/s2.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17509" uniqueCount="4230">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17509" uniqueCount="4234">
   <si>
     <t>list_name</t>
   </si>
@@ -12714,6 +12714,18 @@
   </si>
   <si>
     <t>table27l_note6</t>
+  </si>
+  <si>
+    <t>##### عدد الشعب حسب الصف والجنس</t>
+  </si>
+  <si>
+    <t>form5_1_note1</t>
+  </si>
+  <si>
+    <t>table29_note</t>
+  </si>
+  <si>
+    <t>##### عدد الطلبة التاركين</t>
   </si>
 </sst>
 </file>
@@ -32470,7 +32482,7 @@
       <c r="Q765" s="33"/>
       <c r="R765" s="33"/>
     </row>
-    <row r="766" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="766" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A766" s="35" t="s">
         <v>382</v>
       </c>
@@ -32487,7 +32499,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="767" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="767" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A767" s="28" t="s">
         <v>268</v>
       </c>
@@ -32504,7 +32516,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="768" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="768" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A768" s="28" t="s">
         <v>268</v>
       </c>
@@ -32524,7 +32536,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="769" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="769" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A769" s="28" t="s">
         <v>268</v>
       </c>
@@ -32544,7 +32556,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="770" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="770" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A770" s="28" t="s">
         <v>268</v>
       </c>
@@ -32564,7 +32576,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="771" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="771" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A771" s="24" t="s">
         <v>273</v>
       </c>
@@ -32576,7 +32588,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="772" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="772" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A772" s="24" t="s">
         <v>268</v>
       </c>
@@ -32593,7 +32605,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="773" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="773" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A773" s="24" t="s">
         <v>296</v>
       </c>
@@ -32619,7 +32631,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="774" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="774" spans="1:15" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A774" s="24" t="s">
         <v>296</v>
       </c>
@@ -32645,7 +32657,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="775" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="775" spans="1:15" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A775" s="24" t="s">
         <v>296</v>
       </c>
@@ -32672,13 +32684,13 @@
         <v>1242</v>
       </c>
     </row>
-    <row r="776" spans="1:15" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="776" spans="1:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A776" s="24" t="s">
         <v>374</v>
       </c>
       <c r="H776" s="24"/>
     </row>
-    <row r="777" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="777" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A777" s="24" t="s">
         <v>273</v>
       </c>
@@ -32690,7 +32702,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="778" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="778" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A778" s="24" t="s">
         <v>268</v>
       </c>
@@ -32707,7 +32719,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="779" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="779" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A779" s="24" t="s">
         <v>296</v>
       </c>
@@ -32733,7 +32745,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="780" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="780" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A780" s="24" t="s">
         <v>296</v>
       </c>
@@ -32759,7 +32771,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="781" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="781" spans="1:15" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A781" s="24" t="s">
         <v>296</v>
       </c>
@@ -32786,13 +32798,13 @@
         <v>1248</v>
       </c>
     </row>
-    <row r="782" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="782" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A782" s="24" t="s">
         <v>374</v>
       </c>
       <c r="H782" s="24"/>
     </row>
-    <row r="783" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="783" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A783" s="24" t="s">
         <v>273</v>
       </c>
@@ -32804,7 +32816,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="784" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="784" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A784" s="24" t="s">
         <v>268</v>
       </c>
@@ -32821,7 +32833,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="785" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="785" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A785" s="24" t="s">
         <v>296</v>
       </c>
@@ -32847,7 +32859,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="786" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="786" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A786" s="24" t="s">
         <v>296</v>
       </c>
@@ -32873,7 +32885,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="787" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="787" spans="1:18" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A787" s="24" t="s">
         <v>296</v>
       </c>
@@ -32900,13 +32912,13 @@
         <v>1254</v>
       </c>
     </row>
-    <row r="788" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="788" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A788" s="24" t="s">
         <v>374</v>
       </c>
       <c r="H788" s="24"/>
     </row>
-    <row r="789" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="789" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A789" s="24" t="s">
         <v>273</v>
       </c>
@@ -32918,7 +32930,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="790" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="790" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A790" s="24" t="s">
         <v>268</v>
       </c>
@@ -32935,7 +32947,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="791" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="791" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A791" s="24" t="s">
         <v>296</v>
       </c>
@@ -32961,7 +32973,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="792" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="792" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A792" s="24" t="s">
         <v>296</v>
       </c>
@@ -32987,7 +32999,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="793" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="793" spans="1:18" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A793" s="24" t="s">
         <v>296</v>
       </c>
@@ -33014,13 +33026,13 @@
         <v>1260</v>
       </c>
     </row>
-    <row r="794" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="794" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A794" s="24" t="s">
         <v>374</v>
       </c>
       <c r="H794" s="24"/>
     </row>
-    <row r="795" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="795" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A795" s="24" t="s">
         <v>273</v>
       </c>
@@ -33032,7 +33044,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="796" spans="1:18" s="33" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="796" spans="1:18" s="33" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A796" s="24" t="s">
         <v>268</v>
       </c>
@@ -33062,7 +33074,7 @@
       <c r="Q796" s="24"/>
       <c r="R796" s="24"/>
     </row>
-    <row r="797" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="797" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A797" s="24" t="s">
         <v>296</v>
       </c>
@@ -33088,7 +33100,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="798" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="798" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A798" s="24" t="s">
         <v>296</v>
       </c>
@@ -33114,7 +33126,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="799" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="799" spans="1:18" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A799" s="24" t="s">
         <v>296</v>
       </c>
@@ -33141,13 +33153,13 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="800" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="800" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A800" s="24" t="s">
         <v>374</v>
       </c>
       <c r="H800" s="24"/>
     </row>
-    <row r="801" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="801" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A801" s="24" t="s">
         <v>268</v>
       </c>
@@ -33164,7 +33176,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="802" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="802" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A802" s="38" t="s">
         <v>296</v>
       </c>
@@ -33191,7 +33203,7 @@
         <v>1270</v>
       </c>
     </row>
-    <row r="803" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="803" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A803" s="38" t="s">
         <v>296</v>
       </c>
@@ -33218,7 +33230,7 @@
         <v>1272</v>
       </c>
     </row>
-    <row r="804" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="804" spans="1:18" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A804" s="24" t="s">
         <v>296</v>
       </c>
@@ -33303,7 +33315,7 @@
       <c r="Q807" s="33"/>
       <c r="R807" s="33"/>
     </row>
-    <row r="808" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="808" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A808" s="35" t="s">
         <v>382</v>
       </c>
@@ -33320,7 +33332,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="809" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="809" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A809" s="28" t="s">
         <v>268</v>
       </c>
@@ -33337,7 +33349,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="810" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="810" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A810" s="28" t="s">
         <v>268</v>
       </c>
@@ -33357,7 +33369,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="811" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="811" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A811" s="28" t="s">
         <v>268</v>
       </c>
@@ -33377,7 +33389,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="812" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="812" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A812" s="28" t="s">
         <v>268</v>
       </c>
@@ -33397,7 +33409,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="813" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="813" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A813" s="24" t="s">
         <v>273</v>
       </c>
@@ -33409,7 +33421,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="814" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="814" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A814" s="24" t="s">
         <v>268</v>
       </c>
@@ -33426,7 +33438,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="815" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="815" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A815" s="24" t="s">
         <v>296</v>
       </c>
@@ -33452,7 +33464,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="816" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="816" spans="1:18" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A816" s="24" t="s">
         <v>296</v>
       </c>
@@ -33478,7 +33490,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="817" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="817" spans="1:15" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A817" s="24" t="s">
         <v>296</v>
       </c>
@@ -33505,13 +33517,13 @@
         <v>1287</v>
       </c>
     </row>
-    <row r="818" spans="1:15" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="818" spans="1:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A818" s="24" t="s">
         <v>374</v>
       </c>
       <c r="H818" s="24"/>
     </row>
-    <row r="819" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="819" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A819" s="24" t="s">
         <v>273</v>
       </c>
@@ -33523,7 +33535,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="820" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="820" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A820" s="24" t="s">
         <v>268</v>
       </c>
@@ -33540,7 +33552,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="821" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="821" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A821" s="24" t="s">
         <v>296</v>
       </c>
@@ -33566,7 +33578,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="822" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="822" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A822" s="24" t="s">
         <v>296</v>
       </c>
@@ -33592,7 +33604,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="823" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="823" spans="1:15" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A823" s="24" t="s">
         <v>296</v>
       </c>
@@ -33619,13 +33631,13 @@
         <v>1293</v>
       </c>
     </row>
-    <row r="824" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="824" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A824" s="24" t="s">
         <v>374</v>
       </c>
       <c r="H824" s="24"/>
     </row>
-    <row r="825" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="825" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A825" s="24" t="s">
         <v>273</v>
       </c>
@@ -33637,7 +33649,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="826" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="826" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A826" s="24" t="s">
         <v>268</v>
       </c>
@@ -33654,7 +33666,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="827" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="827" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A827" s="24" t="s">
         <v>296</v>
       </c>
@@ -33680,7 +33692,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="828" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="828" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A828" s="24" t="s">
         <v>296</v>
       </c>
@@ -33706,7 +33718,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="829" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="829" spans="1:15" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A829" s="24" t="s">
         <v>296</v>
       </c>
@@ -33733,13 +33745,13 @@
         <v>1299</v>
       </c>
     </row>
-    <row r="830" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="830" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A830" s="24" t="s">
         <v>374</v>
       </c>
       <c r="H830" s="24"/>
     </row>
-    <row r="831" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="831" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A831" s="24" t="s">
         <v>273</v>
       </c>
@@ -33751,7 +33763,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="832" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="832" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A832" s="24" t="s">
         <v>268</v>
       </c>
@@ -33768,7 +33780,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="833" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="833" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A833" s="24" t="s">
         <v>296</v>
       </c>
@@ -33794,7 +33806,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="834" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="834" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A834" s="24" t="s">
         <v>296</v>
       </c>
@@ -33820,7 +33832,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="835" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="835" spans="1:18" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A835" s="24" t="s">
         <v>296</v>
       </c>
@@ -33847,13 +33859,13 @@
         <v>1305</v>
       </c>
     </row>
-    <row r="836" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="836" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A836" s="24" t="s">
         <v>374</v>
       </c>
       <c r="H836" s="24"/>
     </row>
-    <row r="837" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="837" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A837" s="24" t="s">
         <v>273</v>
       </c>
@@ -33865,7 +33877,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="838" spans="1:18" s="33" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="838" spans="1:18" s="33" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A838" s="24" t="s">
         <v>268</v>
       </c>
@@ -33895,7 +33907,7 @@
       <c r="Q838" s="24"/>
       <c r="R838" s="24"/>
     </row>
-    <row r="839" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="839" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A839" s="24" t="s">
         <v>296</v>
       </c>
@@ -33921,7 +33933,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="840" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="840" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A840" s="24" t="s">
         <v>296</v>
       </c>
@@ -33947,7 +33959,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="841" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="841" spans="1:18" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A841" s="24" t="s">
         <v>296</v>
       </c>
@@ -33974,13 +33986,13 @@
         <v>1311</v>
       </c>
     </row>
-    <row r="842" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="842" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A842" s="24" t="s">
         <v>374</v>
       </c>
       <c r="H842" s="24"/>
     </row>
-    <row r="843" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="843" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A843" s="24" t="s">
         <v>268</v>
       </c>
@@ -33997,7 +34009,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="844" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="844" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A844" s="38" t="s">
         <v>296</v>
       </c>
@@ -34024,7 +34036,7 @@
         <v>1313</v>
       </c>
     </row>
-    <row r="845" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="845" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A845" s="38" t="s">
         <v>296</v>
       </c>
@@ -34051,7 +34063,7 @@
         <v>1315</v>
       </c>
     </row>
-    <row r="846" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="846" spans="1:18" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A846" s="24" t="s">
         <v>296</v>
       </c>
@@ -34136,7 +34148,7 @@
       <c r="Q849" s="33"/>
       <c r="R849" s="33"/>
     </row>
-    <row r="850" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="850" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A850" s="35" t="s">
         <v>382</v>
       </c>
@@ -34153,7 +34165,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="851" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="851" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A851" s="28" t="s">
         <v>268</v>
       </c>
@@ -34170,7 +34182,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="852" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="852" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A852" s="28" t="s">
         <v>268</v>
       </c>
@@ -34190,7 +34202,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="853" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="853" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A853" s="28" t="s">
         <v>268</v>
       </c>
@@ -34210,7 +34222,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="854" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="854" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A854" s="28" t="s">
         <v>268</v>
       </c>
@@ -34230,7 +34242,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="855" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="855" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A855" s="24" t="s">
         <v>273</v>
       </c>
@@ -34242,7 +34254,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="856" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="856" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A856" s="24" t="s">
         <v>268</v>
       </c>
@@ -34259,7 +34271,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="857" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="857" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A857" s="24" t="s">
         <v>296</v>
       </c>
@@ -34285,7 +34297,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="858" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="858" spans="1:18" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A858" s="24" t="s">
         <v>296</v>
       </c>
@@ -34311,7 +34323,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="859" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="859" spans="1:18" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A859" s="24" t="s">
         <v>296</v>
       </c>
@@ -34338,13 +34350,13 @@
         <v>1330</v>
       </c>
     </row>
-    <row r="860" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="860" spans="1:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A860" s="24" t="s">
         <v>374</v>
       </c>
       <c r="H860" s="24"/>
     </row>
-    <row r="861" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="861" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A861" s="24" t="s">
         <v>273</v>
       </c>
@@ -34356,7 +34368,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="862" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="862" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A862" s="24" t="s">
         <v>268</v>
       </c>
@@ -34373,7 +34385,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="863" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="863" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A863" s="24" t="s">
         <v>296</v>
       </c>
@@ -34399,7 +34411,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="864" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="864" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A864" s="24" t="s">
         <v>296</v>
       </c>
@@ -34425,7 +34437,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="865" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="865" spans="1:18" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A865" s="24" t="s">
         <v>296</v>
       </c>
@@ -34452,13 +34464,13 @@
         <v>1336</v>
       </c>
     </row>
-    <row r="866" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="866" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A866" s="24" t="s">
         <v>374</v>
       </c>
       <c r="H866" s="24"/>
     </row>
-    <row r="867" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="867" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A867" s="24" t="s">
         <v>273</v>
       </c>
@@ -34470,7 +34482,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="868" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="868" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A868" s="24" t="s">
         <v>268</v>
       </c>
@@ -34487,7 +34499,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="869" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="869" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A869" s="24" t="s">
         <v>296</v>
       </c>
@@ -34513,7 +34525,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="870" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="870" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A870" s="24" t="s">
         <v>296</v>
       </c>
@@ -34539,7 +34551,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="871" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="871" spans="1:18" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A871" s="24" t="s">
         <v>296</v>
       </c>
@@ -34566,13 +34578,13 @@
         <v>1342</v>
       </c>
     </row>
-    <row r="872" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="872" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A872" s="24" t="s">
         <v>374</v>
       </c>
       <c r="H872" s="24"/>
     </row>
-    <row r="873" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="873" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A873" s="24" t="s">
         <v>273</v>
       </c>
@@ -34584,7 +34596,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="874" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="874" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A874" s="24" t="s">
         <v>268</v>
       </c>
@@ -34601,7 +34613,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="875" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="875" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A875" s="24" t="s">
         <v>296</v>
       </c>
@@ -34627,7 +34639,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="876" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="876" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A876" s="24" t="s">
         <v>296</v>
       </c>
@@ -34653,7 +34665,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="877" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="877" spans="1:18" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A877" s="24" t="s">
         <v>296</v>
       </c>
@@ -34680,13 +34692,13 @@
         <v>1348</v>
       </c>
     </row>
-    <row r="878" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="878" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A878" s="24" t="s">
         <v>374</v>
       </c>
       <c r="H878" s="24"/>
     </row>
-    <row r="879" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="879" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A879" s="24" t="s">
         <v>273</v>
       </c>
@@ -34698,7 +34710,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="880" spans="1:18" s="33" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="880" spans="1:18" s="33" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A880" s="24" t="s">
         <v>268</v>
       </c>
@@ -34728,7 +34740,7 @@
       <c r="Q880" s="24"/>
       <c r="R880" s="24"/>
     </row>
-    <row r="881" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="881" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A881" s="24" t="s">
         <v>296</v>
       </c>
@@ -34754,7 +34766,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="882" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="882" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A882" s="24" t="s">
         <v>296</v>
       </c>
@@ -34780,7 +34792,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="883" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="883" spans="1:18" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A883" s="24" t="s">
         <v>296</v>
       </c>
@@ -34807,13 +34819,13 @@
         <v>1354</v>
       </c>
     </row>
-    <row r="884" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="884" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A884" s="24" t="s">
         <v>374</v>
       </c>
       <c r="H884" s="24"/>
     </row>
-    <row r="885" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="885" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A885" s="24" t="s">
         <v>268</v>
       </c>
@@ -34830,7 +34842,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="886" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="886" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A886" s="38" t="s">
         <v>296</v>
       </c>
@@ -34857,7 +34869,7 @@
         <v>1356</v>
       </c>
     </row>
-    <row r="887" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="887" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A887" s="38" t="s">
         <v>296</v>
       </c>
@@ -34884,7 +34896,7 @@
         <v>1358</v>
       </c>
     </row>
-    <row r="888" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="888" spans="1:18" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A888" s="24" t="s">
         <v>296</v>
       </c>
@@ -34969,7 +34981,7 @@
       <c r="Q891" s="33"/>
       <c r="R891" s="33"/>
     </row>
-    <row r="892" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="892" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A892" s="35" t="s">
         <v>382</v>
       </c>
@@ -34986,7 +34998,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="893" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="893" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A893" s="28" t="s">
         <v>268</v>
       </c>
@@ -35003,7 +35015,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="894" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="894" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A894" s="28" t="s">
         <v>268</v>
       </c>
@@ -35023,7 +35035,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="895" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="895" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A895" s="28" t="s">
         <v>268</v>
       </c>
@@ -35043,7 +35055,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="896" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="896" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A896" s="28" t="s">
         <v>268</v>
       </c>
@@ -35063,7 +35075,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="897" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="897" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A897" s="24" t="s">
         <v>273</v>
       </c>
@@ -35075,7 +35087,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="898" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="898" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A898" s="24" t="s">
         <v>268</v>
       </c>
@@ -35092,7 +35104,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="899" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="899" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A899" s="24" t="s">
         <v>296</v>
       </c>
@@ -35118,7 +35130,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="900" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="900" spans="1:15" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A900" s="24" t="s">
         <v>296</v>
       </c>
@@ -35144,7 +35156,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="901" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="901" spans="1:15" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A901" s="24" t="s">
         <v>296</v>
       </c>
@@ -35171,13 +35183,13 @@
         <v>1373</v>
       </c>
     </row>
-    <row r="902" spans="1:15" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="902" spans="1:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A902" s="24" t="s">
         <v>374</v>
       </c>
       <c r="H902" s="24"/>
     </row>
-    <row r="903" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="903" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A903" s="24" t="s">
         <v>273</v>
       </c>
@@ -35189,7 +35201,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="904" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="904" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A904" s="24" t="s">
         <v>268</v>
       </c>
@@ -35206,7 +35218,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="905" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="905" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A905" s="24" t="s">
         <v>296</v>
       </c>
@@ -35232,7 +35244,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="906" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="906" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A906" s="24" t="s">
         <v>296</v>
       </c>
@@ -35258,7 +35270,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="907" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="907" spans="1:15" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A907" s="24" t="s">
         <v>296</v>
       </c>
@@ -35285,13 +35297,13 @@
         <v>1379</v>
       </c>
     </row>
-    <row r="908" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="908" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A908" s="24" t="s">
         <v>374</v>
       </c>
       <c r="H908" s="24"/>
     </row>
-    <row r="909" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="909" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A909" s="24" t="s">
         <v>273</v>
       </c>
@@ -35303,7 +35315,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="910" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="910" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A910" s="24" t="s">
         <v>268</v>
       </c>
@@ -35320,7 +35332,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="911" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="911" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A911" s="24" t="s">
         <v>296</v>
       </c>
@@ -35346,7 +35358,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="912" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="912" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A912" s="24" t="s">
         <v>296</v>
       </c>
@@ -35372,7 +35384,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="913" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="913" spans="1:18" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A913" s="24" t="s">
         <v>296</v>
       </c>
@@ -35399,13 +35411,13 @@
         <v>1385</v>
       </c>
     </row>
-    <row r="914" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="914" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A914" s="24" t="s">
         <v>374</v>
       </c>
       <c r="H914" s="24"/>
     </row>
-    <row r="915" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="915" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A915" s="24" t="s">
         <v>273</v>
       </c>
@@ -35417,7 +35429,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="916" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="916" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A916" s="24" t="s">
         <v>268</v>
       </c>
@@ -35434,7 +35446,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="917" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="917" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A917" s="24" t="s">
         <v>296</v>
       </c>
@@ -35460,7 +35472,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="918" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="918" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A918" s="24" t="s">
         <v>296</v>
       </c>
@@ -35486,7 +35498,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="919" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="919" spans="1:18" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A919" s="24" t="s">
         <v>296</v>
       </c>
@@ -35513,13 +35525,13 @@
         <v>1391</v>
       </c>
     </row>
-    <row r="920" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="920" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A920" s="24" t="s">
         <v>374</v>
       </c>
       <c r="H920" s="24"/>
     </row>
-    <row r="921" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="921" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A921" s="24" t="s">
         <v>273</v>
       </c>
@@ -35531,7 +35543,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="922" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="922" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A922" s="24" t="s">
         <v>268</v>
       </c>
@@ -35548,7 +35560,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="923" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="923" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A923" s="24" t="s">
         <v>296</v>
       </c>
@@ -35574,7 +35586,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="924" spans="1:18" s="31" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="924" spans="1:18" s="31" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A924" s="24" t="s">
         <v>296</v>
       </c>
@@ -35610,7 +35622,7 @@
       <c r="Q924" s="24"/>
       <c r="R924" s="24"/>
     </row>
-    <row r="925" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="925" spans="1:18" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A925" s="24" t="s">
         <v>296</v>
       </c>
@@ -35637,7 +35649,7 @@
         <v>1397</v>
       </c>
     </row>
-    <row r="926" spans="1:18" s="31" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="926" spans="1:18" s="31" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A926" s="24" t="s">
         <v>374</v>
       </c>
@@ -35659,7 +35671,7 @@
       <c r="Q926" s="24"/>
       <c r="R926" s="24"/>
     </row>
-    <row r="927" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="927" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A927" s="24" t="s">
         <v>268</v>
       </c>
@@ -35676,7 +35688,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="928" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="928" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A928" s="38" t="s">
         <v>296</v>
       </c>
@@ -35703,7 +35715,7 @@
         <v>1399</v>
       </c>
     </row>
-    <row r="929" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="929" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A929" s="38" t="s">
         <v>296</v>
       </c>
@@ -35730,7 +35742,7 @@
         <v>1401</v>
       </c>
     </row>
-    <row r="930" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="930" spans="1:18" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A930" s="24" t="s">
         <v>296</v>
       </c>
@@ -35878,10 +35890,10 @@
         <v>382</v>
       </c>
       <c r="B938" s="24" t="s">
-        <v>1408</v>
+        <v>4231</v>
       </c>
       <c r="H938" s="24" t="s">
-        <v>384</v>
+        <v>4230</v>
       </c>
       <c r="I938" s="33" t="s">
         <v>1407</v>
@@ -35901,7 +35913,7 @@
         <v>268</v>
       </c>
       <c r="B939" s="24" t="s">
-        <v>1409</v>
+        <v>4231</v>
       </c>
       <c r="H939" s="24" t="s">
         <v>1410</v>
@@ -35921,7 +35933,7 @@
         <v>268</v>
       </c>
       <c r="B940" s="24" t="s">
-        <v>1409</v>
+        <v>4231</v>
       </c>
       <c r="H940" s="24" t="s">
         <v>388</v>
@@ -35941,7 +35953,7 @@
         <v>268</v>
       </c>
       <c r="B941" s="24" t="s">
-        <v>1409</v>
+        <v>4231</v>
       </c>
       <c r="H941" s="24" t="s">
         <v>391</v>
@@ -35961,7 +35973,7 @@
         <v>268</v>
       </c>
       <c r="B942" s="24" t="s">
-        <v>1409</v>
+        <v>4231</v>
       </c>
       <c r="H942" s="24" t="s">
         <v>1414</v>
@@ -35981,7 +35993,7 @@
         <v>268</v>
       </c>
       <c r="B943" s="24" t="s">
-        <v>1409</v>
+        <v>4231</v>
       </c>
       <c r="H943" s="24" t="s">
         <v>394</v>
@@ -38339,15 +38351,15 @@
       <c r="Q1056" s="33"/>
       <c r="R1056" s="33"/>
     </row>
-    <row r="1057" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1057" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A1057" s="35" t="s">
         <v>382</v>
       </c>
       <c r="B1057" s="24" t="s">
-        <v>1408</v>
+        <v>1586</v>
       </c>
       <c r="H1057" s="24" t="s">
-        <v>384</v>
+        <v>4233</v>
       </c>
       <c r="I1057" s="33" t="s">
         <v>1587</v>
@@ -38362,12 +38374,12 @@
       <c r="Q1057" s="33"/>
       <c r="R1057" s="33"/>
     </row>
-    <row r="1058" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1058" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A1058" s="28" t="s">
         <v>268</v>
       </c>
       <c r="B1058" s="24" t="s">
-        <v>1409</v>
+        <v>1586</v>
       </c>
       <c r="H1058" s="24" t="s">
         <v>1410</v>
@@ -38382,12 +38394,12 @@
         <v>1588</v>
       </c>
     </row>
-    <row r="1059" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1059" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A1059" s="28" t="s">
         <v>268</v>
       </c>
       <c r="B1059" s="24" t="s">
-        <v>1409</v>
+        <v>1586</v>
       </c>
       <c r="H1059" s="24" t="s">
         <v>388</v>
@@ -38402,12 +38414,12 @@
         <v>1413</v>
       </c>
     </row>
-    <row r="1060" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1060" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A1060" s="28" t="s">
         <v>268</v>
       </c>
       <c r="B1060" s="24" t="s">
-        <v>1409</v>
+        <v>1586</v>
       </c>
       <c r="H1060" s="24" t="s">
         <v>391</v>
@@ -38422,12 +38434,12 @@
         <v>392</v>
       </c>
     </row>
-    <row r="1061" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1061" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A1061" s="28" t="s">
         <v>268</v>
       </c>
       <c r="B1061" s="24" t="s">
-        <v>1409</v>
+        <v>1586</v>
       </c>
       <c r="H1061" s="24" t="s">
         <v>394</v>
@@ -38442,7 +38454,7 @@
         <v>1589</v>
       </c>
     </row>
-    <row r="1062" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1062" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A1062" s="24" t="s">
         <v>273</v>
       </c>
@@ -38454,7 +38466,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="1063" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1063" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A1063" s="24" t="s">
         <v>268</v>
       </c>
@@ -38474,7 +38486,7 @@
         <v>1420</v>
       </c>
     </row>
-    <row r="1064" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1064" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A1064" s="24" t="s">
         <v>296</v>
       </c>
@@ -38500,7 +38512,7 @@
         <v>1422</v>
       </c>
     </row>
-    <row r="1065" spans="1:18" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1065" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1065" s="24" t="s">
         <v>296</v>
       </c>
@@ -38526,7 +38538,7 @@
         <v>1424</v>
       </c>
     </row>
-    <row r="1066" spans="1:18" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1066" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1066" s="24" t="s">
         <v>296</v>
       </c>
@@ -38553,13 +38565,13 @@
         <v>1595</v>
       </c>
     </row>
-    <row r="1067" spans="1:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1067" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1067" s="24" t="s">
         <v>374</v>
       </c>
       <c r="H1067" s="24"/>
     </row>
-    <row r="1068" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1068" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A1068" s="24" t="s">
         <v>273</v>
       </c>
@@ -38571,7 +38583,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="1069" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1069" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A1069" s="24" t="s">
         <v>268</v>
       </c>
@@ -38591,7 +38603,7 @@
         <v>1420</v>
       </c>
     </row>
-    <row r="1070" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1070" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A1070" s="24" t="s">
         <v>296</v>
       </c>
@@ -38617,7 +38629,7 @@
         <v>1422</v>
       </c>
     </row>
-    <row r="1071" spans="1:18" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1071" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1071" s="24" t="s">
         <v>296</v>
       </c>
@@ -38643,7 +38655,7 @@
         <v>1424</v>
       </c>
     </row>
-    <row r="1072" spans="1:18" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1072" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1072" s="24" t="s">
         <v>296</v>
       </c>
@@ -38670,13 +38682,13 @@
         <v>1601</v>
       </c>
     </row>
-    <row r="1073" spans="1:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1073" spans="1:15" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1073" s="24" t="s">
         <v>374</v>
       </c>
       <c r="H1073" s="24"/>
     </row>
-    <row r="1074" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1074" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A1074" s="24" t="s">
         <v>273</v>
       </c>
@@ -38688,7 +38700,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="1075" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1075" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A1075" s="24" t="s">
         <v>268</v>
       </c>
@@ -38708,7 +38720,7 @@
         <v>1420</v>
       </c>
     </row>
-    <row r="1076" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1076" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A1076" s="24" t="s">
         <v>296</v>
       </c>
@@ -38734,7 +38746,7 @@
         <v>1422</v>
       </c>
     </row>
-    <row r="1077" spans="1:15" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1077" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1077" s="24" t="s">
         <v>296</v>
       </c>
@@ -38760,7 +38772,7 @@
         <v>1424</v>
       </c>
     </row>
-    <row r="1078" spans="1:15" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1078" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1078" s="24" t="s">
         <v>296</v>
       </c>
@@ -38787,13 +38799,13 @@
         <v>1607</v>
       </c>
     </row>
-    <row r="1079" spans="1:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1079" spans="1:15" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1079" s="24" t="s">
         <v>374</v>
       </c>
       <c r="H1079" s="24"/>
     </row>
-    <row r="1080" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1080" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A1080" s="24" t="s">
         <v>273</v>
       </c>
@@ -38805,7 +38817,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="1081" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1081" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A1081" s="24" t="s">
         <v>268</v>
       </c>
@@ -38825,7 +38837,7 @@
         <v>1452</v>
       </c>
     </row>
-    <row r="1082" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1082" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A1082" s="24" t="s">
         <v>296</v>
       </c>
@@ -38851,7 +38863,7 @@
         <v>1454</v>
       </c>
     </row>
-    <row r="1083" spans="1:15" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1083" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1083" s="24" t="s">
         <v>296</v>
       </c>
@@ -38877,7 +38889,7 @@
         <v>1456</v>
       </c>
     </row>
-    <row r="1084" spans="1:15" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1084" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1084" s="24" t="s">
         <v>296</v>
       </c>
@@ -38904,13 +38916,13 @@
         <v>1613</v>
       </c>
     </row>
-    <row r="1085" spans="1:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1085" spans="1:15" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1085" s="24" t="s">
         <v>374</v>
       </c>
       <c r="H1085" s="24"/>
     </row>
-    <row r="1086" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1086" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A1086" s="24" t="s">
         <v>273</v>
       </c>
@@ -38922,7 +38934,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="1087" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1087" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A1087" s="24" t="s">
         <v>268</v>
       </c>
@@ -38942,7 +38954,7 @@
         <v>1465</v>
       </c>
     </row>
-    <row r="1088" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1088" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A1088" s="24" t="s">
         <v>296</v>
       </c>
@@ -38968,7 +38980,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="1089" spans="1:15" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1089" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1089" s="24" t="s">
         <v>296</v>
       </c>
@@ -38994,7 +39006,7 @@
         <v>1469</v>
       </c>
     </row>
-    <row r="1090" spans="1:15" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1090" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1090" s="24" t="s">
         <v>296</v>
       </c>
@@ -39021,13 +39033,13 @@
         <v>1619</v>
       </c>
     </row>
-    <row r="1091" spans="1:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1091" spans="1:15" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1091" s="24" t="s">
         <v>374</v>
       </c>
       <c r="H1091" s="24"/>
     </row>
-    <row r="1092" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1092" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A1092" s="24" t="s">
         <v>273</v>
       </c>
@@ -39039,7 +39051,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="1093" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1093" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A1093" s="24" t="s">
         <v>268</v>
       </c>
@@ -39059,7 +39071,7 @@
         <v>1478</v>
       </c>
     </row>
-    <row r="1094" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1094" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A1094" s="24" t="s">
         <v>296</v>
       </c>
@@ -39085,7 +39097,7 @@
         <v>1480</v>
       </c>
     </row>
-    <row r="1095" spans="1:15" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1095" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1095" s="24" t="s">
         <v>296</v>
       </c>
@@ -39111,7 +39123,7 @@
         <v>1482</v>
       </c>
     </row>
-    <row r="1096" spans="1:15" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1096" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1096" s="24" t="s">
         <v>296</v>
       </c>
@@ -39138,13 +39150,13 @@
         <v>1625</v>
       </c>
     </row>
-    <row r="1097" spans="1:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1097" spans="1:15" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1097" s="24" t="s">
         <v>374</v>
       </c>
       <c r="H1097" s="24"/>
     </row>
-    <row r="1098" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1098" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A1098" s="24" t="s">
         <v>273</v>
       </c>
@@ -39156,7 +39168,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="1099" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1099" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A1099" s="24" t="s">
         <v>268</v>
       </c>
@@ -39176,7 +39188,7 @@
         <v>1491</v>
       </c>
     </row>
-    <row r="1100" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1100" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A1100" s="24" t="s">
         <v>296</v>
       </c>
@@ -39202,7 +39214,7 @@
         <v>1493</v>
       </c>
     </row>
-    <row r="1101" spans="1:15" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1101" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1101" s="24" t="s">
         <v>296</v>
       </c>
@@ -39228,7 +39240,7 @@
         <v>1495</v>
       </c>
     </row>
-    <row r="1102" spans="1:15" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1102" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1102" s="24" t="s">
         <v>296</v>
       </c>
@@ -39255,13 +39267,13 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="1103" spans="1:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1103" spans="1:15" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1103" s="24" t="s">
         <v>374</v>
       </c>
       <c r="H1103" s="24"/>
     </row>
-    <row r="1104" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1104" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A1104" s="24" t="s">
         <v>273</v>
       </c>
@@ -39273,7 +39285,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="1105" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1105" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A1105" s="24" t="s">
         <v>268</v>
       </c>
@@ -39293,7 +39305,7 @@
         <v>1452</v>
       </c>
     </row>
-    <row r="1106" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1106" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A1106" s="24" t="s">
         <v>296</v>
       </c>
@@ -39319,7 +39331,7 @@
         <v>1454</v>
       </c>
     </row>
-    <row r="1107" spans="1:15" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1107" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1107" s="24" t="s">
         <v>296</v>
       </c>
@@ -39345,7 +39357,7 @@
         <v>1456</v>
       </c>
     </row>
-    <row r="1108" spans="1:15" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1108" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1108" s="24" t="s">
         <v>296</v>
       </c>
@@ -39372,13 +39384,13 @@
         <v>1637</v>
       </c>
     </row>
-    <row r="1109" spans="1:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1109" spans="1:15" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1109" s="24" t="s">
         <v>374</v>
       </c>
       <c r="H1109" s="24"/>
     </row>
-    <row r="1110" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1110" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A1110" s="24" t="s">
         <v>273</v>
       </c>
@@ -39390,7 +39402,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="1111" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1111" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A1111" s="24" t="s">
         <v>268</v>
       </c>
@@ -39410,7 +39422,7 @@
         <v>1465</v>
       </c>
     </row>
-    <row r="1112" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1112" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A1112" s="24" t="s">
         <v>296</v>
       </c>
@@ -39436,7 +39448,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="1113" spans="1:15" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1113" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1113" s="24" t="s">
         <v>296</v>
       </c>
@@ -39462,7 +39474,7 @@
         <v>1469</v>
       </c>
     </row>
-    <row r="1114" spans="1:15" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1114" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1114" s="24" t="s">
         <v>296</v>
       </c>
@@ -39489,13 +39501,13 @@
         <v>1643</v>
       </c>
     </row>
-    <row r="1115" spans="1:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1115" spans="1:15" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1115" s="24" t="s">
         <v>374</v>
       </c>
       <c r="H1115" s="24"/>
     </row>
-    <row r="1116" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1116" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A1116" s="24" t="s">
         <v>273</v>
       </c>
@@ -39507,7 +39519,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="1117" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1117" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A1117" s="24" t="s">
         <v>268</v>
       </c>
@@ -39527,7 +39539,7 @@
         <v>1478</v>
       </c>
     </row>
-    <row r="1118" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1118" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A1118" s="24" t="s">
         <v>296</v>
       </c>
@@ -39553,7 +39565,7 @@
         <v>1480</v>
       </c>
     </row>
-    <row r="1119" spans="1:15" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1119" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1119" s="24" t="s">
         <v>296</v>
       </c>
@@ -39579,7 +39591,7 @@
         <v>1482</v>
       </c>
     </row>
-    <row r="1120" spans="1:15" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1120" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1120" s="24" t="s">
         <v>296</v>
       </c>
@@ -39606,13 +39618,13 @@
         <v>1649</v>
       </c>
     </row>
-    <row r="1121" spans="1:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1121" spans="1:15" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1121" s="24" t="s">
         <v>374</v>
       </c>
       <c r="H1121" s="24"/>
     </row>
-    <row r="1122" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1122" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A1122" s="24" t="s">
         <v>273</v>
       </c>
@@ -39624,7 +39636,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="1123" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1123" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A1123" s="24" t="s">
         <v>268</v>
       </c>
@@ -39644,7 +39656,7 @@
         <v>1491</v>
       </c>
     </row>
-    <row r="1124" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1124" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A1124" s="24" t="s">
         <v>296</v>
       </c>
@@ -39670,7 +39682,7 @@
         <v>1493</v>
       </c>
     </row>
-    <row r="1125" spans="1:15" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1125" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1125" s="24" t="s">
         <v>296</v>
       </c>
@@ -39696,7 +39708,7 @@
         <v>1495</v>
       </c>
     </row>
-    <row r="1126" spans="1:15" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1126" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1126" s="24" t="s">
         <v>296</v>
       </c>
@@ -39723,13 +39735,13 @@
         <v>1655</v>
       </c>
     </row>
-    <row r="1127" spans="1:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1127" spans="1:15" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1127" s="24" t="s">
         <v>374</v>
       </c>
       <c r="H1127" s="24"/>
     </row>
-    <row r="1128" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1128" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A1128" s="24" t="s">
         <v>273</v>
       </c>
@@ -39741,7 +39753,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="1129" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1129" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A1129" s="24" t="s">
         <v>268</v>
       </c>
@@ -39761,7 +39773,7 @@
         <v>1452</v>
       </c>
     </row>
-    <row r="1130" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1130" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A1130" s="24" t="s">
         <v>296</v>
       </c>
@@ -39787,7 +39799,7 @@
         <v>1454</v>
       </c>
     </row>
-    <row r="1131" spans="1:15" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1131" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1131" s="24" t="s">
         <v>296</v>
       </c>
@@ -39813,7 +39825,7 @@
         <v>1456</v>
       </c>
     </row>
-    <row r="1132" spans="1:15" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1132" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1132" s="24" t="s">
         <v>296</v>
       </c>
@@ -39840,13 +39852,13 @@
         <v>1661</v>
       </c>
     </row>
-    <row r="1133" spans="1:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1133" spans="1:15" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1133" s="24" t="s">
         <v>374</v>
       </c>
       <c r="H1133" s="24"/>
     </row>
-    <row r="1134" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1134" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A1134" s="24" t="s">
         <v>273</v>
       </c>
@@ -39858,7 +39870,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="1135" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1135" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A1135" s="24" t="s">
         <v>268</v>
       </c>
@@ -39878,7 +39890,7 @@
         <v>1465</v>
       </c>
     </row>
-    <row r="1136" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1136" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A1136" s="24" t="s">
         <v>296</v>
       </c>
@@ -39904,7 +39916,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="1137" spans="1:18" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1137" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1137" s="24" t="s">
         <v>296</v>
       </c>
@@ -39930,7 +39942,7 @@
         <v>1469</v>
       </c>
     </row>
-    <row r="1138" spans="1:18" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1138" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1138" s="24" t="s">
         <v>296</v>
       </c>
@@ -39957,13 +39969,13 @@
         <v>1667</v>
       </c>
     </row>
-    <row r="1139" spans="1:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1139" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1139" s="24" t="s">
         <v>374</v>
       </c>
       <c r="H1139" s="24"/>
     </row>
-    <row r="1140" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1140" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A1140" s="24" t="s">
         <v>273</v>
       </c>
@@ -39975,7 +39987,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="1141" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1141" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A1141" s="24" t="s">
         <v>268</v>
       </c>
@@ -39995,7 +40007,7 @@
         <v>1478</v>
       </c>
     </row>
-    <row r="1142" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1142" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A1142" s="24" t="s">
         <v>296</v>
       </c>
@@ -40021,7 +40033,7 @@
         <v>1480</v>
       </c>
     </row>
-    <row r="1143" spans="1:18" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1143" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1143" s="24" t="s">
         <v>296</v>
       </c>
@@ -40047,7 +40059,7 @@
         <v>1482</v>
       </c>
     </row>
-    <row r="1144" spans="1:18" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1144" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1144" s="24" t="s">
         <v>296</v>
       </c>
@@ -40074,13 +40086,13 @@
         <v>1673</v>
       </c>
     </row>
-    <row r="1145" spans="1:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1145" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1145" s="24" t="s">
         <v>374</v>
       </c>
       <c r="H1145" s="24"/>
     </row>
-    <row r="1146" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1146" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A1146" s="24" t="s">
         <v>273</v>
       </c>
@@ -40092,7 +40104,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="1147" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1147" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A1147" s="24" t="s">
         <v>268</v>
       </c>
@@ -40112,7 +40124,7 @@
         <v>1491</v>
       </c>
     </row>
-    <row r="1148" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1148" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A1148" s="24" t="s">
         <v>296</v>
       </c>
@@ -40138,7 +40150,7 @@
         <v>1493</v>
       </c>
     </row>
-    <row r="1149" spans="1:18" s="33" customFormat="1" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1149" spans="1:18" s="33" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1149" s="24" t="s">
         <v>296</v>
       </c>
@@ -40174,7 +40186,7 @@
       <c r="Q1149" s="24"/>
       <c r="R1149" s="24"/>
     </row>
-    <row r="1150" spans="1:18" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1150" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1150" s="24" t="s">
         <v>296</v>
       </c>
@@ -40201,13 +40213,13 @@
         <v>1679</v>
       </c>
     </row>
-    <row r="1151" spans="1:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1151" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1151" s="24" t="s">
         <v>374</v>
       </c>
       <c r="H1151" s="24"/>
     </row>
-    <row r="1152" spans="1:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1152" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1152" s="24" t="s">
         <v>273</v>
       </c>
@@ -40216,12 +40228,12 @@
         <v>398</v>
       </c>
     </row>
-    <row r="1153" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1153" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A1153" s="24" t="s">
         <v>268</v>
       </c>
       <c r="B1153" s="24" t="s">
-        <v>1409</v>
+        <v>4232</v>
       </c>
       <c r="H1153" s="24" t="s">
         <v>1573</v>
@@ -40236,7 +40248,7 @@
         <v>1574</v>
       </c>
     </row>
-    <row r="1154" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1154" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A1154" s="38" t="s">
         <v>296</v>
       </c>
@@ -40262,7 +40274,7 @@
         <v>1681</v>
       </c>
     </row>
-    <row r="1155" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1155" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A1155" s="38" t="s">
         <v>296</v>
       </c>
@@ -40288,7 +40300,7 @@
         <v>1683</v>
       </c>
     </row>
-    <row r="1156" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1156" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A1156" s="38" t="s">
         <v>296</v>
       </c>
@@ -40314,7 +40326,7 @@
         <v>1685</v>
       </c>
     </row>
-    <row r="1157" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1157" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A1157" s="24" t="s">
         <v>374</v>
       </c>

--- a/s2.xlsx
+++ b/s2.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17509" uniqueCount="4234">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17509" uniqueCount="4235">
   <si>
     <t>list_name</t>
   </si>
@@ -12726,6 +12726,9 @@
   </si>
   <si>
     <t>##### عدد الطلبة التاركين</t>
+  </si>
+  <si>
+    <t>form5_2_note</t>
   </si>
 </sst>
 </file>
@@ -38356,7 +38359,7 @@
         <v>382</v>
       </c>
       <c r="B1057" s="24" t="s">
-        <v>1586</v>
+        <v>4234</v>
       </c>
       <c r="H1057" s="24" t="s">
         <v>4233</v>
@@ -38379,7 +38382,7 @@
         <v>268</v>
       </c>
       <c r="B1058" s="24" t="s">
-        <v>1586</v>
+        <v>4234</v>
       </c>
       <c r="H1058" s="24" t="s">
         <v>1410</v>
@@ -38399,7 +38402,7 @@
         <v>268</v>
       </c>
       <c r="B1059" s="24" t="s">
-        <v>1586</v>
+        <v>4234</v>
       </c>
       <c r="H1059" s="24" t="s">
         <v>388</v>
@@ -38419,7 +38422,7 @@
         <v>268</v>
       </c>
       <c r="B1060" s="24" t="s">
-        <v>1586</v>
+        <v>4234</v>
       </c>
       <c r="H1060" s="24" t="s">
         <v>391</v>
@@ -38439,7 +38442,7 @@
         <v>268</v>
       </c>
       <c r="B1061" s="24" t="s">
-        <v>1586</v>
+        <v>4234</v>
       </c>
       <c r="H1061" s="24" t="s">
         <v>394</v>

--- a/s2.xlsx
+++ b/s2.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17511" uniqueCount="4240">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17515" uniqueCount="4256">
   <si>
     <t>list_name</t>
   </si>
@@ -12744,6 +12744,54 @@
   </si>
   <si>
     <t>table30_75</t>
+  </si>
+  <si>
+    <t>##### الطلبة الراسبين بسبب الفشل بالامتحان</t>
+  </si>
+  <si>
+    <t>form5_4_note</t>
+  </si>
+  <si>
+    <t>table31a_74</t>
+  </si>
+  <si>
+    <t>table31a_note</t>
+  </si>
+  <si>
+    <t>##### الطلبة الراسبين بسبب تجاوز أيام الغياب</t>
+  </si>
+  <si>
+    <t>form5_5_note</t>
+  </si>
+  <si>
+    <t>table31b_74</t>
+  </si>
+  <si>
+    <t>table31b_note</t>
+  </si>
+  <si>
+    <t>##### الطلبة الراسبين لاسباب أخرى</t>
+  </si>
+  <si>
+    <t>form5_6_note</t>
+  </si>
+  <si>
+    <t>table31c_74</t>
+  </si>
+  <si>
+    <t>table31c_note</t>
+  </si>
+  <si>
+    <t>##### مجموع الطلبة الراسبين لكل الاسباب</t>
+  </si>
+  <si>
+    <t>form5_7_note</t>
+  </si>
+  <si>
+    <t>table31d_74</t>
+  </si>
+  <si>
+    <t>table31d_note</t>
   </si>
 </sst>
 </file>
@@ -42442,15 +42490,15 @@
       <c r="Q1264" s="33"/>
       <c r="R1264" s="33"/>
     </row>
-    <row r="1265" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="1265" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1265" s="35" t="s">
         <v>382</v>
       </c>
       <c r="B1265" s="24" t="s">
-        <v>1408</v>
+        <v>4241</v>
       </c>
       <c r="H1265" s="24" t="s">
-        <v>384</v>
+        <v>4240</v>
       </c>
       <c r="I1265" s="33" t="s">
         <v>1784</v>
@@ -42465,12 +42513,12 @@
       <c r="Q1265" s="33"/>
       <c r="R1265" s="33"/>
     </row>
-    <row r="1266" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="1266" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1266" s="28" t="s">
         <v>268</v>
       </c>
       <c r="B1266" s="24" t="s">
-        <v>1409</v>
+        <v>4241</v>
       </c>
       <c r="H1266" s="24" t="s">
         <v>1410</v>
@@ -42485,12 +42533,12 @@
         <v>1588</v>
       </c>
     </row>
-    <row r="1267" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="1267" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1267" s="28" t="s">
         <v>268</v>
       </c>
       <c r="B1267" s="24" t="s">
-        <v>1409</v>
+        <v>4241</v>
       </c>
       <c r="H1267" s="24" t="s">
         <v>388</v>
@@ -42505,12 +42553,12 @@
         <v>1413</v>
       </c>
     </row>
-    <row r="1268" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="1268" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1268" s="28" t="s">
         <v>268</v>
       </c>
       <c r="B1268" s="24" t="s">
-        <v>1409</v>
+        <v>4241</v>
       </c>
       <c r="H1268" s="24" t="s">
         <v>391</v>
@@ -42525,12 +42573,12 @@
         <v>392</v>
       </c>
     </row>
-    <row r="1269" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="1269" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1269" s="28" t="s">
         <v>268</v>
       </c>
       <c r="B1269" s="24" t="s">
-        <v>1409</v>
+        <v>4241</v>
       </c>
       <c r="H1269" s="24" t="s">
         <v>394</v>
@@ -42545,7 +42593,7 @@
         <v>1589</v>
       </c>
     </row>
-    <row r="1270" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="1270" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1270" s="28" t="s">
         <v>273</v>
       </c>
@@ -42558,7 +42606,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="1271" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="1271" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1271" s="24" t="s">
         <v>268</v>
       </c>
@@ -42578,7 +42626,7 @@
         <v>1420</v>
       </c>
     </row>
-    <row r="1272" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="1272" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1272" s="24" t="s">
         <v>296</v>
       </c>
@@ -42604,7 +42652,7 @@
         <v>1422</v>
       </c>
     </row>
-    <row r="1273" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="1273" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1273" s="24" t="s">
         <v>296</v>
       </c>
@@ -42630,7 +42678,7 @@
         <v>1424</v>
       </c>
     </row>
-    <row r="1274" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1274" spans="1:18" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1274" s="24" t="s">
         <v>296</v>
       </c>
@@ -42657,13 +42705,13 @@
         <v>1790</v>
       </c>
     </row>
-    <row r="1275" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1275" spans="1:18" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1275" s="24" t="s">
         <v>374</v>
       </c>
       <c r="H1275" s="24"/>
     </row>
-    <row r="1276" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1276" spans="1:18" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1276" s="24" t="s">
         <v>273</v>
       </c>
@@ -42675,7 +42723,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="1277" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1277" spans="1:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1277" s="24" t="s">
         <v>268</v>
       </c>
@@ -42695,7 +42743,7 @@
         <v>1420</v>
       </c>
     </row>
-    <row r="1278" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="1278" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1278" s="24" t="s">
         <v>296</v>
       </c>
@@ -42721,7 +42769,7 @@
         <v>1422</v>
       </c>
     </row>
-    <row r="1279" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="1279" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1279" s="24" t="s">
         <v>296</v>
       </c>
@@ -42747,7 +42795,7 @@
         <v>1424</v>
       </c>
     </row>
-    <row r="1280" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="1280" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1280" s="24" t="s">
         <v>296</v>
       </c>
@@ -42774,13 +42822,13 @@
         <v>1796</v>
       </c>
     </row>
-    <row r="1281" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1281" spans="1:15" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1281" s="24" t="s">
         <v>374</v>
       </c>
       <c r="H1281" s="24"/>
     </row>
-    <row r="1282" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1282" spans="1:15" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1282" s="24" t="s">
         <v>273</v>
       </c>
@@ -42792,7 +42840,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="1283" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1283" spans="1:15" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1283" s="24" t="s">
         <v>268</v>
       </c>
@@ -42812,7 +42860,7 @@
         <v>1420</v>
       </c>
     </row>
-    <row r="1284" spans="1:15" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1284" spans="1:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1284" s="24" t="s">
         <v>296</v>
       </c>
@@ -42838,7 +42886,7 @@
         <v>1422</v>
       </c>
     </row>
-    <row r="1285" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="1285" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1285" s="24" t="s">
         <v>296</v>
       </c>
@@ -42864,7 +42912,7 @@
         <v>1424</v>
       </c>
     </row>
-    <row r="1286" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="1286" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1286" s="24" t="s">
         <v>296</v>
       </c>
@@ -42891,13 +42939,13 @@
         <v>1802</v>
       </c>
     </row>
-    <row r="1287" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="1287" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1287" s="24" t="s">
         <v>374</v>
       </c>
       <c r="H1287" s="24"/>
     </row>
-    <row r="1288" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1288" spans="1:15" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1288" s="24" t="s">
         <v>273</v>
       </c>
@@ -42909,7 +42957,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="1289" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1289" spans="1:15" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1289" s="24" t="s">
         <v>268</v>
       </c>
@@ -42929,7 +42977,7 @@
         <v>1452</v>
       </c>
     </row>
-    <row r="1290" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1290" spans="1:15" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1290" s="24" t="s">
         <v>296</v>
       </c>
@@ -42955,7 +43003,7 @@
         <v>1454</v>
       </c>
     </row>
-    <row r="1291" spans="1:15" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1291" spans="1:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1291" s="24" t="s">
         <v>296</v>
       </c>
@@ -42981,7 +43029,7 @@
         <v>1456</v>
       </c>
     </row>
-    <row r="1292" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="1292" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1292" s="24" t="s">
         <v>296</v>
       </c>
@@ -43008,14 +43056,14 @@
         <v>1808</v>
       </c>
     </row>
-    <row r="1293" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="1293" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1293" s="24" t="s">
         <v>374</v>
       </c>
       <c r="H1293" s="24"/>
       <c r="I1293" s="36"/>
     </row>
-    <row r="1294" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="1294" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1294" s="24" t="s">
         <v>273</v>
       </c>
@@ -43027,7 +43075,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="1295" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1295" spans="1:15" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1295" s="24" t="s">
         <v>268</v>
       </c>
@@ -43047,7 +43095,7 @@
         <v>1465</v>
       </c>
     </row>
-    <row r="1296" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1296" spans="1:15" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1296" s="24" t="s">
         <v>296</v>
       </c>
@@ -43073,7 +43121,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="1297" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1297" spans="1:15" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1297" s="24" t="s">
         <v>296</v>
       </c>
@@ -43099,7 +43147,7 @@
         <v>1469</v>
       </c>
     </row>
-    <row r="1298" spans="1:15" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1298" spans="1:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1298" s="24" t="s">
         <v>296</v>
       </c>
@@ -43126,13 +43174,13 @@
         <v>1814</v>
       </c>
     </row>
-    <row r="1299" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="1299" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1299" s="24" t="s">
         <v>374</v>
       </c>
       <c r="H1299" s="24"/>
     </row>
-    <row r="1300" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="1300" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1300" s="24" t="s">
         <v>273</v>
       </c>
@@ -43145,7 +43193,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="1301" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="1301" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1301" s="24" t="s">
         <v>268</v>
       </c>
@@ -43165,7 +43213,7 @@
         <v>1478</v>
       </c>
     </row>
-    <row r="1302" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1302" spans="1:15" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1302" s="24" t="s">
         <v>296</v>
       </c>
@@ -43191,7 +43239,7 @@
         <v>1480</v>
       </c>
     </row>
-    <row r="1303" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1303" spans="1:15" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1303" s="24" t="s">
         <v>296</v>
       </c>
@@ -43217,7 +43265,7 @@
         <v>1482</v>
       </c>
     </row>
-    <row r="1304" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1304" spans="1:15" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1304" s="24" t="s">
         <v>296</v>
       </c>
@@ -43244,13 +43292,13 @@
         <v>1820</v>
       </c>
     </row>
-    <row r="1305" spans="1:15" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1305" spans="1:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1305" s="24" t="s">
         <v>374</v>
       </c>
       <c r="H1305" s="24"/>
     </row>
-    <row r="1306" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="1306" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1306" s="24" t="s">
         <v>273</v>
       </c>
@@ -43262,7 +43310,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="1307" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="1307" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1307" s="24" t="s">
         <v>268</v>
       </c>
@@ -43282,7 +43330,7 @@
         <v>1491</v>
       </c>
     </row>
-    <row r="1308" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="1308" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1308" s="24" t="s">
         <v>296</v>
       </c>
@@ -43308,7 +43356,7 @@
         <v>1493</v>
       </c>
     </row>
-    <row r="1309" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1309" spans="1:15" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1309" s="24" t="s">
         <v>296</v>
       </c>
@@ -43334,7 +43382,7 @@
         <v>1495</v>
       </c>
     </row>
-    <row r="1310" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1310" spans="1:15" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1310" s="24" t="s">
         <v>296</v>
       </c>
@@ -43361,13 +43409,13 @@
         <v>1826</v>
       </c>
     </row>
-    <row r="1311" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1311" spans="1:15" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1311" s="24" t="s">
         <v>374</v>
       </c>
       <c r="H1311" s="24"/>
     </row>
-    <row r="1312" spans="1:15" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1312" spans="1:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1312" s="24" t="s">
         <v>273</v>
       </c>
@@ -43379,7 +43427,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="1313" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="1313" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1313" s="24" t="s">
         <v>268</v>
       </c>
@@ -43399,7 +43447,7 @@
         <v>1452</v>
       </c>
     </row>
-    <row r="1314" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="1314" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1314" s="24" t="s">
         <v>296</v>
       </c>
@@ -43425,7 +43473,7 @@
         <v>1454</v>
       </c>
     </row>
-    <row r="1315" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="1315" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1315" s="24" t="s">
         <v>296</v>
       </c>
@@ -43451,7 +43499,7 @@
         <v>1456</v>
       </c>
     </row>
-    <row r="1316" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1316" spans="1:15" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1316" s="24" t="s">
         <v>296</v>
       </c>
@@ -43478,13 +43526,13 @@
         <v>1832</v>
       </c>
     </row>
-    <row r="1317" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1317" spans="1:15" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1317" s="24" t="s">
         <v>374</v>
       </c>
       <c r="H1317" s="24"/>
     </row>
-    <row r="1318" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1318" spans="1:15" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1318" s="24" t="s">
         <v>273</v>
       </c>
@@ -43496,7 +43544,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="1319" spans="1:15" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1319" spans="1:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1319" s="24" t="s">
         <v>268</v>
       </c>
@@ -43516,7 +43564,7 @@
         <v>1465</v>
       </c>
     </row>
-    <row r="1320" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="1320" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1320" s="24" t="s">
         <v>296</v>
       </c>
@@ -43542,7 +43590,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="1321" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="1321" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1321" s="24" t="s">
         <v>296</v>
       </c>
@@ -43568,7 +43616,7 @@
         <v>1469</v>
       </c>
     </row>
-    <row r="1322" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="1322" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1322" s="24" t="s">
         <v>296</v>
       </c>
@@ -43595,13 +43643,13 @@
         <v>1838</v>
       </c>
     </row>
-    <row r="1323" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1323" spans="1:15" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1323" s="24" t="s">
         <v>374</v>
       </c>
       <c r="H1323" s="24"/>
     </row>
-    <row r="1324" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1324" spans="1:15" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1324" s="24" t="s">
         <v>273</v>
       </c>
@@ -43613,7 +43661,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="1325" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1325" spans="1:15" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1325" s="24" t="s">
         <v>268</v>
       </c>
@@ -43633,7 +43681,7 @@
         <v>1478</v>
       </c>
     </row>
-    <row r="1326" spans="1:15" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1326" spans="1:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1326" s="24" t="s">
         <v>296</v>
       </c>
@@ -43659,7 +43707,7 @@
         <v>1480</v>
       </c>
     </row>
-    <row r="1327" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="1327" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1327" s="24" t="s">
         <v>296</v>
       </c>
@@ -43685,7 +43733,7 @@
         <v>1482</v>
       </c>
     </row>
-    <row r="1328" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="1328" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1328" s="24" t="s">
         <v>296</v>
       </c>
@@ -43712,13 +43760,13 @@
         <v>1844</v>
       </c>
     </row>
-    <row r="1329" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="1329" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1329" s="24" t="s">
         <v>374</v>
       </c>
       <c r="H1329" s="24"/>
     </row>
-    <row r="1330" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1330" spans="1:15" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1330" s="24" t="s">
         <v>273</v>
       </c>
@@ -43730,7 +43778,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="1331" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1331" spans="1:15" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1331" s="24" t="s">
         <v>268</v>
       </c>
@@ -43750,7 +43798,7 @@
         <v>1491</v>
       </c>
     </row>
-    <row r="1332" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1332" spans="1:15" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1332" s="24" t="s">
         <v>296</v>
       </c>
@@ -43776,7 +43824,7 @@
         <v>1493</v>
       </c>
     </row>
-    <row r="1333" spans="1:15" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1333" spans="1:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1333" s="24" t="s">
         <v>296</v>
       </c>
@@ -43802,7 +43850,7 @@
         <v>1495</v>
       </c>
     </row>
-    <row r="1334" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="1334" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1334" s="24" t="s">
         <v>296</v>
       </c>
@@ -43829,14 +43877,14 @@
         <v>1850</v>
       </c>
     </row>
-    <row r="1335" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="1335" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1335" s="24" t="s">
         <v>374</v>
       </c>
       <c r="H1335" s="24"/>
       <c r="I1335" s="36"/>
     </row>
-    <row r="1336" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="1336" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1336" s="24" t="s">
         <v>273</v>
       </c>
@@ -43848,7 +43896,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="1337" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1337" spans="1:15" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1337" s="24" t="s">
         <v>268</v>
       </c>
@@ -43868,7 +43916,7 @@
         <v>1452</v>
       </c>
     </row>
-    <row r="1338" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1338" spans="1:15" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1338" s="24" t="s">
         <v>296</v>
       </c>
@@ -43894,7 +43942,7 @@
         <v>1454</v>
       </c>
     </row>
-    <row r="1339" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1339" spans="1:15" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1339" s="24" t="s">
         <v>296</v>
       </c>
@@ -43920,7 +43968,7 @@
         <v>1456</v>
       </c>
     </row>
-    <row r="1340" spans="1:15" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1340" spans="1:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1340" s="24" t="s">
         <v>296</v>
       </c>
@@ -43947,13 +43995,13 @@
         <v>1856</v>
       </c>
     </row>
-    <row r="1341" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="1341" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1341" s="24" t="s">
         <v>374</v>
       </c>
       <c r="H1341" s="24"/>
     </row>
-    <row r="1342" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="1342" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1342" s="24" t="s">
         <v>273</v>
       </c>
@@ -43966,7 +44014,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="1343" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="1343" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1343" s="24" t="s">
         <v>268</v>
       </c>
@@ -43986,7 +44034,7 @@
         <v>1465</v>
       </c>
     </row>
-    <row r="1344" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1344" spans="1:15" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1344" s="24" t="s">
         <v>296</v>
       </c>
@@ -44012,7 +44060,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="1345" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1345" spans="1:15" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1345" s="24" t="s">
         <v>296</v>
       </c>
@@ -44038,7 +44086,7 @@
         <v>1469</v>
       </c>
     </row>
-    <row r="1346" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1346" spans="1:15" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1346" s="24" t="s">
         <v>296</v>
       </c>
@@ -44065,13 +44113,13 @@
         <v>1862</v>
       </c>
     </row>
-    <row r="1347" spans="1:15" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1347" spans="1:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1347" s="24" t="s">
         <v>374</v>
       </c>
       <c r="H1347" s="24"/>
     </row>
-    <row r="1348" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="1348" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1348" s="24" t="s">
         <v>273</v>
       </c>
@@ -44083,7 +44131,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="1349" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="1349" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1349" s="24" t="s">
         <v>268</v>
       </c>
@@ -44103,7 +44151,7 @@
         <v>1478</v>
       </c>
     </row>
-    <row r="1350" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="1350" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1350" s="24" t="s">
         <v>296</v>
       </c>
@@ -44129,7 +44177,7 @@
         <v>1480</v>
       </c>
     </row>
-    <row r="1351" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1351" spans="1:15" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1351" s="24" t="s">
         <v>296</v>
       </c>
@@ -44155,7 +44203,7 @@
         <v>1482</v>
       </c>
     </row>
-    <row r="1352" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1352" spans="1:15" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1352" s="24" t="s">
         <v>296</v>
       </c>
@@ -44182,13 +44230,13 @@
         <v>1868</v>
       </c>
     </row>
-    <row r="1353" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1353" spans="1:15" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1353" s="24" t="s">
         <v>374</v>
       </c>
       <c r="H1353" s="24"/>
     </row>
-    <row r="1354" spans="1:15" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1354" spans="1:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1354" s="24" t="s">
         <v>273</v>
       </c>
@@ -44200,7 +44248,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="1355" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="1355" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1355" s="24" t="s">
         <v>268</v>
       </c>
@@ -44220,7 +44268,7 @@
         <v>1491</v>
       </c>
     </row>
-    <row r="1356" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="1356" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1356" s="24" t="s">
         <v>296</v>
       </c>
@@ -44246,7 +44294,7 @@
         <v>1493</v>
       </c>
     </row>
-    <row r="1357" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="1357" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1357" s="24" t="s">
         <v>296</v>
       </c>
@@ -44272,7 +44320,7 @@
         <v>1495</v>
       </c>
     </row>
-    <row r="1358" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1358" spans="1:15" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1358" s="24" t="s">
         <v>296</v>
       </c>
@@ -44299,27 +44347,30 @@
         <v>1874</v>
       </c>
     </row>
-    <row r="1359" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1359" spans="1:15" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1359" s="24" t="s">
         <v>374</v>
       </c>
       <c r="H1359" s="24"/>
     </row>
-    <row r="1360" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1360" spans="1:15" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1360" s="24" t="s">
         <v>273</v>
+      </c>
+      <c r="B1360" s="24" t="s">
+        <v>4242</v>
       </c>
       <c r="H1360" s="24"/>
       <c r="M1360" s="24" t="s">
         <v>398</v>
       </c>
     </row>
-    <row r="1361" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1361" spans="1:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1361" s="24" t="s">
         <v>268</v>
       </c>
       <c r="B1361" s="24" t="s">
-        <v>1409</v>
+        <v>4243</v>
       </c>
       <c r="H1361" s="24" t="s">
         <v>1573</v>
@@ -44334,7 +44385,7 @@
         <v>1574</v>
       </c>
     </row>
-    <row r="1362" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="1362" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1362" s="24" t="s">
         <v>296</v>
       </c>
@@ -44360,7 +44411,7 @@
         <v>1876</v>
       </c>
     </row>
-    <row r="1363" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="1363" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1363" s="24" t="s">
         <v>296</v>
       </c>
@@ -44386,7 +44437,7 @@
         <v>1878</v>
       </c>
     </row>
-    <row r="1364" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="1364" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1364" s="24" t="s">
         <v>296</v>
       </c>
@@ -44412,7 +44463,7 @@
         <v>1880</v>
       </c>
     </row>
-    <row r="1365" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1365" spans="1:18" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1365" s="24" t="s">
         <v>374</v>
       </c>
@@ -44479,10 +44530,10 @@
         <v>382</v>
       </c>
       <c r="B1369" s="24" t="s">
-        <v>1408</v>
+        <v>4245</v>
       </c>
       <c r="H1369" s="24" t="s">
-        <v>384</v>
+        <v>4244</v>
       </c>
       <c r="I1369" s="33" t="s">
         <v>1882</v>
@@ -44502,7 +44553,7 @@
         <v>268</v>
       </c>
       <c r="B1370" s="24" t="s">
-        <v>1409</v>
+        <v>4245</v>
       </c>
       <c r="H1370" s="24" t="s">
         <v>1410</v>
@@ -44522,7 +44573,7 @@
         <v>268</v>
       </c>
       <c r="B1371" s="24" t="s">
-        <v>1409</v>
+        <v>4245</v>
       </c>
       <c r="H1371" s="24" t="s">
         <v>388</v>
@@ -44542,7 +44593,7 @@
         <v>268</v>
       </c>
       <c r="B1372" s="24" t="s">
-        <v>1409</v>
+        <v>4245</v>
       </c>
       <c r="H1372" s="24" t="s">
         <v>391</v>
@@ -44562,7 +44613,7 @@
         <v>268</v>
       </c>
       <c r="B1373" s="24" t="s">
-        <v>1409</v>
+        <v>4245</v>
       </c>
       <c r="H1373" s="24" t="s">
         <v>394</v>
@@ -46341,6 +46392,9 @@
       <c r="A1464" s="24" t="s">
         <v>273</v>
       </c>
+      <c r="B1464" s="24" t="s">
+        <v>4246</v>
+      </c>
       <c r="H1464" s="24"/>
       <c r="M1464" s="24" t="s">
         <v>398</v>
@@ -46351,7 +46405,7 @@
         <v>268</v>
       </c>
       <c r="B1465" s="24" t="s">
-        <v>1409</v>
+        <v>4247</v>
       </c>
       <c r="H1465" s="24" t="s">
         <v>1573</v>
@@ -46511,10 +46565,10 @@
         <v>382</v>
       </c>
       <c r="B1473" s="24" t="s">
-        <v>1408</v>
+        <v>4249</v>
       </c>
       <c r="H1473" s="24" t="s">
-        <v>384</v>
+        <v>4248</v>
       </c>
       <c r="I1473" s="33" t="s">
         <v>1980</v>
@@ -46534,7 +46588,7 @@
         <v>268</v>
       </c>
       <c r="B1474" s="24" t="s">
-        <v>1409</v>
+        <v>4249</v>
       </c>
       <c r="H1474" s="24" t="s">
         <v>1410</v>
@@ -46554,7 +46608,7 @@
         <v>268</v>
       </c>
       <c r="B1475" s="24" t="s">
-        <v>1409</v>
+        <v>4249</v>
       </c>
       <c r="H1475" s="24" t="s">
         <v>388</v>
@@ -46574,7 +46628,7 @@
         <v>268</v>
       </c>
       <c r="B1476" s="24" t="s">
-        <v>1409</v>
+        <v>4249</v>
       </c>
       <c r="H1476" s="24" t="s">
         <v>391</v>
@@ -46594,7 +46648,7 @@
         <v>268</v>
       </c>
       <c r="B1477" s="24" t="s">
-        <v>1409</v>
+        <v>4249</v>
       </c>
       <c r="H1477" s="24" t="s">
         <v>394</v>
@@ -48373,6 +48427,9 @@
       <c r="A1568" s="24" t="s">
         <v>273</v>
       </c>
+      <c r="B1568" s="24" t="s">
+        <v>4250</v>
+      </c>
       <c r="H1568" s="24"/>
       <c r="M1568" s="24" t="s">
         <v>398</v>
@@ -48383,7 +48440,7 @@
         <v>268</v>
       </c>
       <c r="B1569" s="24" t="s">
-        <v>1409</v>
+        <v>4251</v>
       </c>
       <c r="H1569" s="24" t="s">
         <v>1573</v>
@@ -48543,10 +48600,10 @@
         <v>382</v>
       </c>
       <c r="B1577" s="24" t="s">
-        <v>1408</v>
+        <v>4253</v>
       </c>
       <c r="H1577" s="24" t="s">
-        <v>384</v>
+        <v>4252</v>
       </c>
       <c r="I1577" s="33" t="s">
         <v>2078</v>
@@ -48566,7 +48623,7 @@
         <v>268</v>
       </c>
       <c r="B1578" s="24" t="s">
-        <v>1409</v>
+        <v>4253</v>
       </c>
       <c r="H1578" s="24" t="s">
         <v>1410</v>
@@ -48586,7 +48643,7 @@
         <v>268</v>
       </c>
       <c r="B1579" s="24" t="s">
-        <v>1409</v>
+        <v>4253</v>
       </c>
       <c r="H1579" s="24" t="s">
         <v>388</v>
@@ -48606,7 +48663,7 @@
         <v>268</v>
       </c>
       <c r="B1580" s="24" t="s">
-        <v>1409</v>
+        <v>4253</v>
       </c>
       <c r="H1580" s="24" t="s">
         <v>391</v>
@@ -48626,7 +48683,7 @@
         <v>268</v>
       </c>
       <c r="B1581" s="24" t="s">
-        <v>1409</v>
+        <v>4253</v>
       </c>
       <c r="H1581" s="24" t="s">
         <v>394</v>
@@ -50405,6 +50462,9 @@
       <c r="A1672" s="24" t="s">
         <v>273</v>
       </c>
+      <c r="B1672" s="24" t="s">
+        <v>4254</v>
+      </c>
       <c r="H1672" s="24"/>
       <c r="M1672" s="24" t="s">
         <v>398</v>
@@ -50415,7 +50475,7 @@
         <v>268</v>
       </c>
       <c r="B1673" s="24" t="s">
-        <v>1409</v>
+        <v>4255</v>
       </c>
       <c r="C1673" s="24"/>
       <c r="D1673" s="24"/>

--- a/s2.xlsx
+++ b/s2.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17519" uniqueCount="4220">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17519" uniqueCount="4216">
   <si>
     <t>list_name</t>
   </si>
@@ -10676,21 +10676,6 @@
     <t>حسب التخصص</t>
   </si>
   <si>
-    <t>form6_10a23_note0</t>
-  </si>
-  <si>
-    <t>form6_10a23_note1</t>
-  </si>
-  <si>
-    <t>form6_10a23_note2</t>
-  </si>
-  <si>
-    <t>form6_10a23_note3</t>
-  </si>
-  <si>
-    <t>form6_10a23_note4</t>
-  </si>
-  <si>
     <t>form6_10a23_1</t>
   </si>
   <si>
@@ -12684,6 +12669,9 @@
   </si>
   <si>
     <t>form6_9a_note</t>
+  </si>
+  <si>
+    <t>form6_10a23_note</t>
   </si>
 </sst>
 </file>
@@ -18329,7 +18317,7 @@
         <v>268</v>
       </c>
       <c r="B72" s="24" t="s">
-        <v>4164</v>
+        <v>4159</v>
       </c>
       <c r="F72" s="37"/>
       <c r="H72" s="24" t="s">
@@ -19160,7 +19148,7 @@
         <v>268</v>
       </c>
       <c r="B114" s="24" t="s">
-        <v>4165</v>
+        <v>4160</v>
       </c>
       <c r="H114" s="24" t="s">
         <v>394</v>
@@ -19990,7 +19978,7 @@
         <v>268</v>
       </c>
       <c r="B156" s="24" t="s">
-        <v>4166</v>
+        <v>4161</v>
       </c>
       <c r="H156" s="24" t="s">
         <v>394</v>
@@ -20821,7 +20809,7 @@
         <v>268</v>
       </c>
       <c r="B198" s="24" t="s">
-        <v>4167</v>
+        <v>4162</v>
       </c>
       <c r="H198" s="24" t="s">
         <v>394</v>
@@ -21690,7 +21678,7 @@
         <v>268</v>
       </c>
       <c r="B240" s="24" t="s">
-        <v>4168</v>
+        <v>4163</v>
       </c>
       <c r="H240" s="24" t="s">
         <v>394</v>
@@ -22639,7 +22627,7 @@
         <v>268</v>
       </c>
       <c r="B285" s="24" t="s">
-        <v>4169</v>
+        <v>4164</v>
       </c>
       <c r="H285" s="24" t="s">
         <v>394</v>
@@ -23472,7 +23460,7 @@
         <v>268</v>
       </c>
       <c r="B327" s="24" t="s">
-        <v>4170</v>
+        <v>4165</v>
       </c>
       <c r="H327" s="24" t="s">
         <v>394</v>
@@ -24306,7 +24294,7 @@
         <v>268</v>
       </c>
       <c r="B369" s="24" t="s">
-        <v>4171</v>
+        <v>4166</v>
       </c>
       <c r="H369" s="24" t="s">
         <v>394</v>
@@ -26274,7 +26262,7 @@
         <v>268</v>
       </c>
       <c r="B465" s="24" t="s">
-        <v>4172</v>
+        <v>4167</v>
       </c>
       <c r="H465" s="24" t="s">
         <v>394</v>
@@ -27170,7 +27158,7 @@
         <v>268</v>
       </c>
       <c r="B507" s="24" t="s">
-        <v>4173</v>
+        <v>4168</v>
       </c>
       <c r="H507" s="24" t="s">
         <v>394</v>
@@ -28065,7 +28053,7 @@
         <v>268</v>
       </c>
       <c r="B549" s="24" t="s">
-        <v>4174</v>
+        <v>4169</v>
       </c>
       <c r="H549" s="24" t="s">
         <v>394</v>
@@ -28960,7 +28948,7 @@
         <v>268</v>
       </c>
       <c r="B591" s="24" t="s">
-        <v>4175</v>
+        <v>4170</v>
       </c>
       <c r="H591" s="24" t="s">
         <v>394</v>
@@ -29793,7 +29781,7 @@
         <v>268</v>
       </c>
       <c r="B633" s="24" t="s">
-        <v>4176</v>
+        <v>4171</v>
       </c>
       <c r="H633" s="24" t="s">
         <v>394</v>
@@ -30626,7 +30614,7 @@
         <v>268</v>
       </c>
       <c r="B675" s="24" t="s">
-        <v>4177</v>
+        <v>4172</v>
       </c>
       <c r="H675" s="24" t="s">
         <v>394</v>
@@ -31459,7 +31447,7 @@
         <v>268</v>
       </c>
       <c r="B717" s="24" t="s">
-        <v>4178</v>
+        <v>4173</v>
       </c>
       <c r="H717" s="24" t="s">
         <v>394</v>
@@ -32292,7 +32280,7 @@
         <v>268</v>
       </c>
       <c r="B759" s="24" t="s">
-        <v>4179</v>
+        <v>4174</v>
       </c>
       <c r="H759" s="24" t="s">
         <v>394</v>
@@ -33125,7 +33113,7 @@
         <v>268</v>
       </c>
       <c r="B801" s="24" t="s">
-        <v>4180</v>
+        <v>4175</v>
       </c>
       <c r="H801" s="24" t="s">
         <v>394</v>
@@ -33958,7 +33946,7 @@
         <v>268</v>
       </c>
       <c r="B843" s="24" t="s">
-        <v>4181</v>
+        <v>4176</v>
       </c>
       <c r="H843" s="24" t="s">
         <v>394</v>
@@ -34791,7 +34779,7 @@
         <v>268</v>
       </c>
       <c r="B885" s="24" t="s">
-        <v>4182</v>
+        <v>4177</v>
       </c>
       <c r="H885" s="24" t="s">
         <v>394</v>
@@ -35637,7 +35625,7 @@
         <v>268</v>
       </c>
       <c r="B927" s="24" t="s">
-        <v>4183</v>
+        <v>4178</v>
       </c>
       <c r="H927" s="24" t="s">
         <v>394</v>
@@ -35851,10 +35839,10 @@
         <v>382</v>
       </c>
       <c r="B938" s="24" t="s">
-        <v>4185</v>
+        <v>4180</v>
       </c>
       <c r="H938" s="24" t="s">
-        <v>4184</v>
+        <v>4179</v>
       </c>
       <c r="I938" s="33" t="s">
         <v>1407</v>
@@ -35874,7 +35862,7 @@
         <v>268</v>
       </c>
       <c r="B939" s="24" t="s">
-        <v>4185</v>
+        <v>4180</v>
       </c>
       <c r="H939" s="24" t="s">
         <v>1410</v>
@@ -35894,7 +35882,7 @@
         <v>268</v>
       </c>
       <c r="B940" s="24" t="s">
-        <v>4185</v>
+        <v>4180</v>
       </c>
       <c r="H940" s="24" t="s">
         <v>388</v>
@@ -35914,7 +35902,7 @@
         <v>268</v>
       </c>
       <c r="B941" s="24" t="s">
-        <v>4185</v>
+        <v>4180</v>
       </c>
       <c r="H941" s="24" t="s">
         <v>391</v>
@@ -35934,7 +35922,7 @@
         <v>268</v>
       </c>
       <c r="B942" s="24" t="s">
-        <v>4185</v>
+        <v>4180</v>
       </c>
       <c r="H942" s="24" t="s">
         <v>1414</v>
@@ -35954,7 +35942,7 @@
         <v>268</v>
       </c>
       <c r="B943" s="24" t="s">
-        <v>4185</v>
+        <v>4180</v>
       </c>
       <c r="H943" s="24" t="s">
         <v>394</v>
@@ -38317,10 +38305,10 @@
         <v>382</v>
       </c>
       <c r="B1057" s="24" t="s">
-        <v>4188</v>
+        <v>4183</v>
       </c>
       <c r="H1057" s="24" t="s">
-        <v>4187</v>
+        <v>4182</v>
       </c>
       <c r="I1057" s="33" t="s">
         <v>1587</v>
@@ -38340,7 +38328,7 @@
         <v>268</v>
       </c>
       <c r="B1058" s="24" t="s">
-        <v>4188</v>
+        <v>4183</v>
       </c>
       <c r="H1058" s="24" t="s">
         <v>1410</v>
@@ -38360,7 +38348,7 @@
         <v>268</v>
       </c>
       <c r="B1059" s="24" t="s">
-        <v>4188</v>
+        <v>4183</v>
       </c>
       <c r="H1059" s="24" t="s">
         <v>388</v>
@@ -38380,7 +38368,7 @@
         <v>268</v>
       </c>
       <c r="B1060" s="24" t="s">
-        <v>4188</v>
+        <v>4183</v>
       </c>
       <c r="H1060" s="24" t="s">
         <v>391</v>
@@ -38400,7 +38388,7 @@
         <v>268</v>
       </c>
       <c r="B1061" s="24" t="s">
-        <v>4188</v>
+        <v>4183</v>
       </c>
       <c r="H1061" s="24" t="s">
         <v>394</v>
@@ -40185,7 +40173,7 @@
         <v>273</v>
       </c>
       <c r="B1152" s="24" t="s">
-        <v>4189</v>
+        <v>4184</v>
       </c>
       <c r="H1152" s="24"/>
       <c r="M1152" s="24" t="s">
@@ -40197,7 +40185,7 @@
         <v>268</v>
       </c>
       <c r="B1153" s="24" t="s">
-        <v>4186</v>
+        <v>4181</v>
       </c>
       <c r="H1153" s="24" t="s">
         <v>1573</v>
@@ -40335,10 +40323,10 @@
       <c r="F1160" s="33"/>
       <c r="G1160" s="33"/>
       <c r="H1160" s="33" t="s">
-        <v>4192</v>
+        <v>4187</v>
       </c>
       <c r="I1160" s="33" t="s">
-        <v>4192</v>
+        <v>4187</v>
       </c>
       <c r="J1160" s="33"/>
       <c r="K1160" s="33"/>
@@ -40357,13 +40345,13 @@
         <v>382</v>
       </c>
       <c r="B1161" s="24" t="s">
-        <v>4190</v>
+        <v>4185</v>
       </c>
       <c r="H1161" s="24" t="s">
-        <v>4193</v>
+        <v>4188</v>
       </c>
       <c r="I1161" s="33" t="s">
-        <v>4192</v>
+        <v>4187</v>
       </c>
       <c r="J1161" s="33"/>
       <c r="K1161" s="33"/>
@@ -40380,7 +40368,7 @@
         <v>268</v>
       </c>
       <c r="B1162" s="24" t="s">
-        <v>4190</v>
+        <v>4185</v>
       </c>
       <c r="H1162" s="24" t="s">
         <v>1410</v>
@@ -40400,7 +40388,7 @@
         <v>268</v>
       </c>
       <c r="B1163" s="24" t="s">
-        <v>4190</v>
+        <v>4185</v>
       </c>
       <c r="H1163" s="24" t="s">
         <v>388</v>
@@ -40420,7 +40408,7 @@
         <v>268</v>
       </c>
       <c r="B1164" s="24" t="s">
-        <v>4190</v>
+        <v>4185</v>
       </c>
       <c r="H1164" s="24" t="s">
         <v>391</v>
@@ -40440,7 +40428,7 @@
         <v>268</v>
       </c>
       <c r="B1165" s="24" t="s">
-        <v>4190</v>
+        <v>4185</v>
       </c>
       <c r="H1165" s="24" t="s">
         <v>394</v>
@@ -42215,7 +42203,7 @@
         <v>273</v>
       </c>
       <c r="B1256" s="24" t="s">
-        <v>4191</v>
+        <v>4186</v>
       </c>
       <c r="H1256" s="24"/>
       <c r="M1256" s="24" t="s">
@@ -42227,7 +42215,7 @@
         <v>268</v>
       </c>
       <c r="B1257" s="24" t="s">
-        <v>4194</v>
+        <v>4189</v>
       </c>
       <c r="H1257" s="24" t="s">
         <v>1573</v>
@@ -42387,10 +42375,10 @@
         <v>382</v>
       </c>
       <c r="B1265" s="24" t="s">
-        <v>4196</v>
+        <v>4191</v>
       </c>
       <c r="H1265" s="24" t="s">
-        <v>4195</v>
+        <v>4190</v>
       </c>
       <c r="I1265" s="33" t="s">
         <v>1784</v>
@@ -42410,7 +42398,7 @@
         <v>268</v>
       </c>
       <c r="B1266" s="24" t="s">
-        <v>4196</v>
+        <v>4191</v>
       </c>
       <c r="H1266" s="24" t="s">
         <v>1410</v>
@@ -42430,7 +42418,7 @@
         <v>268</v>
       </c>
       <c r="B1267" s="24" t="s">
-        <v>4196</v>
+        <v>4191</v>
       </c>
       <c r="H1267" s="24" t="s">
         <v>388</v>
@@ -42450,7 +42438,7 @@
         <v>268</v>
       </c>
       <c r="B1268" s="24" t="s">
-        <v>4196</v>
+        <v>4191</v>
       </c>
       <c r="H1268" s="24" t="s">
         <v>391</v>
@@ -42470,7 +42458,7 @@
         <v>268</v>
       </c>
       <c r="B1269" s="24" t="s">
-        <v>4196</v>
+        <v>4191</v>
       </c>
       <c r="H1269" s="24" t="s">
         <v>394</v>
@@ -44250,7 +44238,7 @@
         <v>273</v>
       </c>
       <c r="B1360" s="24" t="s">
-        <v>4197</v>
+        <v>4192</v>
       </c>
       <c r="H1360" s="24"/>
       <c r="M1360" s="24" t="s">
@@ -44262,7 +44250,7 @@
         <v>268</v>
       </c>
       <c r="B1361" s="24" t="s">
-        <v>4198</v>
+        <v>4193</v>
       </c>
       <c r="H1361" s="24" t="s">
         <v>1573</v>
@@ -44422,10 +44410,10 @@
         <v>382</v>
       </c>
       <c r="B1369" s="24" t="s">
-        <v>4200</v>
+        <v>4195</v>
       </c>
       <c r="H1369" s="24" t="s">
-        <v>4199</v>
+        <v>4194</v>
       </c>
       <c r="I1369" s="33" t="s">
         <v>1882</v>
@@ -44445,7 +44433,7 @@
         <v>268</v>
       </c>
       <c r="B1370" s="24" t="s">
-        <v>4200</v>
+        <v>4195</v>
       </c>
       <c r="H1370" s="24" t="s">
         <v>1410</v>
@@ -44465,7 +44453,7 @@
         <v>268</v>
       </c>
       <c r="B1371" s="24" t="s">
-        <v>4200</v>
+        <v>4195</v>
       </c>
       <c r="H1371" s="24" t="s">
         <v>388</v>
@@ -44485,7 +44473,7 @@
         <v>268</v>
       </c>
       <c r="B1372" s="24" t="s">
-        <v>4200</v>
+        <v>4195</v>
       </c>
       <c r="H1372" s="24" t="s">
         <v>391</v>
@@ -44505,7 +44493,7 @@
         <v>268</v>
       </c>
       <c r="B1373" s="24" t="s">
-        <v>4200</v>
+        <v>4195</v>
       </c>
       <c r="H1373" s="24" t="s">
         <v>394</v>
@@ -46285,7 +46273,7 @@
         <v>273</v>
       </c>
       <c r="B1464" s="24" t="s">
-        <v>4201</v>
+        <v>4196</v>
       </c>
       <c r="H1464" s="24"/>
       <c r="M1464" s="24" t="s">
@@ -46297,7 +46285,7 @@
         <v>268</v>
       </c>
       <c r="B1465" s="24" t="s">
-        <v>4202</v>
+        <v>4197</v>
       </c>
       <c r="H1465" s="24" t="s">
         <v>1573</v>
@@ -46457,10 +46445,10 @@
         <v>382</v>
       </c>
       <c r="B1473" s="24" t="s">
-        <v>4204</v>
+        <v>4199</v>
       </c>
       <c r="H1473" s="24" t="s">
-        <v>4203</v>
+        <v>4198</v>
       </c>
       <c r="I1473" s="33" t="s">
         <v>1980</v>
@@ -46480,7 +46468,7 @@
         <v>268</v>
       </c>
       <c r="B1474" s="24" t="s">
-        <v>4204</v>
+        <v>4199</v>
       </c>
       <c r="H1474" s="24" t="s">
         <v>1410</v>
@@ -46500,7 +46488,7 @@
         <v>268</v>
       </c>
       <c r="B1475" s="24" t="s">
-        <v>4204</v>
+        <v>4199</v>
       </c>
       <c r="H1475" s="24" t="s">
         <v>388</v>
@@ -46520,7 +46508,7 @@
         <v>268</v>
       </c>
       <c r="B1476" s="24" t="s">
-        <v>4204</v>
+        <v>4199</v>
       </c>
       <c r="H1476" s="24" t="s">
         <v>391</v>
@@ -46540,7 +46528,7 @@
         <v>268</v>
       </c>
       <c r="B1477" s="24" t="s">
-        <v>4204</v>
+        <v>4199</v>
       </c>
       <c r="H1477" s="24" t="s">
         <v>394</v>
@@ -48320,7 +48308,7 @@
         <v>273</v>
       </c>
       <c r="B1568" s="24" t="s">
-        <v>4205</v>
+        <v>4200</v>
       </c>
       <c r="H1568" s="24"/>
       <c r="M1568" s="24" t="s">
@@ -48332,7 +48320,7 @@
         <v>268</v>
       </c>
       <c r="B1569" s="24" t="s">
-        <v>4206</v>
+        <v>4201</v>
       </c>
       <c r="H1569" s="24" t="s">
         <v>1573</v>
@@ -48492,10 +48480,10 @@
         <v>382</v>
       </c>
       <c r="B1577" s="24" t="s">
-        <v>4208</v>
+        <v>4203</v>
       </c>
       <c r="H1577" s="24" t="s">
-        <v>4207</v>
+        <v>4202</v>
       </c>
       <c r="I1577" s="33" t="s">
         <v>2078</v>
@@ -48515,7 +48503,7 @@
         <v>268</v>
       </c>
       <c r="B1578" s="24" t="s">
-        <v>4208</v>
+        <v>4203</v>
       </c>
       <c r="H1578" s="24" t="s">
         <v>1410</v>
@@ -48535,7 +48523,7 @@
         <v>268</v>
       </c>
       <c r="B1579" s="24" t="s">
-        <v>4208</v>
+        <v>4203</v>
       </c>
       <c r="H1579" s="24" t="s">
         <v>388</v>
@@ -48555,7 +48543,7 @@
         <v>268</v>
       </c>
       <c r="B1580" s="24" t="s">
-        <v>4208</v>
+        <v>4203</v>
       </c>
       <c r="H1580" s="24" t="s">
         <v>391</v>
@@ -48575,7 +48563,7 @@
         <v>268</v>
       </c>
       <c r="B1581" s="24" t="s">
-        <v>4208</v>
+        <v>4203</v>
       </c>
       <c r="H1581" s="24" t="s">
         <v>394</v>
@@ -50355,7 +50343,7 @@
         <v>273</v>
       </c>
       <c r="B1672" s="24" t="s">
-        <v>4209</v>
+        <v>4204</v>
       </c>
       <c r="H1672" s="24"/>
       <c r="M1672" s="24" t="s">
@@ -50367,7 +50355,7 @@
         <v>268</v>
       </c>
       <c r="B1673" s="24" t="s">
-        <v>4210</v>
+        <v>4205</v>
       </c>
       <c r="C1673" s="24"/>
       <c r="D1673" s="24"/>
@@ -50673,7 +50661,7 @@
         <v>382</v>
       </c>
       <c r="B1685" s="28" t="s">
-        <v>4211</v>
+        <v>4206</v>
       </c>
       <c r="D1685" s="24"/>
       <c r="E1685" s="24"/>
@@ -50700,7 +50688,7 @@
         <v>268</v>
       </c>
       <c r="B1686" s="28" t="s">
-        <v>4211</v>
+        <v>4206</v>
       </c>
       <c r="H1686" s="28" t="s">
         <v>2206</v>
@@ -50717,7 +50705,7 @@
         <v>268</v>
       </c>
       <c r="B1687" s="28" t="s">
-        <v>4211</v>
+        <v>4206</v>
       </c>
       <c r="H1687" s="28" t="s">
         <v>2208</v>
@@ -50734,7 +50722,7 @@
         <v>268</v>
       </c>
       <c r="B1688" s="28" t="s">
-        <v>4211</v>
+        <v>4206</v>
       </c>
       <c r="H1688" s="28" t="s">
         <v>2210</v>
@@ -50751,7 +50739,7 @@
         <v>268</v>
       </c>
       <c r="B1689" s="28" t="s">
-        <v>4211</v>
+        <v>4206</v>
       </c>
       <c r="H1689" s="28" t="s">
         <v>2212</v>
@@ -51305,7 +51293,7 @@
         <v>382</v>
       </c>
       <c r="B1714" s="28" t="s">
-        <v>4212</v>
+        <v>4207</v>
       </c>
       <c r="D1714" s="24"/>
       <c r="E1714" s="24"/>
@@ -51332,7 +51320,7 @@
         <v>268</v>
       </c>
       <c r="B1715" s="28" t="s">
-        <v>4212</v>
+        <v>4207</v>
       </c>
       <c r="H1715" s="28" t="s">
         <v>2206</v>
@@ -51350,7 +51338,7 @@
         <v>268</v>
       </c>
       <c r="B1716" s="28" t="s">
-        <v>4212</v>
+        <v>4207</v>
       </c>
       <c r="H1716" s="28" t="s">
         <v>2208</v>
@@ -51368,7 +51356,7 @@
         <v>268</v>
       </c>
       <c r="B1717" s="28" t="s">
-        <v>4212</v>
+        <v>4207</v>
       </c>
       <c r="H1717" s="28" t="s">
         <v>2210</v>
@@ -51386,7 +51374,7 @@
         <v>268</v>
       </c>
       <c r="B1718" s="28" t="s">
-        <v>4212</v>
+        <v>4207</v>
       </c>
       <c r="H1718" s="28" t="s">
         <v>2212</v>
@@ -52314,7 +52302,7 @@
         <v>382</v>
       </c>
       <c r="B1763" s="28" t="s">
-        <v>4213</v>
+        <v>4208</v>
       </c>
       <c r="D1763" s="24"/>
       <c r="E1763" s="24"/>
@@ -52341,7 +52329,7 @@
         <v>268</v>
       </c>
       <c r="B1764" s="28" t="s">
-        <v>4213</v>
+        <v>4208</v>
       </c>
       <c r="C1764" s="28"/>
       <c r="D1764" s="28"/>
@@ -52371,7 +52359,7 @@
         <v>268</v>
       </c>
       <c r="B1765" s="28" t="s">
-        <v>4213</v>
+        <v>4208</v>
       </c>
       <c r="C1765" s="28"/>
       <c r="D1765" s="28"/>
@@ -52401,7 +52389,7 @@
         <v>268</v>
       </c>
       <c r="B1766" s="28" t="s">
-        <v>4213</v>
+        <v>4208</v>
       </c>
       <c r="C1766" s="28"/>
       <c r="D1766" s="28"/>
@@ -52431,7 +52419,7 @@
         <v>268</v>
       </c>
       <c r="B1767" s="28" t="s">
-        <v>4213</v>
+        <v>4208</v>
       </c>
       <c r="C1767" s="28"/>
       <c r="D1767" s="28"/>
@@ -52884,7 +52872,7 @@
         <v>382</v>
       </c>
       <c r="B1788" s="28" t="s">
-        <v>4214</v>
+        <v>4209</v>
       </c>
       <c r="D1788" s="24"/>
       <c r="E1788" s="24"/>
@@ -52911,7 +52899,7 @@
         <v>268</v>
       </c>
       <c r="B1789" s="28" t="s">
-        <v>4214</v>
+        <v>4209</v>
       </c>
       <c r="H1789" s="28" t="s">
         <v>2206</v>
@@ -52929,7 +52917,7 @@
         <v>268</v>
       </c>
       <c r="B1790" s="28" t="s">
-        <v>4214</v>
+        <v>4209</v>
       </c>
       <c r="H1790" s="28" t="s">
         <v>2208</v>
@@ -52947,7 +52935,7 @@
         <v>268</v>
       </c>
       <c r="B1791" s="28" t="s">
-        <v>4214</v>
+        <v>4209</v>
       </c>
       <c r="H1791" s="28" t="s">
         <v>2210</v>
@@ -52965,7 +52953,7 @@
         <v>268</v>
       </c>
       <c r="B1792" s="28" t="s">
-        <v>4214</v>
+        <v>4209</v>
       </c>
       <c r="H1792" s="28" t="s">
         <v>2212</v>
@@ -53883,7 +53871,7 @@
         <v>382</v>
       </c>
       <c r="B1837" s="28" t="s">
-        <v>4215</v>
+        <v>4210</v>
       </c>
       <c r="D1837" s="24"/>
       <c r="E1837" s="24"/>
@@ -53908,7 +53896,7 @@
         <v>268</v>
       </c>
       <c r="B1838" s="28" t="s">
-        <v>4215</v>
+        <v>4210</v>
       </c>
       <c r="H1838" s="28" t="s">
         <v>2206</v>
@@ -53925,7 +53913,7 @@
         <v>268</v>
       </c>
       <c r="B1839" s="28" t="s">
-        <v>4215</v>
+        <v>4210</v>
       </c>
       <c r="H1839" s="28" t="s">
         <v>2208</v>
@@ -53942,7 +53930,7 @@
         <v>268</v>
       </c>
       <c r="B1840" s="28" t="s">
-        <v>4215</v>
+        <v>4210</v>
       </c>
       <c r="H1840" s="28" t="s">
         <v>2210</v>
@@ -53959,7 +53947,7 @@
         <v>268</v>
       </c>
       <c r="B1841" s="28" t="s">
-        <v>4215</v>
+        <v>4210</v>
       </c>
       <c r="H1841" s="28" t="s">
         <v>2212</v>
@@ -54507,7 +54495,7 @@
         <v>382</v>
       </c>
       <c r="B1866" s="28" t="s">
-        <v>4216</v>
+        <v>4211</v>
       </c>
       <c r="D1866" s="24"/>
       <c r="E1866" s="24"/>
@@ -54532,7 +54520,7 @@
         <v>268</v>
       </c>
       <c r="B1867" s="28" t="s">
-        <v>4216</v>
+        <v>4211</v>
       </c>
       <c r="H1867" s="28" t="s">
         <v>2206</v>
@@ -54549,7 +54537,7 @@
         <v>268</v>
       </c>
       <c r="B1868" s="28" t="s">
-        <v>4216</v>
+        <v>4211</v>
       </c>
       <c r="H1868" s="28" t="s">
         <v>2208</v>
@@ -54566,7 +54554,7 @@
         <v>268</v>
       </c>
       <c r="B1869" s="28" t="s">
-        <v>4216</v>
+        <v>4211</v>
       </c>
       <c r="H1869" s="28" t="s">
         <v>2210</v>
@@ -54583,7 +54571,7 @@
         <v>268</v>
       </c>
       <c r="B1870" s="28" t="s">
-        <v>4216</v>
+        <v>4211</v>
       </c>
       <c r="H1870" s="28" t="s">
         <v>2212</v>
@@ -55177,7 +55165,7 @@
         <v>382</v>
       </c>
       <c r="B1899" s="28" t="s">
-        <v>4217</v>
+        <v>4212</v>
       </c>
       <c r="C1899" s="28"/>
       <c r="H1899" s="24"/>
@@ -55190,7 +55178,7 @@
         <v>268</v>
       </c>
       <c r="B1900" s="28" t="s">
-        <v>4217</v>
+        <v>4212</v>
       </c>
       <c r="H1900" s="28" t="s">
         <v>2206</v>
@@ -55207,7 +55195,7 @@
         <v>268</v>
       </c>
       <c r="B1901" s="28" t="s">
-        <v>4217</v>
+        <v>4212</v>
       </c>
       <c r="H1901" s="28" t="s">
         <v>2208</v>
@@ -55224,7 +55212,7 @@
         <v>268</v>
       </c>
       <c r="B1902" s="28" t="s">
-        <v>4217</v>
+        <v>4212</v>
       </c>
       <c r="H1902" s="28" t="s">
         <v>2210</v>
@@ -55241,7 +55229,7 @@
         <v>268</v>
       </c>
       <c r="B1903" s="28" t="s">
-        <v>4217</v>
+        <v>4212</v>
       </c>
       <c r="H1903" s="28" t="s">
         <v>2212</v>
@@ -55607,7 +55595,7 @@
         <v>382</v>
       </c>
       <c r="B1920" s="28" t="s">
-        <v>4218</v>
+        <v>4213</v>
       </c>
       <c r="D1920" s="24"/>
       <c r="E1920" s="24"/>
@@ -55632,7 +55620,7 @@
         <v>268</v>
       </c>
       <c r="B1921" s="28" t="s">
-        <v>4218</v>
+        <v>4213</v>
       </c>
       <c r="H1921" s="28" t="s">
         <v>2206</v>
@@ -55649,7 +55637,7 @@
         <v>268</v>
       </c>
       <c r="B1922" s="28" t="s">
-        <v>4218</v>
+        <v>4213</v>
       </c>
       <c r="H1922" s="28" t="s">
         <v>2208</v>
@@ -55666,7 +55654,7 @@
         <v>268</v>
       </c>
       <c r="B1923" s="28" t="s">
-        <v>4218</v>
+        <v>4213</v>
       </c>
       <c r="H1923" s="28" t="s">
         <v>2210</v>
@@ -55683,7 +55671,7 @@
         <v>268</v>
       </c>
       <c r="B1924" s="28" t="s">
-        <v>4218</v>
+        <v>4213</v>
       </c>
       <c r="H1924" s="28" t="s">
         <v>2212</v>
@@ -56282,7 +56270,7 @@
         <v>382</v>
       </c>
       <c r="B1949" s="28" t="s">
-        <v>4219</v>
+        <v>4214</v>
       </c>
       <c r="D1949" s="24"/>
       <c r="E1949" s="24"/>
@@ -56307,7 +56295,7 @@
         <v>268</v>
       </c>
       <c r="B1950" s="28" t="s">
-        <v>4219</v>
+        <v>4214</v>
       </c>
       <c r="H1950" s="28" t="s">
         <v>2568</v>
@@ -56324,7 +56312,7 @@
         <v>268</v>
       </c>
       <c r="B1951" s="28" t="s">
-        <v>4219</v>
+        <v>4214</v>
       </c>
       <c r="H1951" s="28" t="s">
         <v>2208</v>
@@ -56341,7 +56329,7 @@
         <v>268</v>
       </c>
       <c r="B1952" s="28" t="s">
-        <v>4219</v>
+        <v>4214</v>
       </c>
       <c r="H1952" s="28" t="s">
         <v>2210</v>
@@ -56358,7 +56346,7 @@
         <v>268</v>
       </c>
       <c r="B1953" s="28" t="s">
-        <v>4219</v>
+        <v>4214</v>
       </c>
       <c r="H1953" s="28" t="s">
         <v>2212</v>
@@ -72715,12 +72703,12 @@
       <c r="Q2776" s="33"/>
       <c r="R2776" s="33"/>
     </row>
-    <row r="2777" spans="1:18" s="28" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2777" spans="1:18" s="28" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A2777" s="35" t="s">
         <v>382</v>
       </c>
       <c r="B2777" s="28" t="s">
-        <v>3550</v>
+        <v>4215</v>
       </c>
       <c r="D2777" s="24"/>
       <c r="E2777" s="24"/>
@@ -72740,12 +72728,12 @@
       <c r="Q2777" s="24"/>
       <c r="R2777" s="24"/>
     </row>
-    <row r="2778" spans="1:18" s="28" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2778" spans="1:18" s="28" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A2778" s="28" t="s">
         <v>268</v>
       </c>
       <c r="B2778" s="28" t="s">
-        <v>3551</v>
+        <v>4215</v>
       </c>
       <c r="H2778" s="28" t="s">
         <v>2584</v>
@@ -72757,12 +72745,12 @@
         <v>282</v>
       </c>
     </row>
-    <row r="2779" spans="1:18" s="28" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2779" spans="1:18" s="28" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A2779" s="28" t="s">
         <v>268</v>
       </c>
       <c r="B2779" s="28" t="s">
-        <v>3552</v>
+        <v>4215</v>
       </c>
       <c r="H2779" s="28" t="s">
         <v>2208</v>
@@ -72774,12 +72762,12 @@
         <v>282</v>
       </c>
     </row>
-    <row r="2780" spans="1:18" s="28" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2780" spans="1:18" s="28" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A2780" s="28" t="s">
         <v>268</v>
       </c>
       <c r="B2780" s="28" t="s">
-        <v>3553</v>
+        <v>4215</v>
       </c>
       <c r="H2780" s="28" t="s">
         <v>2210</v>
@@ -72791,12 +72779,12 @@
         <v>282</v>
       </c>
     </row>
-    <row r="2781" spans="1:18" s="28" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2781" spans="1:18" s="28" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A2781" s="28" t="s">
         <v>268</v>
       </c>
       <c r="B2781" s="28" t="s">
-        <v>3554</v>
+        <v>4215</v>
       </c>
       <c r="H2781" s="28" t="s">
         <v>2212</v>
@@ -72808,16 +72796,16 @@
         <v>282</v>
       </c>
     </row>
-    <row r="2782" spans="1:18" s="28" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="2783" spans="1:18" s="28" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2782" spans="1:18" s="28" customFormat="1" ht="13.8" x14ac:dyDescent="0.25"/>
+    <row r="2783" spans="1:18" s="28" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A2783" s="28" t="s">
         <v>268</v>
       </c>
       <c r="B2783" s="28" t="s">
-        <v>3555</v>
+        <v>3550</v>
       </c>
       <c r="H2783" s="28" t="s">
-        <v>3556</v>
+        <v>3551</v>
       </c>
       <c r="I2783" s="28" t="s">
         <v>2581</v>
@@ -72826,12 +72814,12 @@
         <v>282</v>
       </c>
     </row>
-    <row r="2784" spans="1:18" s="28" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2784" spans="1:18" s="28" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A2784" s="28" t="s">
         <v>296</v>
       </c>
       <c r="B2784" s="28" t="s">
-        <v>3557</v>
+        <v>3552</v>
       </c>
       <c r="D2784" s="28" t="s">
         <v>404</v>
@@ -72846,15 +72834,15 @@
         <v>286</v>
       </c>
       <c r="O2784" s="28" t="s">
-        <v>3558</v>
-      </c>
-    </row>
-    <row r="2785" spans="1:15" s="28" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+        <v>3553</v>
+      </c>
+    </row>
+    <row r="2785" spans="1:15" s="28" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A2785" s="28" t="s">
         <v>296</v>
       </c>
       <c r="B2785" s="28" t="s">
-        <v>3559</v>
+        <v>3554</v>
       </c>
       <c r="D2785" s="28" t="s">
         <v>404</v>
@@ -72869,15 +72857,15 @@
         <v>282</v>
       </c>
       <c r="O2785" s="28" t="s">
-        <v>3560</v>
-      </c>
-    </row>
-    <row r="2786" spans="1:15" s="28" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+        <v>3555</v>
+      </c>
+    </row>
+    <row r="2786" spans="1:15" s="28" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A2786" s="28" t="s">
         <v>296</v>
       </c>
       <c r="B2786" s="28" t="s">
-        <v>3561</v>
+        <v>3556</v>
       </c>
       <c r="D2786" s="28" t="s">
         <v>404</v>
@@ -72892,18 +72880,18 @@
         <v>282</v>
       </c>
       <c r="O2786" s="28" t="s">
-        <v>3562</v>
-      </c>
-    </row>
-    <row r="2787" spans="1:15" s="28" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+        <v>3557</v>
+      </c>
+    </row>
+    <row r="2787" spans="1:15" s="28" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A2787" s="28" t="s">
         <v>268</v>
       </c>
       <c r="B2787" s="28" t="s">
-        <v>3563</v>
+        <v>3558</v>
       </c>
       <c r="H2787" s="28" t="s">
-        <v>3564</v>
+        <v>3559</v>
       </c>
       <c r="I2787" s="28" t="s">
         <v>2633</v>
@@ -72912,12 +72900,12 @@
         <v>282</v>
       </c>
     </row>
-    <row r="2788" spans="1:15" s="28" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2788" spans="1:15" s="28" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A2788" s="28" t="s">
         <v>296</v>
       </c>
       <c r="B2788" s="28" t="s">
-        <v>3565</v>
+        <v>3560</v>
       </c>
       <c r="D2788" s="28" t="s">
         <v>404</v>
@@ -72932,15 +72920,15 @@
         <v>286</v>
       </c>
       <c r="O2788" s="28" t="s">
-        <v>3566</v>
-      </c>
-    </row>
-    <row r="2789" spans="1:15" s="28" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+        <v>3561</v>
+      </c>
+    </row>
+    <row r="2789" spans="1:15" s="28" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A2789" s="28" t="s">
         <v>296</v>
       </c>
       <c r="B2789" s="28" t="s">
-        <v>3567</v>
+        <v>3562</v>
       </c>
       <c r="D2789" s="28" t="s">
         <v>404</v>
@@ -72955,15 +72943,15 @@
         <v>282</v>
       </c>
       <c r="O2789" s="28" t="s">
-        <v>3568</v>
-      </c>
-    </row>
-    <row r="2790" spans="1:15" s="28" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+        <v>3563</v>
+      </c>
+    </row>
+    <row r="2790" spans="1:15" s="28" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A2790" s="28" t="s">
         <v>296</v>
       </c>
       <c r="B2790" s="28" t="s">
-        <v>3569</v>
+        <v>3564</v>
       </c>
       <c r="D2790" s="28" t="s">
         <v>404</v>
@@ -72978,32 +72966,32 @@
         <v>282</v>
       </c>
       <c r="O2790" s="28" t="s">
-        <v>3570</v>
-      </c>
-    </row>
-    <row r="2791" spans="1:15" s="28" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+        <v>3565</v>
+      </c>
+    </row>
+    <row r="2791" spans="1:15" s="28" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A2791" s="28" t="s">
         <v>268</v>
       </c>
       <c r="B2791" s="28" t="s">
-        <v>3571</v>
+        <v>3566</v>
       </c>
       <c r="H2791" s="28" t="s">
-        <v>3572</v>
+        <v>3567</v>
       </c>
       <c r="I2791" s="28" t="s">
-        <v>3573</v>
+        <v>3568</v>
       </c>
       <c r="M2791" s="28" t="s">
         <v>282</v>
       </c>
     </row>
-    <row r="2792" spans="1:15" s="28" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2792" spans="1:15" s="28" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A2792" s="28" t="s">
         <v>296</v>
       </c>
       <c r="B2792" s="28" t="s">
-        <v>3574</v>
+        <v>3569</v>
       </c>
       <c r="D2792" s="28" t="s">
         <v>404</v>
@@ -73018,15 +73006,15 @@
         <v>286</v>
       </c>
       <c r="O2792" s="28" t="s">
-        <v>3575</v>
-      </c>
-    </row>
-    <row r="2793" spans="1:15" s="28" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+        <v>3570</v>
+      </c>
+    </row>
+    <row r="2793" spans="1:15" s="28" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A2793" s="28" t="s">
         <v>296</v>
       </c>
       <c r="B2793" s="28" t="s">
-        <v>3576</v>
+        <v>3571</v>
       </c>
       <c r="D2793" s="28" t="s">
         <v>404</v>
@@ -73041,15 +73029,15 @@
         <v>282</v>
       </c>
       <c r="O2793" s="28" t="s">
-        <v>3577</v>
-      </c>
-    </row>
-    <row r="2794" spans="1:15" s="28" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+        <v>3572</v>
+      </c>
+    </row>
+    <row r="2794" spans="1:15" s="28" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A2794" s="28" t="s">
         <v>296</v>
       </c>
       <c r="B2794" s="28" t="s">
-        <v>3578</v>
+        <v>3573</v>
       </c>
       <c r="D2794" s="28" t="s">
         <v>404</v>
@@ -73064,32 +73052,32 @@
         <v>282</v>
       </c>
       <c r="O2794" s="28" t="s">
-        <v>3579</v>
-      </c>
-    </row>
-    <row r="2795" spans="1:15" s="28" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+        <v>3574</v>
+      </c>
+    </row>
+    <row r="2795" spans="1:15" s="28" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A2795" s="28" t="s">
         <v>268</v>
       </c>
       <c r="B2795" s="28" t="s">
-        <v>3580</v>
+        <v>3575</v>
       </c>
       <c r="H2795" s="28" t="s">
-        <v>3581</v>
+        <v>3576</v>
       </c>
       <c r="I2795" s="28" t="s">
-        <v>3582</v>
+        <v>3577</v>
       </c>
       <c r="M2795" s="28" t="s">
         <v>282</v>
       </c>
     </row>
-    <row r="2796" spans="1:15" s="28" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2796" spans="1:15" s="28" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A2796" s="28" t="s">
         <v>296</v>
       </c>
       <c r="B2796" s="28" t="s">
-        <v>3583</v>
+        <v>3578</v>
       </c>
       <c r="D2796" s="28" t="s">
         <v>404</v>
@@ -73104,15 +73092,15 @@
         <v>286</v>
       </c>
       <c r="O2796" s="28" t="s">
-        <v>3584</v>
-      </c>
-    </row>
-    <row r="2797" spans="1:15" s="28" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+        <v>3579</v>
+      </c>
+    </row>
+    <row r="2797" spans="1:15" s="28" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A2797" s="28" t="s">
         <v>296</v>
       </c>
       <c r="B2797" s="28" t="s">
-        <v>3585</v>
+        <v>3580</v>
       </c>
       <c r="D2797" s="28" t="s">
         <v>404</v>
@@ -73127,15 +73115,15 @@
         <v>282</v>
       </c>
       <c r="O2797" s="28" t="s">
-        <v>3586</v>
-      </c>
-    </row>
-    <row r="2798" spans="1:15" s="28" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+        <v>3581</v>
+      </c>
+    </row>
+    <row r="2798" spans="1:15" s="28" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A2798" s="28" t="s">
         <v>296</v>
       </c>
       <c r="B2798" s="28" t="s">
-        <v>3587</v>
+        <v>3582</v>
       </c>
       <c r="D2798" s="28" t="s">
         <v>404</v>
@@ -73150,18 +73138,18 @@
         <v>282</v>
       </c>
       <c r="O2798" s="28" t="s">
-        <v>3588</v>
-      </c>
-    </row>
-    <row r="2799" spans="1:15" s="28" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+        <v>3583</v>
+      </c>
+    </row>
+    <row r="2799" spans="1:15" s="28" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A2799" s="28" t="s">
         <v>268</v>
       </c>
       <c r="B2799" s="28" t="s">
-        <v>3589</v>
+        <v>3584</v>
       </c>
       <c r="H2799" s="29" t="s">
-        <v>3590</v>
+        <v>3585</v>
       </c>
       <c r="I2799" s="28" t="s">
         <v>179</v>
@@ -73170,12 +73158,12 @@
         <v>282</v>
       </c>
     </row>
-    <row r="2800" spans="1:15" s="28" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2800" spans="1:15" s="28" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A2800" s="28" t="s">
         <v>296</v>
       </c>
       <c r="B2800" s="28" t="s">
-        <v>3591</v>
+        <v>3586</v>
       </c>
       <c r="D2800" s="28" t="s">
         <v>404</v>
@@ -73190,15 +73178,15 @@
         <v>286</v>
       </c>
       <c r="O2800" s="28" t="s">
-        <v>3592</v>
-      </c>
-    </row>
-    <row r="2801" spans="1:15" s="28" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+        <v>3587</v>
+      </c>
+    </row>
+    <row r="2801" spans="1:15" s="28" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A2801" s="28" t="s">
         <v>296</v>
       </c>
       <c r="B2801" s="28" t="s">
-        <v>3593</v>
+        <v>3588</v>
       </c>
       <c r="D2801" s="28" t="s">
         <v>404</v>
@@ -73213,15 +73201,15 @@
         <v>282</v>
       </c>
       <c r="O2801" s="28" t="s">
-        <v>3594</v>
-      </c>
-    </row>
-    <row r="2802" spans="1:15" s="28" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+        <v>3589</v>
+      </c>
+    </row>
+    <row r="2802" spans="1:15" s="28" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A2802" s="28" t="s">
         <v>296</v>
       </c>
       <c r="B2802" s="28" t="s">
-        <v>3595</v>
+        <v>3590</v>
       </c>
       <c r="D2802" s="28" t="s">
         <v>404</v>
@@ -73236,18 +73224,18 @@
         <v>282</v>
       </c>
       <c r="O2802" s="28" t="s">
-        <v>3596</v>
-      </c>
-    </row>
-    <row r="2803" spans="1:15" s="28" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+        <v>3591</v>
+      </c>
+    </row>
+    <row r="2803" spans="1:15" s="28" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A2803" s="28" t="s">
         <v>268</v>
       </c>
       <c r="B2803" s="28" t="s">
-        <v>3597</v>
+        <v>3592</v>
       </c>
       <c r="H2803" s="29" t="s">
-        <v>3598</v>
+        <v>3593</v>
       </c>
       <c r="I2803" s="28" t="s">
         <v>182</v>
@@ -73256,12 +73244,12 @@
         <v>282</v>
       </c>
     </row>
-    <row r="2804" spans="1:15" s="28" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2804" spans="1:15" s="28" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A2804" s="28" t="s">
         <v>296</v>
       </c>
       <c r="B2804" s="28" t="s">
-        <v>3599</v>
+        <v>3594</v>
       </c>
       <c r="D2804" s="28" t="s">
         <v>404</v>
@@ -73276,15 +73264,15 @@
         <v>286</v>
       </c>
       <c r="O2804" s="28" t="s">
-        <v>3600</v>
-      </c>
-    </row>
-    <row r="2805" spans="1:15" s="28" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+        <v>3595</v>
+      </c>
+    </row>
+    <row r="2805" spans="1:15" s="28" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A2805" s="28" t="s">
         <v>296</v>
       </c>
       <c r="B2805" s="28" t="s">
-        <v>3601</v>
+        <v>3596</v>
       </c>
       <c r="D2805" s="28" t="s">
         <v>404</v>
@@ -73299,15 +73287,15 @@
         <v>282</v>
       </c>
       <c r="O2805" s="28" t="s">
-        <v>3602</v>
-      </c>
-    </row>
-    <row r="2806" spans="1:15" s="28" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+        <v>3597</v>
+      </c>
+    </row>
+    <row r="2806" spans="1:15" s="28" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A2806" s="28" t="s">
         <v>296</v>
       </c>
       <c r="B2806" s="28" t="s">
-        <v>3603</v>
+        <v>3598</v>
       </c>
       <c r="D2806" s="28" t="s">
         <v>404</v>
@@ -73322,18 +73310,18 @@
         <v>282</v>
       </c>
       <c r="O2806" s="28" t="s">
-        <v>3604</v>
-      </c>
-    </row>
-    <row r="2807" spans="1:15" s="28" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+        <v>3599</v>
+      </c>
+    </row>
+    <row r="2807" spans="1:15" s="28" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A2807" s="28" t="s">
         <v>268</v>
       </c>
       <c r="B2807" s="28" t="s">
-        <v>3605</v>
+        <v>3600</v>
       </c>
       <c r="H2807" s="29" t="s">
-        <v>3606</v>
+        <v>3601</v>
       </c>
       <c r="I2807" s="28" t="s">
         <v>181</v>
@@ -73342,12 +73330,12 @@
         <v>282</v>
       </c>
     </row>
-    <row r="2808" spans="1:15" s="28" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2808" spans="1:15" s="28" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A2808" s="28" t="s">
         <v>296</v>
       </c>
       <c r="B2808" s="28" t="s">
-        <v>3607</v>
+        <v>3602</v>
       </c>
       <c r="D2808" s="28" t="s">
         <v>404</v>
@@ -73362,15 +73350,15 @@
         <v>286</v>
       </c>
       <c r="O2808" s="28" t="s">
-        <v>3608</v>
-      </c>
-    </row>
-    <row r="2809" spans="1:15" s="28" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+        <v>3603</v>
+      </c>
+    </row>
+    <row r="2809" spans="1:15" s="28" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A2809" s="28" t="s">
         <v>296</v>
       </c>
       <c r="B2809" s="28" t="s">
-        <v>3609</v>
+        <v>3604</v>
       </c>
       <c r="D2809" s="28" t="s">
         <v>404</v>
@@ -73385,15 +73373,15 @@
         <v>282</v>
       </c>
       <c r="O2809" s="28" t="s">
-        <v>3610</v>
-      </c>
-    </row>
-    <row r="2810" spans="1:15" s="28" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+        <v>3605</v>
+      </c>
+    </row>
+    <row r="2810" spans="1:15" s="28" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A2810" s="28" t="s">
         <v>296</v>
       </c>
       <c r="B2810" s="28" t="s">
-        <v>3611</v>
+        <v>3606</v>
       </c>
       <c r="D2810" s="28" t="s">
         <v>404</v>
@@ -73408,18 +73396,18 @@
         <v>282</v>
       </c>
       <c r="O2810" s="28" t="s">
-        <v>3612</v>
-      </c>
-    </row>
-    <row r="2811" spans="1:15" s="28" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+        <v>3607</v>
+      </c>
+    </row>
+    <row r="2811" spans="1:15" s="28" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A2811" s="28" t="s">
         <v>268</v>
       </c>
       <c r="B2811" s="28" t="s">
-        <v>3613</v>
+        <v>3608</v>
       </c>
       <c r="H2811" s="29" t="s">
-        <v>3614</v>
+        <v>3609</v>
       </c>
       <c r="I2811" s="28" t="s">
         <v>2895</v>
@@ -73428,12 +73416,12 @@
         <v>282</v>
       </c>
     </row>
-    <row r="2812" spans="1:15" s="28" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2812" spans="1:15" s="28" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A2812" s="28" t="s">
         <v>296</v>
       </c>
       <c r="B2812" s="28" t="s">
-        <v>3615</v>
+        <v>3610</v>
       </c>
       <c r="D2812" s="28" t="s">
         <v>404</v>
@@ -73448,15 +73436,15 @@
         <v>286</v>
       </c>
       <c r="O2812" s="28" t="s">
-        <v>3616</v>
-      </c>
-    </row>
-    <row r="2813" spans="1:15" s="28" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+        <v>3611</v>
+      </c>
+    </row>
+    <row r="2813" spans="1:15" s="28" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A2813" s="28" t="s">
         <v>296</v>
       </c>
       <c r="B2813" s="28" t="s">
-        <v>3617</v>
+        <v>3612</v>
       </c>
       <c r="D2813" s="28" t="s">
         <v>404</v>
@@ -73471,15 +73459,15 @@
         <v>282</v>
       </c>
       <c r="O2813" s="28" t="s">
-        <v>3618</v>
-      </c>
-    </row>
-    <row r="2814" spans="1:15" s="28" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+        <v>3613</v>
+      </c>
+    </row>
+    <row r="2814" spans="1:15" s="28" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A2814" s="28" t="s">
         <v>296</v>
       </c>
       <c r="B2814" s="28" t="s">
-        <v>3619</v>
+        <v>3614</v>
       </c>
       <c r="D2814" s="28" t="s">
         <v>404</v>
@@ -73494,18 +73482,18 @@
         <v>282</v>
       </c>
       <c r="O2814" s="28" t="s">
-        <v>3620</v>
-      </c>
-    </row>
-    <row r="2815" spans="1:15" s="28" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+        <v>3615</v>
+      </c>
+    </row>
+    <row r="2815" spans="1:15" s="28" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A2815" s="28" t="s">
         <v>268</v>
       </c>
       <c r="B2815" s="28" t="s">
-        <v>3621</v>
+        <v>3616</v>
       </c>
       <c r="H2815" s="29" t="s">
-        <v>3622</v>
+        <v>3617</v>
       </c>
       <c r="I2815" s="28" t="s">
         <v>2939</v>
@@ -73514,12 +73502,12 @@
         <v>282</v>
       </c>
     </row>
-    <row r="2816" spans="1:15" s="28" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2816" spans="1:15" s="28" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A2816" s="28" t="s">
         <v>296</v>
       </c>
       <c r="B2816" s="28" t="s">
-        <v>3623</v>
+        <v>3618</v>
       </c>
       <c r="D2816" s="28" t="s">
         <v>404</v>
@@ -73534,15 +73522,15 @@
         <v>286</v>
       </c>
       <c r="O2816" s="28" t="s">
-        <v>3624</v>
-      </c>
-    </row>
-    <row r="2817" spans="1:15" s="28" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+        <v>3619</v>
+      </c>
+    </row>
+    <row r="2817" spans="1:15" s="28" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A2817" s="28" t="s">
         <v>296</v>
       </c>
       <c r="B2817" s="28" t="s">
-        <v>3625</v>
+        <v>3620</v>
       </c>
       <c r="D2817" s="28" t="s">
         <v>404</v>
@@ -73557,15 +73545,15 @@
         <v>282</v>
       </c>
       <c r="O2817" s="28" t="s">
-        <v>3626</v>
-      </c>
-    </row>
-    <row r="2818" spans="1:15" s="28" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+        <v>3621</v>
+      </c>
+    </row>
+    <row r="2818" spans="1:15" s="28" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A2818" s="28" t="s">
         <v>296</v>
       </c>
       <c r="B2818" s="28" t="s">
-        <v>3627</v>
+        <v>3622</v>
       </c>
       <c r="D2818" s="28" t="s">
         <v>404</v>
@@ -73580,18 +73568,18 @@
         <v>282</v>
       </c>
       <c r="O2818" s="28" t="s">
-        <v>3628</v>
-      </c>
-    </row>
-    <row r="2819" spans="1:15" s="28" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+        <v>3623</v>
+      </c>
+    </row>
+    <row r="2819" spans="1:15" s="28" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A2819" s="28" t="s">
         <v>268</v>
       </c>
       <c r="B2819" s="28" t="s">
-        <v>3629</v>
+        <v>3624</v>
       </c>
       <c r="H2819" s="29" t="s">
-        <v>3630</v>
+        <v>3625</v>
       </c>
       <c r="I2819" s="28" t="s">
         <v>184</v>
@@ -73600,12 +73588,12 @@
         <v>282</v>
       </c>
     </row>
-    <row r="2820" spans="1:15" s="28" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2820" spans="1:15" s="28" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A2820" s="28" t="s">
         <v>296</v>
       </c>
       <c r="B2820" s="28" t="s">
-        <v>3631</v>
+        <v>3626</v>
       </c>
       <c r="D2820" s="28" t="s">
         <v>404</v>
@@ -73620,15 +73608,15 @@
         <v>286</v>
       </c>
       <c r="O2820" s="28" t="s">
-        <v>3632</v>
-      </c>
-    </row>
-    <row r="2821" spans="1:15" s="28" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+        <v>3627</v>
+      </c>
+    </row>
+    <row r="2821" spans="1:15" s="28" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A2821" s="28" t="s">
         <v>296</v>
       </c>
       <c r="B2821" s="28" t="s">
-        <v>3633</v>
+        <v>3628</v>
       </c>
       <c r="D2821" s="28" t="s">
         <v>404</v>
@@ -73643,15 +73631,15 @@
         <v>282</v>
       </c>
       <c r="O2821" s="28" t="s">
-        <v>3634</v>
-      </c>
-    </row>
-    <row r="2822" spans="1:15" s="28" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+        <v>3629</v>
+      </c>
+    </row>
+    <row r="2822" spans="1:15" s="28" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A2822" s="28" t="s">
         <v>296</v>
       </c>
       <c r="B2822" s="28" t="s">
-        <v>3635</v>
+        <v>3630</v>
       </c>
       <c r="D2822" s="28" t="s">
         <v>404</v>
@@ -73666,18 +73654,18 @@
         <v>282</v>
       </c>
       <c r="O2822" s="28" t="s">
-        <v>3636</v>
-      </c>
-    </row>
-    <row r="2823" spans="1:15" s="28" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+        <v>3631</v>
+      </c>
+    </row>
+    <row r="2823" spans="1:15" s="28" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A2823" s="28" t="s">
         <v>268</v>
       </c>
       <c r="B2823" s="28" t="s">
-        <v>3637</v>
+        <v>3632</v>
       </c>
       <c r="H2823" s="29" t="s">
-        <v>3638</v>
+        <v>3633</v>
       </c>
       <c r="I2823" s="28" t="s">
         <v>185</v>
@@ -73686,12 +73674,12 @@
         <v>282</v>
       </c>
     </row>
-    <row r="2824" spans="1:15" s="28" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2824" spans="1:15" s="28" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A2824" s="28" t="s">
         <v>296</v>
       </c>
       <c r="B2824" s="28" t="s">
-        <v>3639</v>
+        <v>3634</v>
       </c>
       <c r="D2824" s="28" t="s">
         <v>404</v>
@@ -73706,15 +73694,15 @@
         <v>286</v>
       </c>
       <c r="O2824" s="28" t="s">
-        <v>3640</v>
-      </c>
-    </row>
-    <row r="2825" spans="1:15" s="28" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+        <v>3635</v>
+      </c>
+    </row>
+    <row r="2825" spans="1:15" s="28" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A2825" s="28" t="s">
         <v>296</v>
       </c>
       <c r="B2825" s="28" t="s">
-        <v>3641</v>
+        <v>3636</v>
       </c>
       <c r="D2825" s="28" t="s">
         <v>404</v>
@@ -73729,15 +73717,15 @@
         <v>282</v>
       </c>
       <c r="O2825" s="28" t="s">
-        <v>3642</v>
-      </c>
-    </row>
-    <row r="2826" spans="1:15" s="28" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+        <v>3637</v>
+      </c>
+    </row>
+    <row r="2826" spans="1:15" s="28" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A2826" s="28" t="s">
         <v>296</v>
       </c>
       <c r="B2826" s="28" t="s">
-        <v>3643</v>
+        <v>3638</v>
       </c>
       <c r="D2826" s="28" t="s">
         <v>404</v>
@@ -73752,32 +73740,32 @@
         <v>282</v>
       </c>
       <c r="O2826" s="28" t="s">
-        <v>3644</v>
-      </c>
-    </row>
-    <row r="2827" spans="1:15" s="28" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+        <v>3639</v>
+      </c>
+    </row>
+    <row r="2827" spans="1:15" s="28" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A2827" s="28" t="s">
         <v>268</v>
       </c>
       <c r="B2827" s="28" t="s">
-        <v>3645</v>
+        <v>3640</v>
       </c>
       <c r="H2827" s="29" t="s">
-        <v>3646</v>
+        <v>3641</v>
       </c>
       <c r="I2827" s="28" t="s">
-        <v>3647</v>
+        <v>3642</v>
       </c>
       <c r="M2827" s="28" t="s">
         <v>282</v>
       </c>
     </row>
-    <row r="2828" spans="1:15" s="28" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2828" spans="1:15" s="28" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A2828" s="28" t="s">
         <v>296</v>
       </c>
       <c r="B2828" s="28" t="s">
-        <v>3648</v>
+        <v>3643</v>
       </c>
       <c r="D2828" s="28" t="s">
         <v>404</v>
@@ -73792,15 +73780,15 @@
         <v>286</v>
       </c>
       <c r="O2828" s="28" t="s">
-        <v>3649</v>
-      </c>
-    </row>
-    <row r="2829" spans="1:15" s="28" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+        <v>3644</v>
+      </c>
+    </row>
+    <row r="2829" spans="1:15" s="28" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A2829" s="28" t="s">
         <v>296</v>
       </c>
       <c r="B2829" s="28" t="s">
-        <v>3650</v>
+        <v>3645</v>
       </c>
       <c r="D2829" s="28" t="s">
         <v>404</v>
@@ -73815,15 +73803,15 @@
         <v>282</v>
       </c>
       <c r="O2829" s="28" t="s">
-        <v>3651</v>
-      </c>
-    </row>
-    <row r="2830" spans="1:15" s="28" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+        <v>3646</v>
+      </c>
+    </row>
+    <row r="2830" spans="1:15" s="28" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A2830" s="28" t="s">
         <v>296</v>
       </c>
       <c r="B2830" s="28" t="s">
-        <v>3652</v>
+        <v>3647</v>
       </c>
       <c r="D2830" s="28" t="s">
         <v>404</v>
@@ -73838,18 +73826,18 @@
         <v>282</v>
       </c>
       <c r="O2830" s="28" t="s">
-        <v>3653</v>
-      </c>
-    </row>
-    <row r="2831" spans="1:15" s="28" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+        <v>3648</v>
+      </c>
+    </row>
+    <row r="2831" spans="1:15" s="28" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A2831" s="28" t="s">
         <v>268</v>
       </c>
       <c r="B2831" s="28" t="s">
-        <v>3654</v>
+        <v>3649</v>
       </c>
       <c r="H2831" s="29" t="s">
-        <v>3655</v>
+        <v>3650</v>
       </c>
       <c r="I2831" s="28" t="s">
         <v>3113</v>
@@ -73858,12 +73846,12 @@
         <v>282</v>
       </c>
     </row>
-    <row r="2832" spans="1:15" s="28" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2832" spans="1:15" s="28" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A2832" s="28" t="s">
         <v>296</v>
       </c>
       <c r="B2832" s="28" t="s">
-        <v>3656</v>
+        <v>3651</v>
       </c>
       <c r="D2832" s="28" t="s">
         <v>404</v>
@@ -73878,15 +73866,15 @@
         <v>286</v>
       </c>
       <c r="O2832" s="28" t="s">
-        <v>3657</v>
-      </c>
-    </row>
-    <row r="2833" spans="1:15" s="28" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+        <v>3652</v>
+      </c>
+    </row>
+    <row r="2833" spans="1:15" s="28" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A2833" s="28" t="s">
         <v>296</v>
       </c>
       <c r="B2833" s="28" t="s">
-        <v>3658</v>
+        <v>3653</v>
       </c>
       <c r="D2833" s="28" t="s">
         <v>404</v>
@@ -73901,15 +73889,15 @@
         <v>282</v>
       </c>
       <c r="O2833" s="28" t="s">
-        <v>3659</v>
-      </c>
-    </row>
-    <row r="2834" spans="1:15" s="28" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+        <v>3654</v>
+      </c>
+    </row>
+    <row r="2834" spans="1:15" s="28" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A2834" s="28" t="s">
         <v>296</v>
       </c>
       <c r="B2834" s="28" t="s">
-        <v>3660</v>
+        <v>3655</v>
       </c>
       <c r="D2834" s="28" t="s">
         <v>404</v>
@@ -73924,18 +73912,18 @@
         <v>282</v>
       </c>
       <c r="O2834" s="28" t="s">
-        <v>3661</v>
-      </c>
-    </row>
-    <row r="2835" spans="1:15" s="28" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+        <v>3656</v>
+      </c>
+    </row>
+    <row r="2835" spans="1:15" s="28" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A2835" s="28" t="s">
         <v>268</v>
       </c>
       <c r="B2835" s="28" t="s">
-        <v>3662</v>
+        <v>3657</v>
       </c>
       <c r="H2835" s="29" t="s">
-        <v>3663</v>
+        <v>3658</v>
       </c>
       <c r="I2835" s="28" t="s">
         <v>3157</v>
@@ -73944,12 +73932,12 @@
         <v>282</v>
       </c>
     </row>
-    <row r="2836" spans="1:15" s="28" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2836" spans="1:15" s="28" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A2836" s="28" t="s">
         <v>296</v>
       </c>
       <c r="B2836" s="28" t="s">
-        <v>3664</v>
+        <v>3659</v>
       </c>
       <c r="D2836" s="28" t="s">
         <v>404</v>
@@ -73964,15 +73952,15 @@
         <v>286</v>
       </c>
       <c r="O2836" s="28" t="s">
-        <v>3665</v>
-      </c>
-    </row>
-    <row r="2837" spans="1:15" s="28" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+        <v>3660</v>
+      </c>
+    </row>
+    <row r="2837" spans="1:15" s="28" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A2837" s="28" t="s">
         <v>296</v>
       </c>
       <c r="B2837" s="28" t="s">
-        <v>3666</v>
+        <v>3661</v>
       </c>
       <c r="D2837" s="28" t="s">
         <v>404</v>
@@ -73987,15 +73975,15 @@
         <v>282</v>
       </c>
       <c r="O2837" s="28" t="s">
-        <v>3667</v>
-      </c>
-    </row>
-    <row r="2838" spans="1:15" s="28" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+        <v>3662</v>
+      </c>
+    </row>
+    <row r="2838" spans="1:15" s="28" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A2838" s="28" t="s">
         <v>296</v>
       </c>
       <c r="B2838" s="28" t="s">
-        <v>3668</v>
+        <v>3663</v>
       </c>
       <c r="D2838" s="28" t="s">
         <v>404</v>
@@ -74010,18 +73998,18 @@
         <v>282</v>
       </c>
       <c r="O2838" s="28" t="s">
-        <v>3669</v>
-      </c>
-    </row>
-    <row r="2839" spans="1:15" s="28" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+        <v>3664</v>
+      </c>
+    </row>
+    <row r="2839" spans="1:15" s="28" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A2839" s="28" t="s">
         <v>268</v>
       </c>
       <c r="B2839" s="28" t="s">
-        <v>3670</v>
+        <v>3665</v>
       </c>
       <c r="H2839" s="29" t="s">
-        <v>3671</v>
+        <v>3666</v>
       </c>
       <c r="I2839" s="28" t="s">
         <v>3201</v>
@@ -74030,12 +74018,12 @@
         <v>282</v>
       </c>
     </row>
-    <row r="2840" spans="1:15" s="28" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2840" spans="1:15" s="28" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A2840" s="28" t="s">
         <v>296</v>
       </c>
       <c r="B2840" s="28" t="s">
-        <v>3672</v>
+        <v>3667</v>
       </c>
       <c r="D2840" s="28" t="s">
         <v>404</v>
@@ -74050,15 +74038,15 @@
         <v>286</v>
       </c>
       <c r="O2840" s="28" t="s">
-        <v>3673</v>
-      </c>
-    </row>
-    <row r="2841" spans="1:15" s="28" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+        <v>3668</v>
+      </c>
+    </row>
+    <row r="2841" spans="1:15" s="28" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A2841" s="28" t="s">
         <v>296</v>
       </c>
       <c r="B2841" s="28" t="s">
-        <v>3674</v>
+        <v>3669</v>
       </c>
       <c r="D2841" s="28" t="s">
         <v>404</v>
@@ -74073,15 +74061,15 @@
         <v>282</v>
       </c>
       <c r="O2841" s="28" t="s">
-        <v>3675</v>
-      </c>
-    </row>
-    <row r="2842" spans="1:15" s="28" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+        <v>3670</v>
+      </c>
+    </row>
+    <row r="2842" spans="1:15" s="28" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A2842" s="28" t="s">
         <v>296</v>
       </c>
       <c r="B2842" s="28" t="s">
-        <v>3676</v>
+        <v>3671</v>
       </c>
       <c r="D2842" s="28" t="s">
         <v>404</v>
@@ -74096,18 +74084,18 @@
         <v>282</v>
       </c>
       <c r="O2842" s="28" t="s">
-        <v>3677</v>
-      </c>
-    </row>
-    <row r="2843" spans="1:15" s="28" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+        <v>3672</v>
+      </c>
+    </row>
+    <row r="2843" spans="1:15" s="28" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A2843" s="28" t="s">
         <v>268</v>
       </c>
       <c r="B2843" s="28" t="s">
-        <v>3678</v>
+        <v>3673</v>
       </c>
       <c r="H2843" s="29" t="s">
-        <v>3679</v>
+        <v>3674</v>
       </c>
       <c r="I2843" s="28" t="s">
         <v>188</v>
@@ -74116,12 +74104,12 @@
         <v>282</v>
       </c>
     </row>
-    <row r="2844" spans="1:15" s="28" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2844" spans="1:15" s="28" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A2844" s="28" t="s">
         <v>296</v>
       </c>
       <c r="B2844" s="28" t="s">
-        <v>3680</v>
+        <v>3675</v>
       </c>
       <c r="D2844" s="28" t="s">
         <v>404</v>
@@ -74136,15 +74124,15 @@
         <v>286</v>
       </c>
       <c r="O2844" s="28" t="s">
-        <v>3681</v>
-      </c>
-    </row>
-    <row r="2845" spans="1:15" s="28" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+        <v>3676</v>
+      </c>
+    </row>
+    <row r="2845" spans="1:15" s="28" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A2845" s="28" t="s">
         <v>296</v>
       </c>
       <c r="B2845" s="28" t="s">
-        <v>3682</v>
+        <v>3677</v>
       </c>
       <c r="D2845" s="28" t="s">
         <v>404</v>
@@ -74159,15 +74147,15 @@
         <v>282</v>
       </c>
       <c r="O2845" s="28" t="s">
-        <v>3683</v>
-      </c>
-    </row>
-    <row r="2846" spans="1:15" s="28" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+        <v>3678</v>
+      </c>
+    </row>
+    <row r="2846" spans="1:15" s="28" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A2846" s="28" t="s">
         <v>296</v>
       </c>
       <c r="B2846" s="28" t="s">
-        <v>3684</v>
+        <v>3679</v>
       </c>
       <c r="D2846" s="28" t="s">
         <v>404</v>
@@ -74182,18 +74170,18 @@
         <v>282</v>
       </c>
       <c r="O2846" s="28" t="s">
-        <v>3685</v>
-      </c>
-    </row>
-    <row r="2847" spans="1:15" s="28" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+        <v>3680</v>
+      </c>
+    </row>
+    <row r="2847" spans="1:15" s="28" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A2847" s="28" t="s">
         <v>268</v>
       </c>
       <c r="B2847" s="28" t="s">
-        <v>3686</v>
+        <v>3681</v>
       </c>
       <c r="H2847" s="29" t="s">
-        <v>3687</v>
+        <v>3682</v>
       </c>
       <c r="I2847" s="28" t="s">
         <v>3288</v>
@@ -74202,12 +74190,12 @@
         <v>282</v>
       </c>
     </row>
-    <row r="2848" spans="1:15" s="28" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2848" spans="1:15" s="28" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A2848" s="28" t="s">
         <v>296</v>
       </c>
       <c r="B2848" s="28" t="s">
-        <v>3688</v>
+        <v>3683</v>
       </c>
       <c r="D2848" s="28" t="s">
         <v>404</v>
@@ -74222,15 +74210,15 @@
         <v>286</v>
       </c>
       <c r="O2848" s="28" t="s">
-        <v>3689</v>
-      </c>
-    </row>
-    <row r="2849" spans="1:15" s="28" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+        <v>3684</v>
+      </c>
+    </row>
+    <row r="2849" spans="1:15" s="28" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A2849" s="28" t="s">
         <v>296</v>
       </c>
       <c r="B2849" s="28" t="s">
-        <v>3690</v>
+        <v>3685</v>
       </c>
       <c r="D2849" s="28" t="s">
         <v>404</v>
@@ -74245,15 +74233,15 @@
         <v>282</v>
       </c>
       <c r="O2849" s="28" t="s">
-        <v>3691</v>
-      </c>
-    </row>
-    <row r="2850" spans="1:15" s="28" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+        <v>3686</v>
+      </c>
+    </row>
+    <row r="2850" spans="1:15" s="28" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A2850" s="28" t="s">
         <v>296</v>
       </c>
       <c r="B2850" s="28" t="s">
-        <v>3692</v>
+        <v>3687</v>
       </c>
       <c r="D2850" s="28" t="s">
         <v>404</v>
@@ -74268,18 +74256,18 @@
         <v>282</v>
       </c>
       <c r="O2850" s="28" t="s">
-        <v>3693</v>
-      </c>
-    </row>
-    <row r="2851" spans="1:15" s="28" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+        <v>3688</v>
+      </c>
+    </row>
+    <row r="2851" spans="1:15" s="28" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A2851" s="28" t="s">
         <v>268</v>
       </c>
       <c r="B2851" s="28" t="s">
-        <v>3694</v>
+        <v>3689</v>
       </c>
       <c r="H2851" s="29" t="s">
-        <v>3695</v>
+        <v>3690</v>
       </c>
       <c r="I2851" s="28" t="s">
         <v>186</v>
@@ -74288,12 +74276,12 @@
         <v>282</v>
       </c>
     </row>
-    <row r="2852" spans="1:15" s="28" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2852" spans="1:15" s="28" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A2852" s="28" t="s">
         <v>296</v>
       </c>
       <c r="B2852" s="28" t="s">
-        <v>3696</v>
+        <v>3691</v>
       </c>
       <c r="D2852" s="28" t="s">
         <v>404</v>
@@ -74308,15 +74296,15 @@
         <v>286</v>
       </c>
       <c r="O2852" s="28" t="s">
-        <v>3697</v>
-      </c>
-    </row>
-    <row r="2853" spans="1:15" s="28" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+        <v>3692</v>
+      </c>
+    </row>
+    <row r="2853" spans="1:15" s="28" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A2853" s="28" t="s">
         <v>296</v>
       </c>
       <c r="B2853" s="28" t="s">
-        <v>3698</v>
+        <v>3693</v>
       </c>
       <c r="D2853" s="28" t="s">
         <v>404</v>
@@ -74331,15 +74319,15 @@
         <v>282</v>
       </c>
       <c r="O2853" s="28" t="s">
-        <v>3699</v>
-      </c>
-    </row>
-    <row r="2854" spans="1:15" s="28" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+        <v>3694</v>
+      </c>
+    </row>
+    <row r="2854" spans="1:15" s="28" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A2854" s="28" t="s">
         <v>296</v>
       </c>
       <c r="B2854" s="28" t="s">
-        <v>3700</v>
+        <v>3695</v>
       </c>
       <c r="D2854" s="28" t="s">
         <v>404</v>
@@ -74354,18 +74342,18 @@
         <v>282</v>
       </c>
       <c r="O2854" s="28" t="s">
-        <v>3701</v>
-      </c>
-    </row>
-    <row r="2855" spans="1:15" s="28" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+        <v>3696</v>
+      </c>
+    </row>
+    <row r="2855" spans="1:15" s="28" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A2855" s="28" t="s">
         <v>268</v>
       </c>
       <c r="B2855" s="28" t="s">
-        <v>3702</v>
+        <v>3697</v>
       </c>
       <c r="H2855" s="29" t="s">
-        <v>3703</v>
+        <v>3698</v>
       </c>
       <c r="I2855" s="28" t="s">
         <v>191</v>
@@ -74374,12 +74362,12 @@
         <v>282</v>
       </c>
     </row>
-    <row r="2856" spans="1:15" s="28" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2856" spans="1:15" s="28" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A2856" s="28" t="s">
         <v>296</v>
       </c>
       <c r="B2856" s="28" t="s">
-        <v>3704</v>
+        <v>3699</v>
       </c>
       <c r="D2856" s="28" t="s">
         <v>404</v>
@@ -74394,15 +74382,15 @@
         <v>286</v>
       </c>
       <c r="O2856" s="28" t="s">
-        <v>3705</v>
-      </c>
-    </row>
-    <row r="2857" spans="1:15" s="28" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+        <v>3700</v>
+      </c>
+    </row>
+    <row r="2857" spans="1:15" s="28" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A2857" s="28" t="s">
         <v>296</v>
       </c>
       <c r="B2857" s="28" t="s">
-        <v>3706</v>
+        <v>3701</v>
       </c>
       <c r="D2857" s="28" t="s">
         <v>404</v>
@@ -74417,15 +74405,15 @@
         <v>282</v>
       </c>
       <c r="O2857" s="28" t="s">
-        <v>3707</v>
-      </c>
-    </row>
-    <row r="2858" spans="1:15" s="28" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+        <v>3702</v>
+      </c>
+    </row>
+    <row r="2858" spans="1:15" s="28" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A2858" s="28" t="s">
         <v>296</v>
       </c>
       <c r="B2858" s="28" t="s">
-        <v>3708</v>
+        <v>3703</v>
       </c>
       <c r="D2858" s="28" t="s">
         <v>404</v>
@@ -74440,18 +74428,18 @@
         <v>282</v>
       </c>
       <c r="O2858" s="28" t="s">
-        <v>3709</v>
-      </c>
-    </row>
-    <row r="2859" spans="1:15" s="28" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+        <v>3704</v>
+      </c>
+    </row>
+    <row r="2859" spans="1:15" s="28" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A2859" s="28" t="s">
         <v>268</v>
       </c>
       <c r="B2859" s="28" t="s">
-        <v>3710</v>
+        <v>3705</v>
       </c>
       <c r="H2859" s="29" t="s">
-        <v>3711</v>
+        <v>3706</v>
       </c>
       <c r="I2859" s="28" t="s">
         <v>3418</v>
@@ -74460,12 +74448,12 @@
         <v>282</v>
       </c>
     </row>
-    <row r="2860" spans="1:15" s="28" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2860" spans="1:15" s="28" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A2860" s="28" t="s">
         <v>296</v>
       </c>
       <c r="B2860" s="28" t="s">
-        <v>3712</v>
+        <v>3707</v>
       </c>
       <c r="D2860" s="28" t="s">
         <v>404</v>
@@ -74480,15 +74468,15 @@
         <v>286</v>
       </c>
       <c r="O2860" s="28" t="s">
-        <v>3713</v>
-      </c>
-    </row>
-    <row r="2861" spans="1:15" s="28" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+        <v>3708</v>
+      </c>
+    </row>
+    <row r="2861" spans="1:15" s="28" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A2861" s="28" t="s">
         <v>296</v>
       </c>
       <c r="B2861" s="28" t="s">
-        <v>3714</v>
+        <v>3709</v>
       </c>
       <c r="D2861" s="28" t="s">
         <v>404</v>
@@ -74503,15 +74491,15 @@
         <v>282</v>
       </c>
       <c r="O2861" s="28" t="s">
-        <v>3715</v>
-      </c>
-    </row>
-    <row r="2862" spans="1:15" s="28" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+        <v>3710</v>
+      </c>
+    </row>
+    <row r="2862" spans="1:15" s="28" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A2862" s="28" t="s">
         <v>296</v>
       </c>
       <c r="B2862" s="28" t="s">
-        <v>3716</v>
+        <v>3711</v>
       </c>
       <c r="D2862" s="28" t="s">
         <v>404</v>
@@ -74526,18 +74514,18 @@
         <v>282</v>
       </c>
       <c r="O2862" s="28" t="s">
-        <v>3717</v>
-      </c>
-    </row>
-    <row r="2863" spans="1:15" s="28" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+        <v>3712</v>
+      </c>
+    </row>
+    <row r="2863" spans="1:15" s="28" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A2863" s="28" t="s">
         <v>268</v>
       </c>
       <c r="B2863" s="28" t="s">
-        <v>3718</v>
+        <v>3713</v>
       </c>
       <c r="H2863" s="29" t="s">
-        <v>3719</v>
+        <v>3714</v>
       </c>
       <c r="I2863" s="28" t="s">
         <v>3462</v>
@@ -74546,12 +74534,12 @@
         <v>282</v>
       </c>
     </row>
-    <row r="2864" spans="1:15" s="28" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2864" spans="1:15" s="28" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A2864" s="28" t="s">
         <v>296</v>
       </c>
       <c r="B2864" s="28" t="s">
-        <v>3720</v>
+        <v>3715</v>
       </c>
       <c r="D2864" s="28" t="s">
         <v>404</v>
@@ -74566,15 +74554,15 @@
         <v>286</v>
       </c>
       <c r="O2864" s="28" t="s">
-        <v>3721</v>
-      </c>
-    </row>
-    <row r="2865" spans="1:18" s="28" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+        <v>3716</v>
+      </c>
+    </row>
+    <row r="2865" spans="1:18" s="28" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A2865" s="28" t="s">
         <v>296</v>
       </c>
       <c r="B2865" s="28" t="s">
-        <v>3722</v>
+        <v>3717</v>
       </c>
       <c r="D2865" s="28" t="s">
         <v>404</v>
@@ -74589,15 +74577,15 @@
         <v>282</v>
       </c>
       <c r="O2865" s="28" t="s">
-        <v>3723</v>
-      </c>
-    </row>
-    <row r="2866" spans="1:18" s="28" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+        <v>3718</v>
+      </c>
+    </row>
+    <row r="2866" spans="1:18" s="28" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A2866" s="28" t="s">
         <v>296</v>
       </c>
       <c r="B2866" s="28" t="s">
-        <v>3724</v>
+        <v>3719</v>
       </c>
       <c r="D2866" s="28" t="s">
         <v>404</v>
@@ -74612,18 +74600,18 @@
         <v>282</v>
       </c>
       <c r="O2866" s="28" t="s">
-        <v>3725</v>
-      </c>
-    </row>
-    <row r="2867" spans="1:18" s="28" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+        <v>3720</v>
+      </c>
+    </row>
+    <row r="2867" spans="1:18" s="28" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A2867" s="28" t="s">
         <v>268</v>
       </c>
       <c r="B2867" s="28" t="s">
-        <v>3726</v>
+        <v>3721</v>
       </c>
       <c r="H2867" s="29" t="s">
-        <v>3727</v>
+        <v>3722</v>
       </c>
       <c r="I2867" s="28" t="s">
         <v>121</v>
@@ -74632,12 +74620,12 @@
         <v>282</v>
       </c>
     </row>
-    <row r="2868" spans="1:18" s="28" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2868" spans="1:18" s="28" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A2868" s="28" t="s">
         <v>296</v>
       </c>
       <c r="B2868" s="28" t="s">
-        <v>3728</v>
+        <v>3723</v>
       </c>
       <c r="D2868" s="28" t="s">
         <v>404</v>
@@ -74652,15 +74640,15 @@
         <v>286</v>
       </c>
       <c r="O2868" s="28" t="s">
-        <v>3729</v>
-      </c>
-    </row>
-    <row r="2869" spans="1:18" s="28" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+        <v>3724</v>
+      </c>
+    </row>
+    <row r="2869" spans="1:18" s="28" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A2869" s="28" t="s">
         <v>296</v>
       </c>
       <c r="B2869" s="28" t="s">
-        <v>3730</v>
+        <v>3725</v>
       </c>
       <c r="D2869" s="28" t="s">
         <v>404</v>
@@ -74675,15 +74663,15 @@
         <v>282</v>
       </c>
       <c r="O2869" s="28" t="s">
-        <v>3731</v>
-      </c>
-    </row>
-    <row r="2870" spans="1:18" s="28" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+        <v>3726</v>
+      </c>
+    </row>
+    <row r="2870" spans="1:18" s="28" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A2870" s="28" t="s">
         <v>296</v>
       </c>
       <c r="B2870" s="28" t="s">
-        <v>3732</v>
+        <v>3727</v>
       </c>
       <c r="D2870" s="28" t="s">
         <v>404</v>
@@ -74698,15 +74686,15 @@
         <v>282</v>
       </c>
       <c r="O2870" s="28" t="s">
-        <v>3733</v>
-      </c>
-    </row>
-    <row r="2871" spans="1:18" s="28" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+        <v>3728</v>
+      </c>
+    </row>
+    <row r="2871" spans="1:18" s="28" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A2871" s="28" t="s">
         <v>268</v>
       </c>
       <c r="B2871" s="28" t="s">
-        <v>3734</v>
+        <v>3729</v>
       </c>
       <c r="H2871" s="29" t="s">
         <v>2243</v>
@@ -74718,12 +74706,12 @@
         <v>282</v>
       </c>
     </row>
-    <row r="2872" spans="1:18" s="28" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2872" spans="1:18" s="28" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A2872" s="28" t="s">
         <v>296</v>
       </c>
       <c r="B2872" s="28" t="s">
-        <v>3735</v>
+        <v>3730</v>
       </c>
       <c r="D2872" s="28" t="s">
         <v>404</v>
@@ -74738,7 +74726,7 @@
         <v>286</v>
       </c>
       <c r="O2872" s="28" t="s">
-        <v>3736</v>
+        <v>3731</v>
       </c>
       <c r="Q2872" s="28" t="s">
         <v>2345</v>
@@ -74747,12 +74735,12 @@
         <v>2346</v>
       </c>
     </row>
-    <row r="2873" spans="1:18" s="28" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2873" spans="1:18" s="28" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A2873" s="28" t="s">
         <v>296</v>
       </c>
       <c r="B2873" s="28" t="s">
-        <v>3737</v>
+        <v>3732</v>
       </c>
       <c r="D2873" s="28" t="s">
         <v>404</v>
@@ -74767,7 +74755,7 @@
         <v>282</v>
       </c>
       <c r="O2873" s="28" t="s">
-        <v>3738</v>
+        <v>3733</v>
       </c>
       <c r="P2873" s="12"/>
       <c r="Q2873" s="28" t="s">
@@ -74777,12 +74765,12 @@
         <v>2346</v>
       </c>
     </row>
-    <row r="2874" spans="1:18" s="28" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2874" spans="1:18" s="28" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A2874" s="28" t="s">
         <v>296</v>
       </c>
       <c r="B2874" s="28" t="s">
-        <v>3739</v>
+        <v>3734</v>
       </c>
       <c r="D2874" s="28" t="s">
         <v>404</v>
@@ -74797,7 +74785,7 @@
         <v>282</v>
       </c>
       <c r="O2874" s="12" t="s">
-        <v>3740</v>
+        <v>3735</v>
       </c>
       <c r="P2874" s="12"/>
       <c r="Q2874" s="28" t="s">
@@ -74837,7 +74825,7 @@
         <v>273</v>
       </c>
       <c r="B2877" s="33" t="s">
-        <v>3741</v>
+        <v>3736</v>
       </c>
       <c r="C2877" s="33"/>
       <c r="D2877" s="33"/>
@@ -74845,10 +74833,10 @@
       <c r="F2877" s="33"/>
       <c r="G2877" s="33"/>
       <c r="H2877" s="33" t="s">
-        <v>3742</v>
+        <v>3737</v>
       </c>
       <c r="I2877" s="33" t="s">
-        <v>3742</v>
+        <v>3737</v>
       </c>
       <c r="J2877" s="33"/>
       <c r="K2877" s="33"/>
@@ -74867,7 +74855,7 @@
         <v>382</v>
       </c>
       <c r="B2878" s="28" t="s">
-        <v>3743</v>
+        <v>3738</v>
       </c>
       <c r="D2878" s="24"/>
       <c r="E2878" s="24"/>
@@ -74875,7 +74863,7 @@
       <c r="G2878" s="24"/>
       <c r="H2878" s="24"/>
       <c r="I2878" s="33" t="s">
-        <v>3742</v>
+        <v>3737</v>
       </c>
       <c r="J2878" s="24"/>
       <c r="K2878" s="24"/>
@@ -74892,7 +74880,7 @@
         <v>268</v>
       </c>
       <c r="B2879" s="28" t="s">
-        <v>3744</v>
+        <v>3739</v>
       </c>
       <c r="H2879" s="28" t="s">
         <v>2584</v>
@@ -74910,7 +74898,7 @@
         <v>268</v>
       </c>
       <c r="B2880" s="28" t="s">
-        <v>3745</v>
+        <v>3740</v>
       </c>
       <c r="C2880" s="28"/>
       <c r="D2880" s="28"/>
@@ -74940,7 +74928,7 @@
         <v>268</v>
       </c>
       <c r="B2881" s="28" t="s">
-        <v>3746</v>
+        <v>3741</v>
       </c>
       <c r="C2881" s="28"/>
       <c r="D2881" s="28"/>
@@ -74970,7 +74958,7 @@
         <v>268</v>
       </c>
       <c r="B2882" s="28" t="s">
-        <v>3747</v>
+        <v>3742</v>
       </c>
       <c r="C2882" s="28"/>
       <c r="D2882" s="12"/>
@@ -75020,7 +75008,7 @@
         <v>268</v>
       </c>
       <c r="B2884" s="28" t="s">
-        <v>3748</v>
+        <v>3743</v>
       </c>
       <c r="C2884" s="28"/>
       <c r="D2884" s="28"/>
@@ -75050,7 +75038,7 @@
         <v>296</v>
       </c>
       <c r="B2885" s="28" t="s">
-        <v>3749</v>
+        <v>3744</v>
       </c>
       <c r="C2885" s="28"/>
       <c r="D2885" s="28" t="s">
@@ -75073,7 +75061,7 @@
       </c>
       <c r="N2885" s="28"/>
       <c r="O2885" s="42" t="s">
-        <v>3750</v>
+        <v>3745</v>
       </c>
       <c r="P2885" s="28"/>
       <c r="Q2885" s="28"/>
@@ -75084,7 +75072,7 @@
         <v>296</v>
       </c>
       <c r="B2886" s="28" t="s">
-        <v>3751</v>
+        <v>3746</v>
       </c>
       <c r="C2886" s="28"/>
       <c r="D2886" s="28" t="s">
@@ -75107,7 +75095,7 @@
       </c>
       <c r="N2886" s="28"/>
       <c r="O2886" s="42" t="s">
-        <v>3752</v>
+        <v>3747</v>
       </c>
       <c r="P2886" s="28"/>
       <c r="Q2886" s="28"/>
@@ -75118,7 +75106,7 @@
         <v>296</v>
       </c>
       <c r="B2887" s="28" t="s">
-        <v>3753</v>
+        <v>3748</v>
       </c>
       <c r="C2887" s="28"/>
       <c r="D2887" s="28" t="s">
@@ -75141,7 +75129,7 @@
       </c>
       <c r="N2887" s="28"/>
       <c r="O2887" s="42" t="s">
-        <v>3754</v>
+        <v>3749</v>
       </c>
       <c r="P2887" s="28"/>
       <c r="Q2887" s="28"/>
@@ -75152,7 +75140,7 @@
         <v>268</v>
       </c>
       <c r="B2888" s="28" t="s">
-        <v>3755</v>
+        <v>3750</v>
       </c>
       <c r="C2888" s="28"/>
       <c r="D2888" s="28"/>
@@ -75182,7 +75170,7 @@
         <v>296</v>
       </c>
       <c r="B2889" s="28" t="s">
-        <v>3756</v>
+        <v>3751</v>
       </c>
       <c r="C2889" s="28"/>
       <c r="D2889" s="28" t="s">
@@ -75205,7 +75193,7 @@
       </c>
       <c r="N2889" s="28"/>
       <c r="O2889" s="42" t="s">
-        <v>3757</v>
+        <v>3752</v>
       </c>
       <c r="P2889" s="28"/>
       <c r="Q2889" s="28"/>
@@ -75216,7 +75204,7 @@
         <v>296</v>
       </c>
       <c r="B2890" s="28" t="s">
-        <v>3758</v>
+        <v>3753</v>
       </c>
       <c r="C2890" s="28"/>
       <c r="D2890" s="28" t="s">
@@ -75239,7 +75227,7 @@
       </c>
       <c r="N2890" s="28"/>
       <c r="O2890" s="42" t="s">
-        <v>3759</v>
+        <v>3754</v>
       </c>
       <c r="P2890" s="28"/>
       <c r="Q2890" s="28"/>
@@ -75250,7 +75238,7 @@
         <v>296</v>
       </c>
       <c r="B2891" s="28" t="s">
-        <v>3760</v>
+        <v>3755</v>
       </c>
       <c r="C2891" s="28"/>
       <c r="D2891" s="28" t="s">
@@ -75273,7 +75261,7 @@
       </c>
       <c r="N2891" s="28"/>
       <c r="O2891" s="42" t="s">
-        <v>3761</v>
+        <v>3756</v>
       </c>
       <c r="P2891" s="28"/>
       <c r="Q2891" s="28"/>
@@ -75284,7 +75272,7 @@
         <v>268</v>
       </c>
       <c r="B2892" s="28" t="s">
-        <v>3762</v>
+        <v>3757</v>
       </c>
       <c r="C2892" s="28"/>
       <c r="D2892" s="28"/>
@@ -75314,7 +75302,7 @@
         <v>296</v>
       </c>
       <c r="B2893" s="28" t="s">
-        <v>3763</v>
+        <v>3758</v>
       </c>
       <c r="C2893" s="28"/>
       <c r="D2893" s="28" t="s">
@@ -75337,7 +75325,7 @@
       </c>
       <c r="N2893" s="28"/>
       <c r="O2893" s="42" t="s">
-        <v>3764</v>
+        <v>3759</v>
       </c>
       <c r="P2893" s="28"/>
       <c r="Q2893" s="28"/>
@@ -75348,7 +75336,7 @@
         <v>296</v>
       </c>
       <c r="B2894" s="28" t="s">
-        <v>3765</v>
+        <v>3760</v>
       </c>
       <c r="C2894" s="28"/>
       <c r="D2894" s="28" t="s">
@@ -75371,7 +75359,7 @@
       </c>
       <c r="N2894" s="28"/>
       <c r="O2894" s="42" t="s">
-        <v>3766</v>
+        <v>3761</v>
       </c>
       <c r="P2894" s="28"/>
       <c r="Q2894" s="28"/>
@@ -75382,7 +75370,7 @@
         <v>296</v>
       </c>
       <c r="B2895" s="28" t="s">
-        <v>3767</v>
+        <v>3762</v>
       </c>
       <c r="C2895" s="28"/>
       <c r="D2895" s="28" t="s">
@@ -75405,7 +75393,7 @@
       </c>
       <c r="N2895" s="28"/>
       <c r="O2895" s="42" t="s">
-        <v>3768</v>
+        <v>3763</v>
       </c>
       <c r="P2895" s="28"/>
       <c r="Q2895" s="28"/>
@@ -75416,7 +75404,7 @@
         <v>268</v>
       </c>
       <c r="B2896" s="28" t="s">
-        <v>3769</v>
+        <v>3764</v>
       </c>
       <c r="C2896" s="28"/>
       <c r="D2896" s="28"/>
@@ -75446,7 +75434,7 @@
         <v>296</v>
       </c>
       <c r="B2897" s="28" t="s">
-        <v>3770</v>
+        <v>3765</v>
       </c>
       <c r="C2897" s="28"/>
       <c r="D2897" s="28" t="s">
@@ -75469,7 +75457,7 @@
       </c>
       <c r="N2897" s="28"/>
       <c r="O2897" s="42" t="s">
-        <v>3771</v>
+        <v>3766</v>
       </c>
       <c r="P2897" s="28"/>
       <c r="Q2897" s="28"/>
@@ -75480,7 +75468,7 @@
         <v>296</v>
       </c>
       <c r="B2898" s="28" t="s">
-        <v>3772</v>
+        <v>3767</v>
       </c>
       <c r="C2898" s="28"/>
       <c r="D2898" s="28" t="s">
@@ -75503,7 +75491,7 @@
       </c>
       <c r="N2898" s="28"/>
       <c r="O2898" s="42" t="s">
-        <v>3773</v>
+        <v>3768</v>
       </c>
       <c r="P2898" s="28"/>
       <c r="Q2898" s="28"/>
@@ -75514,7 +75502,7 @@
         <v>296</v>
       </c>
       <c r="B2899" s="28" t="s">
-        <v>3774</v>
+        <v>3769</v>
       </c>
       <c r="C2899" s="28"/>
       <c r="D2899" s="28" t="s">
@@ -75537,7 +75525,7 @@
       </c>
       <c r="N2899" s="28"/>
       <c r="O2899" s="42" t="s">
-        <v>3775</v>
+        <v>3770</v>
       </c>
       <c r="P2899" s="28"/>
       <c r="Q2899" s="28"/>
@@ -75548,7 +75536,7 @@
         <v>268</v>
       </c>
       <c r="B2900" s="28" t="s">
-        <v>3776</v>
+        <v>3771</v>
       </c>
       <c r="C2900" s="28"/>
       <c r="D2900" s="28"/>
@@ -75578,7 +75566,7 @@
         <v>296</v>
       </c>
       <c r="B2901" s="28" t="s">
-        <v>3777</v>
+        <v>3772</v>
       </c>
       <c r="C2901" s="28"/>
       <c r="D2901" s="28" t="s">
@@ -75601,7 +75589,7 @@
       </c>
       <c r="N2901" s="28"/>
       <c r="O2901" s="42" t="s">
-        <v>3778</v>
+        <v>3773</v>
       </c>
       <c r="P2901" s="28"/>
       <c r="Q2901" s="28"/>
@@ -75612,7 +75600,7 @@
         <v>296</v>
       </c>
       <c r="B2902" s="28" t="s">
-        <v>3779</v>
+        <v>3774</v>
       </c>
       <c r="C2902" s="28"/>
       <c r="D2902" s="28" t="s">
@@ -75635,7 +75623,7 @@
       </c>
       <c r="N2902" s="28"/>
       <c r="O2902" s="42" t="s">
-        <v>3780</v>
+        <v>3775</v>
       </c>
       <c r="P2902" s="28"/>
       <c r="Q2902" s="28"/>
@@ -75646,7 +75634,7 @@
         <v>296</v>
       </c>
       <c r="B2903" s="28" t="s">
-        <v>3781</v>
+        <v>3776</v>
       </c>
       <c r="C2903" s="28"/>
       <c r="D2903" s="28" t="s">
@@ -75669,7 +75657,7 @@
       </c>
       <c r="N2903" s="28"/>
       <c r="O2903" s="42" t="s">
-        <v>3782</v>
+        <v>3777</v>
       </c>
       <c r="P2903" s="28"/>
       <c r="Q2903" s="28"/>
@@ -75680,7 +75668,7 @@
         <v>268</v>
       </c>
       <c r="B2904" s="28" t="s">
-        <v>3783</v>
+        <v>3778</v>
       </c>
       <c r="C2904" s="28"/>
       <c r="D2904" s="28"/>
@@ -75710,7 +75698,7 @@
         <v>296</v>
       </c>
       <c r="B2905" s="28" t="s">
-        <v>3784</v>
+        <v>3779</v>
       </c>
       <c r="C2905" s="28"/>
       <c r="D2905" s="28" t="s">
@@ -75733,7 +75721,7 @@
       </c>
       <c r="N2905" s="28"/>
       <c r="O2905" s="42" t="s">
-        <v>3785</v>
+        <v>3780</v>
       </c>
       <c r="P2905" s="28"/>
       <c r="Q2905" s="28"/>
@@ -75744,7 +75732,7 @@
         <v>296</v>
       </c>
       <c r="B2906" s="28" t="s">
-        <v>3786</v>
+        <v>3781</v>
       </c>
       <c r="C2906" s="28"/>
       <c r="D2906" s="28" t="s">
@@ -75767,7 +75755,7 @@
       </c>
       <c r="N2906" s="28"/>
       <c r="O2906" s="42" t="s">
-        <v>3787</v>
+        <v>3782</v>
       </c>
       <c r="P2906" s="28"/>
       <c r="Q2906" s="28"/>
@@ -75778,7 +75766,7 @@
         <v>296</v>
       </c>
       <c r="B2907" s="28" t="s">
-        <v>3788</v>
+        <v>3783</v>
       </c>
       <c r="C2907" s="28"/>
       <c r="D2907" s="28" t="s">
@@ -75801,7 +75789,7 @@
       </c>
       <c r="N2907" s="28"/>
       <c r="O2907" s="42" t="s">
-        <v>3789</v>
+        <v>3784</v>
       </c>
       <c r="P2907" s="28"/>
       <c r="Q2907" s="28"/>
@@ -75812,7 +75800,7 @@
         <v>268</v>
       </c>
       <c r="B2908" s="28" t="s">
-        <v>3790</v>
+        <v>3785</v>
       </c>
       <c r="C2908" s="28"/>
       <c r="D2908" s="28"/>
@@ -75842,7 +75830,7 @@
         <v>296</v>
       </c>
       <c r="B2909" s="28" t="s">
-        <v>3791</v>
+        <v>3786</v>
       </c>
       <c r="C2909" s="28"/>
       <c r="D2909" s="28" t="s">
@@ -75865,7 +75853,7 @@
       </c>
       <c r="N2909" s="28"/>
       <c r="O2909" s="42" t="s">
-        <v>3792</v>
+        <v>3787</v>
       </c>
       <c r="P2909" s="28"/>
       <c r="Q2909" s="28" t="s">
@@ -75880,7 +75868,7 @@
         <v>296</v>
       </c>
       <c r="B2910" s="28" t="s">
-        <v>3793</v>
+        <v>3788</v>
       </c>
       <c r="C2910" s="28"/>
       <c r="D2910" s="28" t="s">
@@ -75903,7 +75891,7 @@
       </c>
       <c r="N2910" s="28"/>
       <c r="O2910" s="42" t="s">
-        <v>3794</v>
+        <v>3789</v>
       </c>
       <c r="P2910" s="28"/>
       <c r="Q2910" s="28" t="s">
@@ -75918,7 +75906,7 @@
         <v>296</v>
       </c>
       <c r="B2911" s="28" t="s">
-        <v>3795</v>
+        <v>3790</v>
       </c>
       <c r="C2911" s="28"/>
       <c r="D2911" s="28" t="s">
@@ -75941,7 +75929,7 @@
       </c>
       <c r="N2911" s="28"/>
       <c r="O2911" s="42" t="s">
-        <v>3796</v>
+        <v>3791</v>
       </c>
       <c r="P2911" s="28"/>
       <c r="Q2911" s="28" t="s">
@@ -76026,7 +76014,7 @@
         <v>273</v>
       </c>
       <c r="B2916" s="31" t="s">
-        <v>3797</v>
+        <v>3792</v>
       </c>
       <c r="C2916" s="31"/>
       <c r="D2916" s="31"/>
@@ -76034,16 +76022,16 @@
       <c r="F2916" s="31"/>
       <c r="G2916" s="31"/>
       <c r="H2916" s="52" t="s">
-        <v>3798</v>
+        <v>3793</v>
       </c>
       <c r="I2916" s="52" t="s">
-        <v>3798</v>
+        <v>3793</v>
       </c>
       <c r="J2916" s="31"/>
       <c r="K2916" s="31"/>
       <c r="L2916" s="31"/>
       <c r="M2916" s="31" t="s">
-        <v>3799</v>
+        <v>3794</v>
       </c>
       <c r="N2916" s="31"/>
       <c r="O2916" s="31"/>
@@ -76067,7 +76055,7 @@
         <v>384</v>
       </c>
       <c r="I2917" s="36" t="s">
-        <v>3798</v>
+        <v>3793</v>
       </c>
       <c r="J2917" s="28"/>
       <c r="K2917" s="28"/>
@@ -76164,7 +76152,7 @@
         <v>273</v>
       </c>
       <c r="B2922" s="24" t="s">
-        <v>3800</v>
+        <v>3795</v>
       </c>
       <c r="H2922" s="24"/>
       <c r="J2922" s="24" t="s">
@@ -76179,7 +76167,7 @@
         <v>268</v>
       </c>
       <c r="B2923" s="24" t="s">
-        <v>3801</v>
+        <v>3796</v>
       </c>
       <c r="H2923" s="24" t="s">
         <v>1418</v>
@@ -76202,7 +76190,7 @@
         <v>296</v>
       </c>
       <c r="B2924" s="24" t="s">
-        <v>3802</v>
+        <v>3797</v>
       </c>
       <c r="H2924" s="24" t="s">
         <v>403</v>
@@ -76228,7 +76216,7 @@
         <v>296</v>
       </c>
       <c r="B2925" s="24" t="s">
-        <v>3803</v>
+        <v>3798</v>
       </c>
       <c r="H2925" s="24" t="s">
         <v>407</v>
@@ -76254,7 +76242,7 @@
         <v>296</v>
       </c>
       <c r="B2926" s="24" t="s">
-        <v>3804</v>
+        <v>3799</v>
       </c>
       <c r="D2926" s="24" t="b">
         <f>TRUE()</f>
@@ -76279,7 +76267,7 @@
         <v>1427</v>
       </c>
       <c r="O2926" s="24" t="s">
-        <v>3805</v>
+        <v>3800</v>
       </c>
     </row>
     <row r="2927" spans="1:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
@@ -76293,7 +76281,7 @@
         <v>273</v>
       </c>
       <c r="B2928" s="24" t="s">
-        <v>3806</v>
+        <v>3801</v>
       </c>
       <c r="H2928" s="24"/>
       <c r="J2928" s="24" t="s">
@@ -76308,7 +76296,7 @@
         <v>268</v>
       </c>
       <c r="B2929" s="24" t="s">
-        <v>3807</v>
+        <v>3802</v>
       </c>
       <c r="H2929" s="24" t="s">
         <v>1432</v>
@@ -76331,7 +76319,7 @@
         <v>296</v>
       </c>
       <c r="B2930" s="24" t="s">
-        <v>3808</v>
+        <v>3803</v>
       </c>
       <c r="H2930" s="24" t="s">
         <v>403</v>
@@ -76357,7 +76345,7 @@
         <v>296</v>
       </c>
       <c r="B2931" s="24" t="s">
-        <v>3809</v>
+        <v>3804</v>
       </c>
       <c r="H2931" s="24" t="s">
         <v>407</v>
@@ -76383,7 +76371,7 @@
         <v>296</v>
       </c>
       <c r="B2932" s="24" t="s">
-        <v>3810</v>
+        <v>3805</v>
       </c>
       <c r="D2932" s="24" t="b">
         <f>TRUE()</f>
@@ -76408,7 +76396,7 @@
         <v>1427</v>
       </c>
       <c r="O2932" s="24" t="s">
-        <v>3811</v>
+        <v>3806</v>
       </c>
     </row>
     <row r="2933" spans="1:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
@@ -76422,7 +76410,7 @@
         <v>273</v>
       </c>
       <c r="B2934" s="24" t="s">
-        <v>3812</v>
+        <v>3807</v>
       </c>
       <c r="H2934" s="24"/>
       <c r="J2934" s="24" t="s">
@@ -76437,7 +76425,7 @@
         <v>268</v>
       </c>
       <c r="B2935" s="24" t="s">
-        <v>3813</v>
+        <v>3808</v>
       </c>
       <c r="H2935" s="24" t="s">
         <v>1441</v>
@@ -76460,7 +76448,7 @@
         <v>296</v>
       </c>
       <c r="B2936" s="24" t="s">
-        <v>3814</v>
+        <v>3809</v>
       </c>
       <c r="H2936" s="24" t="s">
         <v>403</v>
@@ -76486,7 +76474,7 @@
         <v>296</v>
       </c>
       <c r="B2937" s="24" t="s">
-        <v>3815</v>
+        <v>3810</v>
       </c>
       <c r="H2937" s="24" t="s">
         <v>407</v>
@@ -76512,7 +76500,7 @@
         <v>296</v>
       </c>
       <c r="B2938" s="24" t="s">
-        <v>3816</v>
+        <v>3811</v>
       </c>
       <c r="D2938" s="24" t="b">
         <f>TRUE()</f>
@@ -76537,7 +76525,7 @@
         <v>1427</v>
       </c>
       <c r="O2938" s="24" t="s">
-        <v>3817</v>
+        <v>3812</v>
       </c>
     </row>
     <row r="2939" spans="1:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
@@ -76551,7 +76539,7 @@
         <v>273</v>
       </c>
       <c r="B2940" s="24" t="s">
-        <v>3818</v>
+        <v>3813</v>
       </c>
       <c r="H2940" s="24"/>
       <c r="J2940" s="24" t="s">
@@ -76566,7 +76554,7 @@
         <v>268</v>
       </c>
       <c r="B2941" s="24" t="s">
-        <v>3819</v>
+        <v>3814</v>
       </c>
       <c r="H2941" s="24" t="s">
         <v>1450</v>
@@ -76589,7 +76577,7 @@
         <v>296</v>
       </c>
       <c r="B2942" s="24" t="s">
-        <v>3820</v>
+        <v>3815</v>
       </c>
       <c r="H2942" s="24" t="s">
         <v>403</v>
@@ -76615,7 +76603,7 @@
         <v>296</v>
       </c>
       <c r="B2943" s="24" t="s">
-        <v>3821</v>
+        <v>3816</v>
       </c>
       <c r="H2943" s="24" t="s">
         <v>407</v>
@@ -76641,7 +76629,7 @@
         <v>296</v>
       </c>
       <c r="B2944" s="24" t="s">
-        <v>3822</v>
+        <v>3817</v>
       </c>
       <c r="D2944" s="24" t="b">
         <f>TRUE()</f>
@@ -76666,7 +76654,7 @@
         <v>1458</v>
       </c>
       <c r="O2944" s="24" t="s">
-        <v>3823</v>
+        <v>3818</v>
       </c>
     </row>
     <row r="2945" spans="1:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
@@ -76680,7 +76668,7 @@
         <v>273</v>
       </c>
       <c r="B2946" s="24" t="s">
-        <v>3824</v>
+        <v>3819</v>
       </c>
       <c r="H2946" s="24"/>
       <c r="J2946" s="24" t="s">
@@ -76695,7 +76683,7 @@
         <v>268</v>
       </c>
       <c r="B2947" s="24" t="s">
-        <v>3825</v>
+        <v>3820</v>
       </c>
       <c r="H2947" s="24" t="s">
         <v>1463</v>
@@ -76718,7 +76706,7 @@
         <v>296</v>
       </c>
       <c r="B2948" s="24" t="s">
-        <v>3826</v>
+        <v>3821</v>
       </c>
       <c r="H2948" s="24" t="s">
         <v>403</v>
@@ -76744,7 +76732,7 @@
         <v>296</v>
       </c>
       <c r="B2949" s="24" t="s">
-        <v>3827</v>
+        <v>3822</v>
       </c>
       <c r="H2949" s="24" t="s">
         <v>407</v>
@@ -76770,7 +76758,7 @@
         <v>296</v>
       </c>
       <c r="B2950" s="24" t="s">
-        <v>3828</v>
+        <v>3823</v>
       </c>
       <c r="D2950" s="24" t="b">
         <f>TRUE()</f>
@@ -76795,7 +76783,7 @@
         <v>1471</v>
       </c>
       <c r="O2950" s="24" t="s">
-        <v>3829</v>
+        <v>3824</v>
       </c>
     </row>
     <row r="2951" spans="1:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
@@ -76809,7 +76797,7 @@
         <v>273</v>
       </c>
       <c r="B2952" s="24" t="s">
-        <v>3830</v>
+        <v>3825</v>
       </c>
       <c r="H2952" s="24"/>
       <c r="J2952" s="24" t="s">
@@ -76824,7 +76812,7 @@
         <v>268</v>
       </c>
       <c r="B2953" s="24" t="s">
-        <v>3831</v>
+        <v>3826</v>
       </c>
       <c r="H2953" s="24" t="s">
         <v>1476</v>
@@ -76847,7 +76835,7 @@
         <v>296</v>
       </c>
       <c r="B2954" s="24" t="s">
-        <v>3832</v>
+        <v>3827</v>
       </c>
       <c r="H2954" s="24" t="s">
         <v>403</v>
@@ -76873,7 +76861,7 @@
         <v>296</v>
       </c>
       <c r="B2955" s="24" t="s">
-        <v>3833</v>
+        <v>3828</v>
       </c>
       <c r="H2955" s="24" t="s">
         <v>407</v>
@@ -76899,7 +76887,7 @@
         <v>296</v>
       </c>
       <c r="B2956" s="24" t="s">
-        <v>3834</v>
+        <v>3829</v>
       </c>
       <c r="D2956" s="24" t="b">
         <f>TRUE()</f>
@@ -76924,7 +76912,7 @@
         <v>1484</v>
       </c>
       <c r="O2956" s="24" t="s">
-        <v>3835</v>
+        <v>3830</v>
       </c>
     </row>
     <row r="2957" spans="1:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
@@ -76938,7 +76926,7 @@
         <v>273</v>
       </c>
       <c r="B2958" s="24" t="s">
-        <v>3836</v>
+        <v>3831</v>
       </c>
       <c r="H2958" s="24"/>
       <c r="J2958" s="24" t="s">
@@ -76953,7 +76941,7 @@
         <v>268</v>
       </c>
       <c r="B2959" s="24" t="s">
-        <v>3837</v>
+        <v>3832</v>
       </c>
       <c r="H2959" s="24" t="s">
         <v>1489</v>
@@ -76976,7 +76964,7 @@
         <v>296</v>
       </c>
       <c r="B2960" s="24" t="s">
-        <v>3838</v>
+        <v>3833</v>
       </c>
       <c r="H2960" s="24" t="s">
         <v>403</v>
@@ -77002,7 +76990,7 @@
         <v>296</v>
       </c>
       <c r="B2961" s="24" t="s">
-        <v>3839</v>
+        <v>3834</v>
       </c>
       <c r="H2961" s="24" t="s">
         <v>407</v>
@@ -77028,7 +77016,7 @@
         <v>296</v>
       </c>
       <c r="B2962" s="24" t="s">
-        <v>3840</v>
+        <v>3835</v>
       </c>
       <c r="D2962" s="24" t="b">
         <f>TRUE()</f>
@@ -77053,7 +77041,7 @@
         <v>1497</v>
       </c>
       <c r="O2962" s="24" t="s">
-        <v>3841</v>
+        <v>3836</v>
       </c>
     </row>
     <row r="2963" spans="1:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
@@ -77067,7 +77055,7 @@
         <v>273</v>
       </c>
       <c r="B2964" s="24" t="s">
-        <v>3842</v>
+        <v>3837</v>
       </c>
       <c r="H2964" s="24"/>
       <c r="J2964" s="24" t="s">
@@ -77082,7 +77070,7 @@
         <v>268</v>
       </c>
       <c r="B2965" s="24" t="s">
-        <v>3843</v>
+        <v>3838</v>
       </c>
       <c r="H2965" s="24" t="s">
         <v>1502</v>
@@ -77105,7 +77093,7 @@
         <v>296</v>
       </c>
       <c r="B2966" s="24" t="s">
-        <v>3844</v>
+        <v>3839</v>
       </c>
       <c r="H2966" s="24" t="s">
         <v>403</v>
@@ -77131,7 +77119,7 @@
         <v>296</v>
       </c>
       <c r="B2967" s="24" t="s">
-        <v>3845</v>
+        <v>3840</v>
       </c>
       <c r="H2967" s="24" t="s">
         <v>407</v>
@@ -77157,7 +77145,7 @@
         <v>296</v>
       </c>
       <c r="B2968" s="24" t="s">
-        <v>3846</v>
+        <v>3841</v>
       </c>
       <c r="D2968" s="24" t="b">
         <f>TRUE()</f>
@@ -77182,7 +77170,7 @@
         <v>1458</v>
       </c>
       <c r="O2968" s="24" t="s">
-        <v>3847</v>
+        <v>3842</v>
       </c>
     </row>
     <row r="2969" spans="1:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
@@ -77196,7 +77184,7 @@
         <v>273</v>
       </c>
       <c r="B2970" s="24" t="s">
-        <v>3848</v>
+        <v>3843</v>
       </c>
       <c r="H2970" s="24"/>
       <c r="J2970" s="24" t="s">
@@ -77211,7 +77199,7 @@
         <v>268</v>
       </c>
       <c r="B2971" s="24" t="s">
-        <v>3849</v>
+        <v>3844</v>
       </c>
       <c r="H2971" s="24" t="s">
         <v>1512</v>
@@ -77234,7 +77222,7 @@
         <v>296</v>
       </c>
       <c r="B2972" s="24" t="s">
-        <v>3850</v>
+        <v>3845</v>
       </c>
       <c r="H2972" s="24" t="s">
         <v>403</v>
@@ -77260,7 +77248,7 @@
         <v>296</v>
       </c>
       <c r="B2973" s="24" t="s">
-        <v>3851</v>
+        <v>3846</v>
       </c>
       <c r="H2973" s="24" t="s">
         <v>407</v>
@@ -77286,7 +77274,7 @@
         <v>296</v>
       </c>
       <c r="B2974" s="24" t="s">
-        <v>3852</v>
+        <v>3847</v>
       </c>
       <c r="D2974" s="24" t="b">
         <f>TRUE()</f>
@@ -77311,7 +77299,7 @@
         <v>1471</v>
       </c>
       <c r="O2974" s="24" t="s">
-        <v>3853</v>
+        <v>3848</v>
       </c>
     </row>
     <row r="2975" spans="1:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
@@ -77325,7 +77313,7 @@
         <v>273</v>
       </c>
       <c r="B2976" s="24" t="s">
-        <v>3854</v>
+        <v>3849</v>
       </c>
       <c r="H2976" s="24"/>
       <c r="J2976" s="24" t="s">
@@ -77340,7 +77328,7 @@
         <v>268</v>
       </c>
       <c r="B2977" s="24" t="s">
-        <v>3855</v>
+        <v>3850</v>
       </c>
       <c r="H2977" s="24" t="s">
         <v>1521</v>
@@ -77363,7 +77351,7 @@
         <v>296</v>
       </c>
       <c r="B2978" s="24" t="s">
-        <v>3856</v>
+        <v>3851</v>
       </c>
       <c r="H2978" s="24" t="s">
         <v>403</v>
@@ -77389,7 +77377,7 @@
         <v>296</v>
       </c>
       <c r="B2979" s="24" t="s">
-        <v>3857</v>
+        <v>3852</v>
       </c>
       <c r="H2979" s="24" t="s">
         <v>407</v>
@@ -77415,7 +77403,7 @@
         <v>296</v>
       </c>
       <c r="B2980" s="24" t="s">
-        <v>3858</v>
+        <v>3853</v>
       </c>
       <c r="D2980" s="24" t="b">
         <f>TRUE()</f>
@@ -77440,7 +77428,7 @@
         <v>1484</v>
       </c>
       <c r="O2980" s="24" t="s">
-        <v>3859</v>
+        <v>3854</v>
       </c>
     </row>
     <row r="2981" spans="1:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
@@ -77454,7 +77442,7 @@
         <v>273</v>
       </c>
       <c r="B2982" s="24" t="s">
-        <v>3860</v>
+        <v>3855</v>
       </c>
       <c r="H2982" s="24"/>
       <c r="J2982" s="24" t="s">
@@ -77469,7 +77457,7 @@
         <v>268</v>
       </c>
       <c r="B2983" s="24" t="s">
-        <v>3861</v>
+        <v>3856</v>
       </c>
       <c r="H2983" s="24" t="s">
         <v>1530</v>
@@ -77492,7 +77480,7 @@
         <v>296</v>
       </c>
       <c r="B2984" s="24" t="s">
-        <v>3862</v>
+        <v>3857</v>
       </c>
       <c r="H2984" s="24" t="s">
         <v>403</v>
@@ -77518,7 +77506,7 @@
         <v>296</v>
       </c>
       <c r="B2985" s="24" t="s">
-        <v>3863</v>
+        <v>3858</v>
       </c>
       <c r="H2985" s="24" t="s">
         <v>407</v>
@@ -77544,7 +77532,7 @@
         <v>296</v>
       </c>
       <c r="B2986" s="24" t="s">
-        <v>3864</v>
+        <v>3859</v>
       </c>
       <c r="D2986" s="24" t="b">
         <f>TRUE()</f>
@@ -77569,7 +77557,7 @@
         <v>1497</v>
       </c>
       <c r="O2986" s="24" t="s">
-        <v>3865</v>
+        <v>3860</v>
       </c>
     </row>
     <row r="2987" spans="1:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
@@ -77583,7 +77571,7 @@
         <v>273</v>
       </c>
       <c r="B2988" s="24" t="s">
-        <v>3866</v>
+        <v>3861</v>
       </c>
       <c r="H2988" s="24"/>
       <c r="J2988" s="24" t="s">
@@ -77598,7 +77586,7 @@
         <v>268</v>
       </c>
       <c r="B2989" s="24" t="s">
-        <v>3867</v>
+        <v>3862</v>
       </c>
       <c r="C2989" s="24"/>
       <c r="D2989" s="24"/>
@@ -77632,7 +77620,7 @@
         <v>296</v>
       </c>
       <c r="B2990" s="24" t="s">
-        <v>3868</v>
+        <v>3863</v>
       </c>
       <c r="H2990" s="24" t="s">
         <v>403</v>
@@ -77658,7 +77646,7 @@
         <v>296</v>
       </c>
       <c r="B2991" s="24" t="s">
-        <v>3869</v>
+        <v>3864</v>
       </c>
       <c r="C2991" s="24"/>
       <c r="D2991" s="24"/>
@@ -77694,7 +77682,7 @@
         <v>296</v>
       </c>
       <c r="B2992" s="24" t="s">
-        <v>3870</v>
+        <v>3865</v>
       </c>
       <c r="D2992" s="24" t="b">
         <f>TRUE()</f>
@@ -77719,7 +77707,7 @@
         <v>1458</v>
       </c>
       <c r="O2992" s="24" t="s">
-        <v>3871</v>
+        <v>3866</v>
       </c>
     </row>
     <row r="2993" spans="1:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
@@ -77733,7 +77721,7 @@
         <v>273</v>
       </c>
       <c r="B2994" s="24" t="s">
-        <v>3872</v>
+        <v>3867</v>
       </c>
       <c r="H2994" s="24"/>
       <c r="J2994" s="24" t="s">
@@ -77748,7 +77736,7 @@
         <v>268</v>
       </c>
       <c r="B2995" s="24" t="s">
-        <v>3873</v>
+        <v>3868</v>
       </c>
       <c r="H2995" s="24" t="s">
         <v>1548</v>
@@ -77771,7 +77759,7 @@
         <v>296</v>
       </c>
       <c r="B2996" s="24" t="s">
-        <v>3874</v>
+        <v>3869</v>
       </c>
       <c r="H2996" s="24" t="s">
         <v>403</v>
@@ -77797,7 +77785,7 @@
         <v>296</v>
       </c>
       <c r="B2997" s="24" t="s">
-        <v>3875</v>
+        <v>3870</v>
       </c>
       <c r="C2997" s="24"/>
       <c r="D2997" s="24"/>
@@ -77833,7 +77821,7 @@
         <v>296</v>
       </c>
       <c r="B2998" s="24" t="s">
-        <v>3876</v>
+        <v>3871</v>
       </c>
       <c r="C2998" s="24"/>
       <c r="D2998" s="24" t="b">
@@ -77863,7 +77851,7 @@
         <v>1471</v>
       </c>
       <c r="O2998" s="24" t="s">
-        <v>3877</v>
+        <v>3872</v>
       </c>
       <c r="P2998" s="24"/>
       <c r="Q2998" s="24"/>
@@ -77880,7 +77868,7 @@
         <v>273</v>
       </c>
       <c r="B3000" s="24" t="s">
-        <v>3878</v>
+        <v>3873</v>
       </c>
       <c r="H3000" s="24"/>
       <c r="J3000" s="24" t="s">
@@ -77895,7 +77883,7 @@
         <v>268</v>
       </c>
       <c r="B3001" s="24" t="s">
-        <v>3879</v>
+        <v>3874</v>
       </c>
       <c r="C3001" s="24"/>
       <c r="D3001" s="24"/>
@@ -77929,7 +77917,7 @@
         <v>296</v>
       </c>
       <c r="B3002" s="24" t="s">
-        <v>3880</v>
+        <v>3875</v>
       </c>
       <c r="H3002" s="24" t="s">
         <v>403</v>
@@ -77955,7 +77943,7 @@
         <v>296</v>
       </c>
       <c r="B3003" s="24" t="s">
-        <v>3881</v>
+        <v>3876</v>
       </c>
       <c r="C3003" s="24"/>
       <c r="D3003" s="24"/>
@@ -77991,7 +77979,7 @@
         <v>296</v>
       </c>
       <c r="B3004" s="24" t="s">
-        <v>3882</v>
+        <v>3877</v>
       </c>
       <c r="D3004" s="24" t="b">
         <f>TRUE()</f>
@@ -78016,7 +78004,7 @@
         <v>1484</v>
       </c>
       <c r="O3004" s="24" t="s">
-        <v>3883</v>
+        <v>3878</v>
       </c>
     </row>
     <row r="3005" spans="1:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
@@ -78030,7 +78018,7 @@
         <v>273</v>
       </c>
       <c r="B3006" s="24" t="s">
-        <v>3884</v>
+        <v>3879</v>
       </c>
       <c r="H3006" s="24"/>
       <c r="J3006" s="24" t="s">
@@ -78045,7 +78033,7 @@
         <v>268</v>
       </c>
       <c r="B3007" s="24" t="s">
-        <v>3885</v>
+        <v>3880</v>
       </c>
       <c r="H3007" s="24" t="s">
         <v>1566</v>
@@ -78068,7 +78056,7 @@
         <v>296</v>
       </c>
       <c r="B3008" s="24" t="s">
-        <v>3886</v>
+        <v>3881</v>
       </c>
       <c r="H3008" s="24" t="s">
         <v>403</v>
@@ -78094,7 +78082,7 @@
         <v>296</v>
       </c>
       <c r="B3009" s="24" t="s">
-        <v>3887</v>
+        <v>3882</v>
       </c>
       <c r="H3009" s="24" t="s">
         <v>407</v>
@@ -78120,7 +78108,7 @@
         <v>296</v>
       </c>
       <c r="B3010" s="24" t="s">
-        <v>3888</v>
+        <v>3883</v>
       </c>
       <c r="D3010" s="24" t="b">
         <f>TRUE()</f>
@@ -78145,7 +78133,7 @@
         <v>1497</v>
       </c>
       <c r="O3010" s="24" t="s">
-        <v>3889</v>
+        <v>3884</v>
       </c>
     </row>
     <row r="3011" spans="1:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
@@ -78188,7 +78176,7 @@
         <v>296</v>
       </c>
       <c r="B3014" s="24" t="s">
-        <v>3890</v>
+        <v>3885</v>
       </c>
       <c r="D3014" s="24" t="b">
         <f>TRUE()</f>
@@ -78207,7 +78195,7 @@
         <v>1576</v>
       </c>
       <c r="O3014" s="24" t="s">
-        <v>3891</v>
+        <v>3886</v>
       </c>
     </row>
     <row r="3015" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
@@ -78215,7 +78203,7 @@
         <v>296</v>
       </c>
       <c r="B3015" s="24" t="s">
-        <v>3892</v>
+        <v>3887</v>
       </c>
       <c r="D3015" s="24" t="b">
         <f>TRUE()</f>
@@ -78234,7 +78222,7 @@
         <v>1579</v>
       </c>
       <c r="O3015" s="24" t="s">
-        <v>3893</v>
+        <v>3888</v>
       </c>
     </row>
     <row r="3016" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
@@ -78242,7 +78230,7 @@
         <v>296</v>
       </c>
       <c r="B3016" s="24" t="s">
-        <v>3894</v>
+        <v>3889</v>
       </c>
       <c r="D3016" s="24" t="b">
         <f>TRUE()</f>
@@ -78261,7 +78249,7 @@
         <v>1582</v>
       </c>
       <c r="O3016" s="24" t="s">
-        <v>3895</v>
+        <v>3890</v>
       </c>
     </row>
     <row r="3017" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
@@ -78301,7 +78289,7 @@
         <v>273</v>
       </c>
       <c r="B3020" s="31" t="s">
-        <v>3896</v>
+        <v>3891</v>
       </c>
       <c r="C3020" s="31"/>
       <c r="D3020" s="31"/>
@@ -78309,16 +78297,16 @@
       <c r="F3020" s="31"/>
       <c r="G3020" s="31"/>
       <c r="H3020" s="31" t="s">
-        <v>3897</v>
+        <v>3892</v>
       </c>
       <c r="I3020" s="31" t="s">
-        <v>3897</v>
+        <v>3892</v>
       </c>
       <c r="J3020" s="31"/>
       <c r="K3020" s="31"/>
       <c r="L3020" s="31"/>
       <c r="M3020" s="31" t="s">
-        <v>3898</v>
+        <v>3893</v>
       </c>
       <c r="N3020" s="31"/>
       <c r="O3020" s="31"/>
@@ -78342,7 +78330,7 @@
         <v>384</v>
       </c>
       <c r="I3021" s="31" t="s">
-        <v>3897</v>
+        <v>3892</v>
       </c>
       <c r="J3021" s="28"/>
       <c r="K3021" s="28"/>
@@ -78362,27 +78350,27 @@
         <v>268</v>
       </c>
       <c r="H3022" s="24" t="s">
-        <v>3899</v>
+        <v>3894</v>
       </c>
       <c r="I3022" s="24" t="s">
-        <v>3900</v>
+        <v>3895</v>
       </c>
       <c r="M3022" s="24" t="s">
-        <v>3898</v>
+        <v>3893</v>
       </c>
     </row>
     <row r="3023" spans="1:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3023" s="38" t="s">
-        <v>3901</v>
+        <v>3896</v>
       </c>
       <c r="B3023" s="24" t="s">
-        <v>3902</v>
+        <v>3897</v>
       </c>
       <c r="H3023" s="25" t="s">
-        <v>3903</v>
+        <v>3898</v>
       </c>
       <c r="I3023" s="24" t="s">
-        <v>3904</v>
+        <v>3899</v>
       </c>
       <c r="J3023" s="54" t="s">
         <v>404</v>
@@ -78394,7 +78382,7 @@
         <v>286</v>
       </c>
       <c r="Q3023" s="24" t="s">
-        <v>3905</v>
+        <v>3900</v>
       </c>
       <c r="R3023" s="24" t="s">
         <v>648</v>
@@ -78402,16 +78390,16 @@
     </row>
     <row r="3024" spans="1:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3024" s="38" t="s">
+        <v>3896</v>
+      </c>
+      <c r="B3024" s="24" t="s">
         <v>3901</v>
       </c>
-      <c r="B3024" s="24" t="s">
-        <v>3906</v>
-      </c>
       <c r="H3024" s="25" t="s">
-        <v>3907</v>
+        <v>3902</v>
       </c>
       <c r="I3024" s="24" t="s">
-        <v>3908</v>
+        <v>3903</v>
       </c>
       <c r="J3024" s="54" t="s">
         <v>404</v>
@@ -78425,16 +78413,16 @@
     </row>
     <row r="3025" spans="1:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3025" s="38" t="s">
-        <v>3901</v>
+        <v>3896</v>
       </c>
       <c r="B3025" s="24" t="s">
-        <v>3909</v>
+        <v>3904</v>
       </c>
       <c r="H3025" s="25" t="s">
-        <v>3910</v>
+        <v>3905</v>
       </c>
       <c r="I3025" s="24" t="s">
-        <v>3911</v>
+        <v>3906</v>
       </c>
       <c r="J3025" s="54" t="s">
         <v>404</v>
@@ -78448,16 +78436,16 @@
     </row>
     <row r="3026" spans="1:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3026" s="38" t="s">
-        <v>3901</v>
+        <v>3896</v>
       </c>
       <c r="B3026" s="24" t="s">
-        <v>3912</v>
+        <v>3907</v>
       </c>
       <c r="H3026" s="25" t="s">
-        <v>3913</v>
+        <v>3908</v>
       </c>
       <c r="I3026" s="24" t="s">
-        <v>3914</v>
+        <v>3909</v>
       </c>
       <c r="J3026" s="54" t="s">
         <v>404</v>
@@ -78474,16 +78462,16 @@
     </row>
     <row r="3027" spans="1:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3027" s="38" t="s">
-        <v>3915</v>
+        <v>3910</v>
       </c>
       <c r="B3027" s="24" t="s">
-        <v>3916</v>
+        <v>3911</v>
       </c>
       <c r="H3027" s="25" t="s">
-        <v>3917</v>
+        <v>3912</v>
       </c>
       <c r="I3027" s="24" t="s">
-        <v>3918</v>
+        <v>3913</v>
       </c>
       <c r="J3027" s="54" t="s">
         <v>404</v>
@@ -78495,7 +78483,7 @@
         <v>286</v>
       </c>
       <c r="N3027" s="24" t="s">
-        <v>3919</v>
+        <v>3914</v>
       </c>
     </row>
     <row r="3028" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.25">
@@ -78529,7 +78517,7 @@
         <v>273</v>
       </c>
       <c r="B3030" s="31" t="s">
-        <v>3896</v>
+        <v>3891</v>
       </c>
       <c r="C3030" s="31"/>
       <c r="D3030" s="31"/>
@@ -78537,16 +78525,16 @@
       <c r="F3030" s="31"/>
       <c r="G3030" s="31"/>
       <c r="H3030" s="31" t="s">
-        <v>3920</v>
+        <v>3915</v>
       </c>
       <c r="I3030" s="31" t="s">
-        <v>3920</v>
+        <v>3915</v>
       </c>
       <c r="J3030" s="31"/>
       <c r="K3030" s="31"/>
       <c r="L3030" s="31"/>
       <c r="M3030" s="31" t="s">
-        <v>3898</v>
+        <v>3893</v>
       </c>
       <c r="N3030" s="31"/>
       <c r="O3030" s="31"/>
@@ -78570,7 +78558,7 @@
         <v>384</v>
       </c>
       <c r="I3031" s="31" t="s">
-        <v>3920</v>
+        <v>3915</v>
       </c>
       <c r="J3031" s="28"/>
       <c r="K3031" s="28"/>
@@ -78590,27 +78578,27 @@
         <v>268</v>
       </c>
       <c r="H3032" s="24" t="s">
-        <v>3899</v>
+        <v>3894</v>
       </c>
       <c r="I3032" s="24" t="s">
-        <v>3900</v>
+        <v>3895</v>
       </c>
       <c r="M3032" s="24" t="s">
-        <v>3898</v>
+        <v>3893</v>
       </c>
     </row>
     <row r="3033" spans="1:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3033" s="38" t="s">
-        <v>3921</v>
+        <v>3916</v>
       </c>
       <c r="B3033" s="24" t="s">
-        <v>3922</v>
+        <v>3917</v>
       </c>
       <c r="H3033" s="25" t="s">
-        <v>3923</v>
+        <v>3918</v>
       </c>
       <c r="I3033" s="24" t="s">
-        <v>3924</v>
+        <v>3919</v>
       </c>
       <c r="J3033" s="54" t="s">
         <v>648</v>
@@ -78669,7 +78657,7 @@
         <v>273</v>
       </c>
       <c r="B3036" s="31" t="s">
-        <v>3925</v>
+        <v>3920</v>
       </c>
       <c r="C3036" s="31"/>
       <c r="D3036" s="31"/>
@@ -78677,10 +78665,10 @@
       <c r="F3036" s="31"/>
       <c r="G3036" s="31"/>
       <c r="H3036" s="52" t="s">
-        <v>3926</v>
+        <v>3921</v>
       </c>
       <c r="I3036" s="31" t="s">
-        <v>3926</v>
+        <v>3921</v>
       </c>
       <c r="J3036" s="31"/>
       <c r="K3036" s="31"/>
@@ -78689,7 +78677,7 @@
         <v>272</v>
       </c>
       <c r="N3036" s="31" t="s">
-        <v>3927</v>
+        <v>3922</v>
       </c>
       <c r="O3036" s="31"/>
       <c r="P3036" s="31"/>
@@ -78712,7 +78700,7 @@
         <v>384</v>
       </c>
       <c r="I3037" s="52" t="s">
-        <v>3926</v>
+        <v>3921</v>
       </c>
       <c r="J3037" s="28"/>
       <c r="K3037" s="28"/>
@@ -78726,10 +78714,10 @@
     </row>
     <row r="3038" spans="1:18" s="31" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3038" s="24" t="s">
-        <v>3928</v>
+        <v>3923</v>
       </c>
       <c r="B3038" s="24" t="s">
-        <v>3929</v>
+        <v>3924</v>
       </c>
       <c r="C3038" s="24"/>
       <c r="D3038" s="24"/>
@@ -78737,10 +78725,10 @@
       <c r="F3038" s="24"/>
       <c r="G3038" s="24"/>
       <c r="H3038" s="25" t="s">
-        <v>3930</v>
+        <v>3925</v>
       </c>
       <c r="I3038" s="24" t="s">
-        <v>3931</v>
+        <v>3926</v>
       </c>
       <c r="J3038" s="54" t="s">
         <v>404</v>
@@ -78765,13 +78753,13 @@
         <v>305</v>
       </c>
       <c r="B3039" s="24" t="s">
-        <v>3932</v>
+        <v>3927</v>
       </c>
       <c r="H3039" s="25" t="s">
-        <v>3933</v>
+        <v>3928</v>
       </c>
       <c r="I3039" s="24" t="s">
-        <v>3934</v>
+        <v>3929</v>
       </c>
       <c r="J3039" s="54" t="s">
         <v>404</v>
@@ -78797,13 +78785,13 @@
         <v>305</v>
       </c>
       <c r="B3040" s="24" t="s">
-        <v>3935</v>
+        <v>3930</v>
       </c>
       <c r="H3040" s="25" t="s">
-        <v>3936</v>
+        <v>3931</v>
       </c>
       <c r="I3040" s="24" t="s">
-        <v>3937</v>
+        <v>3932</v>
       </c>
       <c r="J3040" s="54" t="s">
         <v>404</v>
@@ -78823,13 +78811,13 @@
         <v>305</v>
       </c>
       <c r="B3041" s="24" t="s">
-        <v>3938</v>
+        <v>3933</v>
       </c>
       <c r="H3041" s="25" t="s">
-        <v>3939</v>
+        <v>3934</v>
       </c>
       <c r="I3041" s="24" t="s">
-        <v>3940</v>
+        <v>3935</v>
       </c>
       <c r="J3041" s="54" t="s">
         <v>404</v>
@@ -78846,16 +78834,16 @@
     </row>
     <row r="3042" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3042" s="24" t="s">
-        <v>3941</v>
+        <v>3936</v>
       </c>
       <c r="B3042" s="24" t="s">
         <v>79</v>
       </c>
       <c r="H3042" s="25" t="s">
-        <v>3942</v>
+        <v>3937</v>
       </c>
       <c r="I3042" s="24" t="s">
-        <v>3943</v>
+        <v>3938</v>
       </c>
       <c r="J3042" s="54" t="s">
         <v>404</v>
@@ -78869,16 +78857,16 @@
     </row>
     <row r="3043" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3043" s="24" t="s">
-        <v>3944</v>
+        <v>3939</v>
       </c>
       <c r="B3043" s="24" t="s">
-        <v>3945</v>
+        <v>3940</v>
       </c>
       <c r="H3043" s="25" t="s">
-        <v>3946</v>
+        <v>3941</v>
       </c>
       <c r="I3043" s="24" t="s">
-        <v>3947</v>
+        <v>3942</v>
       </c>
       <c r="J3043" s="54" t="s">
         <v>404</v>
@@ -78892,16 +78880,16 @@
     </row>
     <row r="3044" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3044" s="24" t="s">
-        <v>3948</v>
+        <v>3943</v>
       </c>
       <c r="B3044" s="24" t="s">
-        <v>3949</v>
+        <v>3944</v>
       </c>
       <c r="H3044" s="25" t="s">
-        <v>3950</v>
+        <v>3945</v>
       </c>
       <c r="I3044" s="24" t="s">
-        <v>3951</v>
+        <v>3946</v>
       </c>
       <c r="J3044" s="54" t="s">
         <v>404</v>
@@ -78918,13 +78906,13 @@
         <v>296</v>
       </c>
       <c r="B3045" s="24" t="s">
-        <v>3952</v>
+        <v>3947</v>
       </c>
       <c r="H3045" s="25" t="s">
-        <v>3953</v>
+        <v>3948</v>
       </c>
       <c r="I3045" s="24" t="s">
-        <v>3954</v>
+        <v>3949</v>
       </c>
       <c r="J3045" s="54" t="s">
         <v>404</v>
@@ -78936,21 +78924,21 @@
         <v>282</v>
       </c>
       <c r="N3045" s="24" t="s">
-        <v>3955</v>
+        <v>3950</v>
       </c>
     </row>
     <row r="3046" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3046" s="24" t="s">
-        <v>3956</v>
+        <v>3951</v>
       </c>
       <c r="B3046" s="24" t="s">
-        <v>3957</v>
+        <v>3952</v>
       </c>
       <c r="H3046" s="25" t="s">
-        <v>3958</v>
+        <v>3953</v>
       </c>
       <c r="I3046" s="24" t="s">
-        <v>3959</v>
+        <v>3954</v>
       </c>
       <c r="J3046" s="54" t="s">
         <v>404</v>
@@ -78967,13 +78955,13 @@
         <v>296</v>
       </c>
       <c r="B3047" s="24" t="s">
-        <v>3960</v>
+        <v>3955</v>
       </c>
       <c r="H3047" s="25" t="s">
-        <v>3961</v>
+        <v>3956</v>
       </c>
       <c r="I3047" s="24" t="s">
-        <v>3962</v>
+        <v>3957</v>
       </c>
       <c r="J3047" s="54" t="s">
         <v>404</v>
@@ -78990,13 +78978,13 @@
         <v>296</v>
       </c>
       <c r="B3048" s="24" t="s">
-        <v>3963</v>
+        <v>3958</v>
       </c>
       <c r="H3048" s="25" t="s">
-        <v>3964</v>
+        <v>3959</v>
       </c>
       <c r="I3048" s="24" t="s">
-        <v>3965</v>
+        <v>3960</v>
       </c>
       <c r="J3048" s="54" t="s">
         <v>404</v>
@@ -79013,13 +79001,13 @@
         <v>296</v>
       </c>
       <c r="B3049" s="24" t="s">
-        <v>3966</v>
+        <v>3961</v>
       </c>
       <c r="D3049" s="54" t="s">
         <v>404</v>
       </c>
       <c r="H3049" s="25" t="s">
-        <v>3967</v>
+        <v>3962</v>
       </c>
       <c r="I3049" s="24" t="s">
         <v>395</v>
@@ -79028,21 +79016,21 @@
         <v>282</v>
       </c>
       <c r="O3049" s="24" t="s">
-        <v>3968</v>
+        <v>3963</v>
       </c>
     </row>
     <row r="3050" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3050" s="24" t="s">
-        <v>3969</v>
+        <v>3964</v>
       </c>
       <c r="B3050" s="24" t="s">
         <v>83</v>
       </c>
       <c r="H3050" s="25" t="s">
-        <v>3970</v>
+        <v>3965</v>
       </c>
       <c r="I3050" s="24" t="s">
-        <v>3971</v>
+        <v>3966</v>
       </c>
       <c r="J3050" s="54" t="s">
         <v>404</v>
@@ -79059,16 +79047,16 @@
     </row>
     <row r="3051" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3051" s="24" t="s">
-        <v>3972</v>
+        <v>3967</v>
       </c>
       <c r="B3051" s="24" t="s">
         <v>87</v>
       </c>
       <c r="H3051" s="25" t="s">
-        <v>3973</v>
+        <v>3968</v>
       </c>
       <c r="I3051" s="24" t="s">
-        <v>3974</v>
+        <v>3969</v>
       </c>
       <c r="J3051" s="54" t="s">
         <v>404</v>
@@ -79082,16 +79070,16 @@
     </row>
     <row r="3052" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3052" s="24" t="s">
-        <v>3975</v>
+        <v>3970</v>
       </c>
       <c r="B3052" s="24" t="s">
-        <v>3976</v>
+        <v>3971</v>
       </c>
       <c r="H3052" s="25" t="s">
-        <v>3977</v>
+        <v>3972</v>
       </c>
       <c r="I3052" s="24" t="s">
-        <v>3978</v>
+        <v>3973</v>
       </c>
       <c r="J3052" s="54" t="s">
         <v>404</v>
@@ -79103,21 +79091,21 @@
         <v>282</v>
       </c>
       <c r="N3052" s="24" t="s">
-        <v>3979</v>
+        <v>3974</v>
       </c>
     </row>
     <row r="3053" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3053" s="24" t="s">
-        <v>3980</v>
+        <v>3975</v>
       </c>
       <c r="B3053" s="24" t="s">
-        <v>3981</v>
+        <v>3976</v>
       </c>
       <c r="H3053" s="25" t="s">
-        <v>3982</v>
+        <v>3977</v>
       </c>
       <c r="I3053" s="24" t="s">
-        <v>3983</v>
+        <v>3978</v>
       </c>
       <c r="J3053" s="54" t="s">
         <v>404</v>
@@ -79129,21 +79117,21 @@
         <v>282</v>
       </c>
       <c r="N3053" s="24" t="s">
-        <v>3979</v>
+        <v>3974</v>
       </c>
     </row>
     <row r="3054" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3054" s="24" t="s">
-        <v>3984</v>
+        <v>3979</v>
       </c>
       <c r="B3054" s="24" t="s">
-        <v>3985</v>
+        <v>3980</v>
       </c>
       <c r="H3054" s="25" t="s">
-        <v>3986</v>
+        <v>3981</v>
       </c>
       <c r="I3054" s="24" t="s">
-        <v>3987</v>
+        <v>3982</v>
       </c>
       <c r="J3054" s="54" t="s">
         <v>404</v>
@@ -79157,16 +79145,16 @@
     </row>
     <row r="3055" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3055" s="24" t="s">
-        <v>3988</v>
+        <v>3983</v>
       </c>
       <c r="B3055" s="24" t="s">
         <v>88</v>
       </c>
       <c r="H3055" s="25" t="s">
-        <v>3989</v>
+        <v>3984</v>
       </c>
       <c r="I3055" s="24" t="s">
-        <v>3990</v>
+        <v>3985</v>
       </c>
       <c r="J3055" s="54" t="s">
         <v>404</v>
@@ -79178,21 +79166,21 @@
         <v>282</v>
       </c>
       <c r="N3055" s="24" t="s">
-        <v>3991</v>
+        <v>3986</v>
       </c>
     </row>
     <row r="3056" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3056" s="24" t="s">
-        <v>3992</v>
+        <v>3987</v>
       </c>
       <c r="B3056" s="24" t="s">
-        <v>3993</v>
+        <v>3988</v>
       </c>
       <c r="H3056" s="25" t="s">
-        <v>3994</v>
+        <v>3989</v>
       </c>
       <c r="I3056" s="24" t="s">
-        <v>3995</v>
+        <v>3990</v>
       </c>
       <c r="J3056" s="54" t="s">
         <v>404</v>
@@ -79206,10 +79194,10 @@
     </row>
     <row r="3057" spans="1:18" s="31" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3057" s="24" t="s">
-        <v>3996</v>
+        <v>3991</v>
       </c>
       <c r="B3057" s="24" t="s">
-        <v>3997</v>
+        <v>3992</v>
       </c>
       <c r="C3057" s="24"/>
       <c r="D3057" s="24"/>
@@ -79217,10 +79205,10 @@
       <c r="F3057" s="24"/>
       <c r="G3057" s="24"/>
       <c r="H3057" s="25" t="s">
-        <v>3998</v>
+        <v>3993</v>
       </c>
       <c r="I3057" s="24" t="s">
-        <v>3999</v>
+        <v>3994</v>
       </c>
       <c r="J3057" s="54" t="s">
         <v>404</v>
@@ -79233,7 +79221,7 @@
         <v>282</v>
       </c>
       <c r="N3057" s="24" t="s">
-        <v>4000</v>
+        <v>3995</v>
       </c>
       <c r="O3057" s="24"/>
       <c r="P3057" s="24"/>
@@ -79242,16 +79230,16 @@
     </row>
     <row r="3058" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3058" s="24" t="s">
-        <v>4001</v>
+        <v>3996</v>
       </c>
       <c r="B3058" s="24" t="s">
         <v>94</v>
       </c>
       <c r="H3058" s="25" t="s">
-        <v>4002</v>
+        <v>3997</v>
       </c>
       <c r="I3058" s="24" t="s">
-        <v>4003</v>
+        <v>3998</v>
       </c>
       <c r="J3058" s="54" t="s">
         <v>404</v>
@@ -79265,10 +79253,10 @@
     </row>
     <row r="3059" spans="1:18" s="31" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3059" s="24" t="s">
-        <v>4004</v>
+        <v>3999</v>
       </c>
       <c r="B3059" s="24" t="s">
-        <v>4005</v>
+        <v>4000</v>
       </c>
       <c r="C3059" s="24"/>
       <c r="D3059" s="24"/>
@@ -79276,10 +79264,10 @@
       <c r="F3059" s="24"/>
       <c r="G3059" s="24"/>
       <c r="H3059" s="25" t="s">
-        <v>4006</v>
+        <v>4001</v>
       </c>
       <c r="I3059" s="24" t="s">
-        <v>4007</v>
+        <v>4002</v>
       </c>
       <c r="J3059" s="54" t="s">
         <v>404</v>
@@ -79292,7 +79280,7 @@
         <v>282</v>
       </c>
       <c r="N3059" s="24" t="s">
-        <v>4008</v>
+        <v>4003</v>
       </c>
       <c r="O3059" s="24"/>
       <c r="P3059" s="24"/>
@@ -79301,16 +79289,16 @@
     </row>
     <row r="3060" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3060" s="24" t="s">
-        <v>4009</v>
+        <v>4004</v>
       </c>
       <c r="B3060" s="24" t="s">
-        <v>4010</v>
+        <v>4005</v>
       </c>
       <c r="H3060" s="25" t="s">
-        <v>4011</v>
+        <v>4006</v>
       </c>
       <c r="I3060" s="24" t="s">
-        <v>4012</v>
+        <v>4007</v>
       </c>
       <c r="J3060" s="54" t="s">
         <v>404</v>
@@ -79322,21 +79310,21 @@
         <v>282</v>
       </c>
       <c r="N3060" s="24" t="s">
-        <v>4008</v>
+        <v>4003</v>
       </c>
     </row>
     <row r="3061" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3061" s="24" t="s">
-        <v>4013</v>
+        <v>4008</v>
       </c>
       <c r="B3061" s="24" t="s">
         <v>101</v>
       </c>
       <c r="H3061" s="25" t="s">
-        <v>4014</v>
+        <v>4009</v>
       </c>
       <c r="I3061" s="24" t="s">
-        <v>4015</v>
+        <v>4010</v>
       </c>
       <c r="J3061" s="54" t="s">
         <v>404</v>
@@ -79350,16 +79338,16 @@
     </row>
     <row r="3062" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3062" s="24" t="s">
-        <v>4016</v>
+        <v>4011</v>
       </c>
       <c r="B3062" s="24" t="s">
         <v>102</v>
       </c>
       <c r="H3062" s="25" t="s">
-        <v>4017</v>
+        <v>4012</v>
       </c>
       <c r="I3062" s="24" t="s">
-        <v>4018</v>
+        <v>4013</v>
       </c>
       <c r="J3062" s="54" t="s">
         <v>404</v>
@@ -79373,16 +79361,16 @@
     </row>
     <row r="3063" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3063" s="24" t="s">
-        <v>4019</v>
+        <v>4014</v>
       </c>
       <c r="B3063" s="24" t="s">
         <v>105</v>
       </c>
       <c r="H3063" s="25" t="s">
-        <v>4020</v>
+        <v>4015</v>
       </c>
       <c r="I3063" s="24" t="s">
-        <v>4021</v>
+        <v>4016</v>
       </c>
       <c r="J3063" s="54" t="s">
         <v>404</v>
@@ -79396,16 +79384,16 @@
     </row>
     <row r="3064" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3064" s="24" t="s">
-        <v>4022</v>
+        <v>4017</v>
       </c>
       <c r="B3064" s="24" t="s">
-        <v>4023</v>
+        <v>4018</v>
       </c>
       <c r="H3064" s="25" t="s">
-        <v>4024</v>
+        <v>4019</v>
       </c>
       <c r="I3064" s="24" t="s">
-        <v>4025</v>
+        <v>4020</v>
       </c>
       <c r="J3064" s="54" t="s">
         <v>404</v>
@@ -79417,21 +79405,21 @@
         <v>282</v>
       </c>
       <c r="N3064" s="24" t="s">
-        <v>4026</v>
+        <v>4021</v>
       </c>
     </row>
     <row r="3065" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3065" s="24" t="s">
-        <v>4027</v>
+        <v>4022</v>
       </c>
       <c r="B3065" s="24" t="s">
         <v>108</v>
       </c>
       <c r="H3065" s="25" t="s">
-        <v>4028</v>
+        <v>4023</v>
       </c>
       <c r="I3065" s="24" t="s">
-        <v>4029</v>
+        <v>4024</v>
       </c>
       <c r="J3065" s="54" t="s">
         <v>404</v>
@@ -79445,7 +79433,7 @@
     </row>
     <row r="3066" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3066" s="24" t="s">
-        <v>4030</v>
+        <v>4025</v>
       </c>
       <c r="B3066" s="24" t="s">
         <v>114</v>
@@ -79471,7 +79459,7 @@
     </row>
     <row r="3067" spans="1:18" s="31" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3067" s="24" t="s">
-        <v>4031</v>
+        <v>4026</v>
       </c>
       <c r="B3067" s="24" t="s">
         <v>117</v>
@@ -79482,10 +79470,10 @@
       <c r="F3067" s="24"/>
       <c r="G3067" s="24"/>
       <c r="H3067" s="25" t="s">
-        <v>4032</v>
+        <v>4027</v>
       </c>
       <c r="I3067" s="24" t="s">
-        <v>4033</v>
+        <v>4028</v>
       </c>
       <c r="J3067" s="54" t="s">
         <v>404</v>
@@ -79550,7 +79538,7 @@
         <v>273</v>
       </c>
       <c r="B3070" s="31" t="s">
-        <v>4034</v>
+        <v>4029</v>
       </c>
       <c r="C3070" s="31"/>
       <c r="D3070" s="31"/>
@@ -79558,16 +79546,16 @@
       <c r="F3070" s="31"/>
       <c r="G3070" s="31"/>
       <c r="H3070" s="52" t="s">
-        <v>4035</v>
+        <v>4030</v>
       </c>
       <c r="I3070" s="52" t="s">
-        <v>4035</v>
+        <v>4030</v>
       </c>
       <c r="J3070" s="31"/>
       <c r="K3070" s="31"/>
       <c r="L3070" s="31"/>
       <c r="M3070" s="31" t="s">
-        <v>4036</v>
+        <v>4031</v>
       </c>
       <c r="N3070" s="31"/>
       <c r="O3070" s="31"/>
@@ -79591,7 +79579,7 @@
         <v>384</v>
       </c>
       <c r="I3071" s="52" t="s">
-        <v>4035</v>
+        <v>4030</v>
       </c>
       <c r="J3071" s="28"/>
       <c r="K3071" s="28"/>
@@ -79611,10 +79599,10 @@
         <v>268</v>
       </c>
       <c r="H3072" s="25" t="s">
-        <v>4037</v>
+        <v>4032</v>
       </c>
       <c r="I3072" s="24" t="s">
-        <v>4038</v>
+        <v>4033</v>
       </c>
       <c r="J3072" s="54"/>
       <c r="M3072" s="24" t="s">
@@ -79629,7 +79617,7 @@
         <v>127</v>
       </c>
       <c r="H3073" s="25" t="s">
-        <v>4039</v>
+        <v>4034</v>
       </c>
       <c r="I3073" s="24" t="s">
         <v>103</v>
@@ -79655,7 +79643,7 @@
         <v>128</v>
       </c>
       <c r="H3074" s="25" t="s">
-        <v>4040</v>
+        <v>4035</v>
       </c>
       <c r="I3074" s="24" t="s">
         <v>104</v>
@@ -79681,10 +79669,10 @@
         <v>268</v>
       </c>
       <c r="H3075" s="25" t="s">
-        <v>4041</v>
+        <v>4036</v>
       </c>
       <c r="I3075" s="24" t="s">
-        <v>4042</v>
+        <v>4037</v>
       </c>
       <c r="J3075" s="54"/>
       <c r="M3075" s="24" t="s">
@@ -79696,7 +79684,7 @@
         <v>296</v>
       </c>
       <c r="B3076" s="24" t="s">
-        <v>4043</v>
+        <v>4038</v>
       </c>
       <c r="C3076" s="24"/>
       <c r="D3076" s="24"/>
@@ -79704,7 +79692,7 @@
       <c r="F3076" s="24"/>
       <c r="G3076" s="24"/>
       <c r="H3076" s="25" t="s">
-        <v>4039</v>
+        <v>4034</v>
       </c>
       <c r="I3076" s="24" t="s">
         <v>103</v>
@@ -79732,10 +79720,10 @@
         <v>296</v>
       </c>
       <c r="B3077" s="24" t="s">
-        <v>4044</v>
+        <v>4039</v>
       </c>
       <c r="H3077" s="25" t="s">
-        <v>4040</v>
+        <v>4035</v>
       </c>
       <c r="I3077" s="24" t="s">
         <v>104</v>
@@ -79761,10 +79749,10 @@
         <v>268</v>
       </c>
       <c r="H3078" s="25" t="s">
-        <v>4045</v>
+        <v>4040</v>
       </c>
       <c r="I3078" s="24" t="s">
-        <v>4046</v>
+        <v>4041</v>
       </c>
       <c r="J3078" s="54"/>
       <c r="M3078" s="24" t="s">
@@ -79776,10 +79764,10 @@
         <v>296</v>
       </c>
       <c r="B3079" s="24" t="s">
-        <v>4047</v>
+        <v>4042</v>
       </c>
       <c r="H3079" s="25" t="s">
-        <v>4039</v>
+        <v>4034</v>
       </c>
       <c r="I3079" s="24" t="s">
         <v>103</v>
@@ -79802,10 +79790,10 @@
         <v>296</v>
       </c>
       <c r="B3080" s="24" t="s">
-        <v>4048</v>
+        <v>4043</v>
       </c>
       <c r="H3080" s="25" t="s">
-        <v>4040</v>
+        <v>4035</v>
       </c>
       <c r="I3080" s="24" t="s">
         <v>104</v>
@@ -79831,10 +79819,10 @@
         <v>268</v>
       </c>
       <c r="H3081" s="25" t="s">
-        <v>4049</v>
+        <v>4044</v>
       </c>
       <c r="I3081" s="24" t="s">
-        <v>4050</v>
+        <v>4045</v>
       </c>
       <c r="J3081" s="54"/>
       <c r="M3081" s="24" t="s">
@@ -79846,10 +79834,10 @@
         <v>296</v>
       </c>
       <c r="B3082" s="24" t="s">
-        <v>4051</v>
+        <v>4046</v>
       </c>
       <c r="H3082" s="25" t="s">
-        <v>4039</v>
+        <v>4034</v>
       </c>
       <c r="I3082" s="24" t="s">
         <v>103</v>
@@ -79872,10 +79860,10 @@
         <v>296</v>
       </c>
       <c r="B3083" s="24" t="s">
-        <v>4052</v>
+        <v>4047</v>
       </c>
       <c r="H3083" s="25" t="s">
-        <v>4040</v>
+        <v>4035</v>
       </c>
       <c r="I3083" s="24" t="s">
         <v>104</v>
@@ -79901,10 +79889,10 @@
         <v>268</v>
       </c>
       <c r="H3084" s="25" t="s">
-        <v>4053</v>
+        <v>4048</v>
       </c>
       <c r="I3084" s="24" t="s">
-        <v>4054</v>
+        <v>4049</v>
       </c>
       <c r="J3084" s="54"/>
       <c r="M3084" s="24" t="s">
@@ -79916,10 +79904,10 @@
         <v>296</v>
       </c>
       <c r="B3085" s="24" t="s">
-        <v>4055</v>
+        <v>4050</v>
       </c>
       <c r="H3085" s="25" t="s">
-        <v>4039</v>
+        <v>4034</v>
       </c>
       <c r="I3085" s="24" t="s">
         <v>103</v>
@@ -79942,10 +79930,10 @@
         <v>296</v>
       </c>
       <c r="B3086" s="24" t="s">
-        <v>4056</v>
+        <v>4051</v>
       </c>
       <c r="H3086" s="25" t="s">
-        <v>4040</v>
+        <v>4035</v>
       </c>
       <c r="I3086" s="24" t="s">
         <v>104</v>
@@ -79971,10 +79959,10 @@
         <v>268</v>
       </c>
       <c r="H3087" s="25" t="s">
-        <v>4057</v>
+        <v>4052</v>
       </c>
       <c r="I3087" s="24" t="s">
-        <v>4058</v>
+        <v>4053</v>
       </c>
       <c r="J3087" s="54"/>
       <c r="M3087" s="24" t="s">
@@ -79986,10 +79974,10 @@
         <v>296</v>
       </c>
       <c r="B3088" s="24" t="s">
-        <v>4059</v>
+        <v>4054</v>
       </c>
       <c r="H3088" s="25" t="s">
-        <v>4039</v>
+        <v>4034</v>
       </c>
       <c r="I3088" s="24" t="s">
         <v>103</v>
@@ -80012,10 +80000,10 @@
         <v>296</v>
       </c>
       <c r="B3089" s="24" t="s">
-        <v>4060</v>
+        <v>4055</v>
       </c>
       <c r="H3089" s="25" t="s">
-        <v>4040</v>
+        <v>4035</v>
       </c>
       <c r="I3089" s="24" t="s">
         <v>104</v>
@@ -80063,7 +80051,7 @@
         <v>273</v>
       </c>
       <c r="B3092" s="31" t="s">
-        <v>4061</v>
+        <v>4056</v>
       </c>
       <c r="C3092" s="31"/>
       <c r="D3092" s="31"/>
@@ -80071,16 +80059,16 @@
       <c r="F3092" s="31"/>
       <c r="G3092" s="31"/>
       <c r="H3092" s="52" t="s">
-        <v>4062</v>
+        <v>4057</v>
       </c>
       <c r="I3092" s="52" t="s">
-        <v>4062</v>
+        <v>4057</v>
       </c>
       <c r="J3092" s="31"/>
       <c r="K3092" s="31"/>
       <c r="L3092" s="31"/>
       <c r="M3092" s="31" t="s">
-        <v>4036</v>
+        <v>4031</v>
       </c>
       <c r="N3092" s="31"/>
       <c r="O3092" s="31"/>
@@ -80104,7 +80092,7 @@
         <v>384</v>
       </c>
       <c r="I3093" s="52" t="s">
-        <v>4062</v>
+        <v>4057</v>
       </c>
       <c r="J3093" s="28"/>
       <c r="K3093" s="28"/>
@@ -80118,16 +80106,16 @@
     </row>
     <row r="3094" spans="1:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3094" s="38" t="s">
-        <v>4063</v>
+        <v>4058</v>
       </c>
       <c r="B3094" s="24" t="s">
-        <v>4064</v>
+        <v>4059</v>
       </c>
       <c r="H3094" s="25" t="s">
-        <v>4065</v>
+        <v>4060</v>
       </c>
       <c r="I3094" s="24" t="s">
-        <v>4066</v>
+        <v>4061</v>
       </c>
       <c r="J3094" s="54" t="s">
         <v>404</v>
@@ -80136,15 +80124,15 @@
         <v>280</v>
       </c>
       <c r="M3094" s="24" t="s">
-        <v>4067</v>
+        <v>4062</v>
       </c>
     </row>
     <row r="3095" spans="1:18" s="56" customFormat="1" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3095" s="38" t="s">
-        <v>4068</v>
+        <v>4063</v>
       </c>
       <c r="B3095" s="24" t="s">
-        <v>4069</v>
+        <v>4064</v>
       </c>
       <c r="C3095" s="24"/>
       <c r="D3095" s="24"/>
@@ -80152,10 +80140,10 @@
       <c r="F3095" s="24"/>
       <c r="G3095" s="24"/>
       <c r="H3095" s="25" t="s">
-        <v>4070</v>
+        <v>4065</v>
       </c>
       <c r="I3095" s="24" t="s">
-        <v>4071</v>
+        <v>4066</v>
       </c>
       <c r="J3095" s="54" t="s">
         <v>404</v>
@@ -80165,10 +80153,10 @@
       </c>
       <c r="L3095" s="24"/>
       <c r="M3095" s="24" t="s">
+        <v>4062</v>
+      </c>
+      <c r="N3095" s="24" t="s">
         <v>4067</v>
-      </c>
-      <c r="N3095" s="24" t="s">
-        <v>4072</v>
       </c>
       <c r="O3095" s="24"/>
       <c r="P3095" s="24"/>
@@ -80177,16 +80165,16 @@
     </row>
     <row r="3096" spans="1:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3096" s="38" t="s">
-        <v>4073</v>
+        <v>4068</v>
       </c>
       <c r="B3096" s="24" t="s">
-        <v>4074</v>
+        <v>4069</v>
       </c>
       <c r="H3096" s="25" t="s">
-        <v>4075</v>
+        <v>4070</v>
       </c>
       <c r="I3096" s="24" t="s">
-        <v>4076</v>
+        <v>4071</v>
       </c>
       <c r="J3096" s="54" t="s">
         <v>404</v>
@@ -80195,10 +80183,10 @@
         <v>280</v>
       </c>
       <c r="M3096" s="24" t="s">
+        <v>4062</v>
+      </c>
+      <c r="N3096" s="24" t="s">
         <v>4067</v>
-      </c>
-      <c r="N3096" s="24" t="s">
-        <v>4072</v>
       </c>
     </row>
     <row r="3097" spans="1:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
@@ -80209,17 +80197,17 @@
         <v>268</v>
       </c>
       <c r="H3097" s="25" t="s">
-        <v>4077</v>
+        <v>4072</v>
       </c>
       <c r="I3097" s="24" t="s">
-        <v>4078</v>
+        <v>4073</v>
       </c>
       <c r="J3097" s="54"/>
       <c r="M3097" s="24" t="s">
-        <v>4079</v>
+        <v>4074</v>
       </c>
       <c r="N3097" s="24" t="s">
-        <v>4072</v>
+        <v>4067</v>
       </c>
     </row>
     <row r="3098" spans="1:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
@@ -80227,13 +80215,13 @@
         <v>296</v>
       </c>
       <c r="B3098" s="24" t="s">
-        <v>4080</v>
+        <v>4075</v>
       </c>
       <c r="H3098" s="25" t="s">
-        <v>4081</v>
+        <v>4076</v>
       </c>
       <c r="I3098" s="24" t="s">
-        <v>4082</v>
+        <v>4077</v>
       </c>
       <c r="J3098" s="54" t="s">
         <v>404</v>
@@ -80245,7 +80233,7 @@
         <v>286</v>
       </c>
       <c r="N3098" s="24" t="s">
-        <v>4072</v>
+        <v>4067</v>
       </c>
     </row>
     <row r="3099" spans="1:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
@@ -80253,13 +80241,13 @@
         <v>296</v>
       </c>
       <c r="B3099" s="24" t="s">
-        <v>4083</v>
+        <v>4078</v>
       </c>
       <c r="H3099" s="25" t="s">
-        <v>4084</v>
+        <v>4079</v>
       </c>
       <c r="I3099" s="24" t="s">
-        <v>4085</v>
+        <v>4080</v>
       </c>
       <c r="J3099" s="54" t="s">
         <v>404</v>
@@ -80271,7 +80259,7 @@
         <v>286</v>
       </c>
       <c r="N3099" s="24" t="s">
-        <v>4072</v>
+        <v>4067</v>
       </c>
     </row>
     <row r="3100" spans="1:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
@@ -80279,13 +80267,13 @@
         <v>296</v>
       </c>
       <c r="B3100" s="24" t="s">
-        <v>4086</v>
+        <v>4081</v>
       </c>
       <c r="D3100" s="24" t="s">
         <v>404</v>
       </c>
       <c r="H3100" s="25" t="s">
-        <v>4087</v>
+        <v>4082</v>
       </c>
       <c r="I3100" s="24" t="s">
         <v>395</v>
@@ -80295,10 +80283,10 @@
         <v>286</v>
       </c>
       <c r="N3100" s="24" t="s">
-        <v>4072</v>
+        <v>4067</v>
       </c>
       <c r="O3100" s="24" t="s">
-        <v>4088</v>
+        <v>4083</v>
       </c>
     </row>
     <row r="3101" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.25">
@@ -80331,7 +80319,7 @@
         <v>273</v>
       </c>
       <c r="B3103" s="31" t="s">
-        <v>4089</v>
+        <v>4084</v>
       </c>
       <c r="C3103" s="31"/>
       <c r="D3103" s="31"/>
@@ -80339,16 +80327,16 @@
       <c r="F3103" s="31"/>
       <c r="G3103" s="31"/>
       <c r="H3103" s="52" t="s">
-        <v>4090</v>
+        <v>4085</v>
       </c>
       <c r="I3103" s="52" t="s">
-        <v>4090</v>
+        <v>4085</v>
       </c>
       <c r="J3103" s="31"/>
       <c r="K3103" s="31"/>
       <c r="L3103" s="31"/>
       <c r="M3103" s="31" t="s">
-        <v>4036</v>
+        <v>4031</v>
       </c>
       <c r="N3103" s="31"/>
       <c r="O3103" s="31"/>
@@ -80372,7 +80360,7 @@
         <v>384</v>
       </c>
       <c r="I3104" s="52" t="s">
-        <v>4090</v>
+        <v>4085</v>
       </c>
       <c r="J3104" s="31"/>
       <c r="K3104" s="31"/>
@@ -80386,16 +80374,16 @@
     </row>
     <row r="3105" spans="1:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3105" s="38" t="s">
-        <v>4091</v>
+        <v>4086</v>
       </c>
       <c r="B3105" s="24" t="s">
         <v>218</v>
       </c>
       <c r="H3105" s="25" t="s">
-        <v>4092</v>
+        <v>4087</v>
       </c>
       <c r="I3105" s="24" t="s">
-        <v>4093</v>
+        <v>4088</v>
       </c>
       <c r="J3105" s="54" t="s">
         <v>404</v>
@@ -80404,21 +80392,21 @@
         <v>280</v>
       </c>
       <c r="M3105" s="24" t="s">
-        <v>4067</v>
+        <v>4062</v>
       </c>
     </row>
     <row r="3106" spans="1:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3106" s="38" t="s">
-        <v>4094</v>
+        <v>4089</v>
       </c>
       <c r="B3106" s="24" t="s">
         <v>235</v>
       </c>
       <c r="H3106" s="25" t="s">
-        <v>4095</v>
+        <v>4090</v>
       </c>
       <c r="I3106" s="24" t="s">
-        <v>4096</v>
+        <v>4091</v>
       </c>
       <c r="J3106" s="54" t="s">
         <v>404</v>
@@ -80427,10 +80415,10 @@
         <v>280</v>
       </c>
       <c r="M3106" s="24" t="s">
-        <v>4067</v>
+        <v>4062</v>
       </c>
       <c r="N3106" s="24" t="s">
-        <v>4097</v>
+        <v>4092</v>
       </c>
     </row>
     <row r="3107" spans="1:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
@@ -80438,34 +80426,34 @@
         <v>268</v>
       </c>
       <c r="B3107" s="24" t="s">
-        <v>4098</v>
+        <v>4093</v>
       </c>
       <c r="H3107" s="25" t="s">
-        <v>4099</v>
+        <v>4094</v>
       </c>
       <c r="I3107" s="24" t="s">
         <v>236</v>
       </c>
       <c r="J3107" s="54"/>
       <c r="M3107" s="24" t="s">
-        <v>4100</v>
+        <v>4095</v>
       </c>
       <c r="N3107" s="24" t="s">
-        <v>4101</v>
+        <v>4096</v>
       </c>
     </row>
     <row r="3108" spans="1:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3108" s="38" t="s">
-        <v>4102</v>
+        <v>4097</v>
       </c>
       <c r="B3108" s="24" t="s">
-        <v>4103</v>
+        <v>4098</v>
       </c>
       <c r="H3108" s="25" t="s">
-        <v>4104</v>
+        <v>4099</v>
       </c>
       <c r="I3108" s="24" t="s">
-        <v>4105</v>
+        <v>4100</v>
       </c>
       <c r="J3108" s="54" t="s">
         <v>404</v>
@@ -80477,24 +80465,24 @@
         <v>1</v>
       </c>
       <c r="M3108" s="24" t="s">
-        <v>4100</v>
+        <v>4095</v>
       </c>
       <c r="N3108" s="24" t="s">
-        <v>4101</v>
+        <v>4096</v>
       </c>
     </row>
     <row r="3109" spans="1:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3109" s="38" t="s">
-        <v>4106</v>
+        <v>4101</v>
       </c>
       <c r="B3109" s="24" t="s">
-        <v>4107</v>
+        <v>4102</v>
       </c>
       <c r="H3109" s="25" t="s">
-        <v>4108</v>
+        <v>4103</v>
       </c>
       <c r="I3109" s="24" t="s">
-        <v>4109</v>
+        <v>4104</v>
       </c>
       <c r="J3109" s="54" t="s">
         <v>404</v>
@@ -80506,10 +80494,10 @@
         <v>1</v>
       </c>
       <c r="M3109" s="24" t="s">
-        <v>4100</v>
+        <v>4095</v>
       </c>
       <c r="N3109" s="24" t="s">
-        <v>4101</v>
+        <v>4096</v>
       </c>
     </row>
     <row r="3110" spans="1:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
@@ -80517,34 +80505,34 @@
         <v>268</v>
       </c>
       <c r="B3110" s="24" t="s">
-        <v>4110</v>
+        <v>4105</v>
       </c>
       <c r="H3110" s="25" t="s">
-        <v>4111</v>
+        <v>4106</v>
       </c>
       <c r="I3110" s="24" t="s">
         <v>237</v>
       </c>
       <c r="J3110" s="54"/>
       <c r="M3110" s="24" t="s">
-        <v>4100</v>
+        <v>4095</v>
       </c>
       <c r="N3110" s="24" t="s">
-        <v>4112</v>
+        <v>4107</v>
       </c>
     </row>
     <row r="3111" spans="1:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3111" s="38" t="s">
-        <v>4102</v>
+        <v>4097</v>
       </c>
       <c r="B3111" s="24" t="s">
-        <v>4113</v>
+        <v>4108</v>
       </c>
       <c r="H3111" s="25" t="s">
-        <v>4104</v>
+        <v>4099</v>
       </c>
       <c r="I3111" s="24" t="s">
-        <v>4114</v>
+        <v>4109</v>
       </c>
       <c r="J3111" s="54" t="s">
         <v>404</v>
@@ -80556,10 +80544,10 @@
         <v>1</v>
       </c>
       <c r="M3111" s="24" t="s">
-        <v>4100</v>
+        <v>4095</v>
       </c>
       <c r="N3111" s="24" t="s">
-        <v>4112</v>
+        <v>4107</v>
       </c>
       <c r="O3111" s="28"/>
       <c r="P3111" s="28"/>
@@ -80568,16 +80556,16 @@
     </row>
     <row r="3112" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3112" s="38" t="s">
-        <v>4106</v>
+        <v>4101</v>
       </c>
       <c r="B3112" s="24" t="s">
-        <v>4115</v>
+        <v>4110</v>
       </c>
       <c r="H3112" s="25" t="s">
-        <v>4108</v>
+        <v>4103</v>
       </c>
       <c r="I3112" s="24" t="s">
-        <v>4116</v>
+        <v>4111</v>
       </c>
       <c r="J3112" s="54" t="s">
         <v>404</v>
@@ -80589,10 +80577,10 @@
         <v>1</v>
       </c>
       <c r="M3112" s="24" t="s">
-        <v>4100</v>
+        <v>4095</v>
       </c>
       <c r="N3112" s="24" t="s">
-        <v>4112</v>
+        <v>4107</v>
       </c>
     </row>
     <row r="3113" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
@@ -80600,34 +80588,34 @@
         <v>268</v>
       </c>
       <c r="B3113" s="24" t="s">
-        <v>4117</v>
+        <v>4112</v>
       </c>
       <c r="H3113" s="25" t="s">
-        <v>4118</v>
+        <v>4113</v>
       </c>
       <c r="I3113" s="24" t="s">
         <v>238</v>
       </c>
       <c r="J3113" s="54"/>
       <c r="M3113" s="24" t="s">
-        <v>4100</v>
+        <v>4095</v>
       </c>
       <c r="N3113" s="24" t="s">
-        <v>4119</v>
+        <v>4114</v>
       </c>
     </row>
     <row r="3114" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3114" s="38" t="s">
-        <v>4102</v>
+        <v>4097</v>
       </c>
       <c r="B3114" s="24" t="s">
-        <v>4120</v>
+        <v>4115</v>
       </c>
       <c r="H3114" s="25" t="s">
-        <v>4104</v>
+        <v>4099</v>
       </c>
       <c r="I3114" s="24" t="s">
-        <v>4121</v>
+        <v>4116</v>
       </c>
       <c r="J3114" s="54" t="s">
         <v>404</v>
@@ -80639,24 +80627,24 @@
         <v>1</v>
       </c>
       <c r="M3114" s="24" t="s">
-        <v>4100</v>
+        <v>4095</v>
       </c>
       <c r="N3114" s="24" t="s">
-        <v>4119</v>
+        <v>4114</v>
       </c>
     </row>
     <row r="3115" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3115" s="38" t="s">
-        <v>4106</v>
+        <v>4101</v>
       </c>
       <c r="B3115" s="24" t="s">
-        <v>4122</v>
+        <v>4117</v>
       </c>
       <c r="H3115" s="25" t="s">
-        <v>4108</v>
+        <v>4103</v>
       </c>
       <c r="I3115" s="24" t="s">
-        <v>4123</v>
+        <v>4118</v>
       </c>
       <c r="J3115" s="54" t="s">
         <v>404</v>
@@ -80668,10 +80656,10 @@
         <v>1</v>
       </c>
       <c r="M3115" s="24" t="s">
-        <v>4100</v>
+        <v>4095</v>
       </c>
       <c r="N3115" s="24" t="s">
-        <v>4119</v>
+        <v>4114</v>
       </c>
     </row>
     <row r="3116" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
@@ -80679,34 +80667,34 @@
         <v>268</v>
       </c>
       <c r="B3116" s="24" t="s">
-        <v>4124</v>
+        <v>4119</v>
       </c>
       <c r="H3116" s="25" t="s">
-        <v>4125</v>
+        <v>4120</v>
       </c>
       <c r="I3116" s="24" t="s">
         <v>239</v>
       </c>
       <c r="J3116" s="54"/>
       <c r="M3116" s="24" t="s">
-        <v>4100</v>
+        <v>4095</v>
       </c>
       <c r="N3116" s="24" t="s">
-        <v>4126</v>
+        <v>4121</v>
       </c>
     </row>
     <row r="3117" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3117" s="38" t="s">
-        <v>4102</v>
+        <v>4097</v>
       </c>
       <c r="B3117" s="24" t="s">
-        <v>4127</v>
+        <v>4122</v>
       </c>
       <c r="H3117" s="25" t="s">
-        <v>4104</v>
+        <v>4099</v>
       </c>
       <c r="I3117" s="24" t="s">
-        <v>4128</v>
+        <v>4123</v>
       </c>
       <c r="J3117" s="54" t="s">
         <v>404</v>
@@ -80718,24 +80706,24 @@
         <v>1</v>
       </c>
       <c r="M3117" s="24" t="s">
-        <v>4100</v>
+        <v>4095</v>
       </c>
       <c r="N3117" s="24" t="s">
-        <v>4126</v>
+        <v>4121</v>
       </c>
     </row>
     <row r="3118" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3118" s="38" t="s">
-        <v>4106</v>
+        <v>4101</v>
       </c>
       <c r="B3118" s="24" t="s">
-        <v>4129</v>
+        <v>4124</v>
       </c>
       <c r="H3118" s="25" t="s">
-        <v>4108</v>
+        <v>4103</v>
       </c>
       <c r="I3118" s="24" t="s">
-        <v>4130</v>
+        <v>4125</v>
       </c>
       <c r="J3118" s="54" t="s">
         <v>404</v>
@@ -80747,10 +80735,10 @@
         <v>1</v>
       </c>
       <c r="M3118" s="24" t="s">
-        <v>4100</v>
+        <v>4095</v>
       </c>
       <c r="N3118" s="24" t="s">
-        <v>4126</v>
+        <v>4121</v>
       </c>
     </row>
     <row r="3119" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
@@ -80758,34 +80746,34 @@
         <v>268</v>
       </c>
       <c r="B3119" s="24" t="s">
-        <v>4131</v>
+        <v>4126</v>
       </c>
       <c r="H3119" s="25" t="s">
-        <v>4132</v>
+        <v>4127</v>
       </c>
       <c r="I3119" s="24" t="s">
         <v>240</v>
       </c>
       <c r="J3119" s="54"/>
       <c r="M3119" s="24" t="s">
-        <v>4100</v>
+        <v>4095</v>
       </c>
       <c r="N3119" s="24" t="s">
-        <v>4133</v>
+        <v>4128</v>
       </c>
     </row>
     <row r="3120" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3120" s="38" t="s">
-        <v>4102</v>
+        <v>4097</v>
       </c>
       <c r="B3120" s="24" t="s">
-        <v>4134</v>
+        <v>4129</v>
       </c>
       <c r="H3120" s="25" t="s">
-        <v>4104</v>
+        <v>4099</v>
       </c>
       <c r="I3120" s="24" t="s">
-        <v>4135</v>
+        <v>4130</v>
       </c>
       <c r="J3120" s="54" t="s">
         <v>404</v>
@@ -80797,24 +80785,24 @@
         <v>1</v>
       </c>
       <c r="M3120" s="24" t="s">
-        <v>4100</v>
+        <v>4095</v>
       </c>
       <c r="N3120" s="24" t="s">
-        <v>4133</v>
+        <v>4128</v>
       </c>
     </row>
     <row r="3121" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3121" s="38" t="s">
-        <v>4106</v>
+        <v>4101</v>
       </c>
       <c r="B3121" s="24" t="s">
-        <v>4136</v>
+        <v>4131</v>
       </c>
       <c r="H3121" s="25" t="s">
-        <v>4108</v>
+        <v>4103</v>
       </c>
       <c r="I3121" s="24" t="s">
-        <v>4137</v>
+        <v>4132</v>
       </c>
       <c r="J3121" s="54" t="s">
         <v>404</v>
@@ -80826,10 +80814,10 @@
         <v>1</v>
       </c>
       <c r="M3121" s="24" t="s">
-        <v>4100</v>
+        <v>4095</v>
       </c>
       <c r="N3121" s="24" t="s">
-        <v>4133</v>
+        <v>4128</v>
       </c>
     </row>
     <row r="3122" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
@@ -80837,34 +80825,34 @@
         <v>268</v>
       </c>
       <c r="B3122" s="24" t="s">
-        <v>4138</v>
+        <v>4133</v>
       </c>
       <c r="H3122" s="25" t="s">
-        <v>4139</v>
+        <v>4134</v>
       </c>
       <c r="I3122" s="24" t="s">
-        <v>4140</v>
+        <v>4135</v>
       </c>
       <c r="J3122" s="54"/>
       <c r="M3122" s="24" t="s">
-        <v>4100</v>
+        <v>4095</v>
       </c>
       <c r="N3122" s="24" t="s">
-        <v>4141</v>
+        <v>4136</v>
       </c>
     </row>
     <row r="3123" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3123" s="38" t="s">
-        <v>4102</v>
+        <v>4097</v>
       </c>
       <c r="B3123" s="24" t="s">
-        <v>4142</v>
+        <v>4137</v>
       </c>
       <c r="H3123" s="25" t="s">
-        <v>4104</v>
+        <v>4099</v>
       </c>
       <c r="I3123" s="24" t="s">
-        <v>4143</v>
+        <v>4138</v>
       </c>
       <c r="J3123" s="54" t="s">
         <v>404</v>
@@ -80876,24 +80864,24 @@
         <v>1</v>
       </c>
       <c r="M3123" s="24" t="s">
-        <v>4100</v>
+        <v>4095</v>
       </c>
       <c r="N3123" s="24" t="s">
-        <v>4141</v>
+        <v>4136</v>
       </c>
     </row>
     <row r="3124" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3124" s="38" t="s">
-        <v>4106</v>
+        <v>4101</v>
       </c>
       <c r="B3124" s="24" t="s">
-        <v>4144</v>
+        <v>4139</v>
       </c>
       <c r="H3124" s="25" t="s">
-        <v>4108</v>
+        <v>4103</v>
       </c>
       <c r="I3124" s="24" t="s">
-        <v>4145</v>
+        <v>4140</v>
       </c>
       <c r="J3124" s="54" t="s">
         <v>404</v>
@@ -80905,10 +80893,10 @@
         <v>1</v>
       </c>
       <c r="M3124" s="24" t="s">
-        <v>4100</v>
+        <v>4095</v>
       </c>
       <c r="N3124" s="24" t="s">
-        <v>4141</v>
+        <v>4136</v>
       </c>
     </row>
     <row r="3125" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
@@ -80916,34 +80904,34 @@
         <v>268</v>
       </c>
       <c r="B3125" s="24" t="s">
-        <v>4146</v>
+        <v>4141</v>
       </c>
       <c r="H3125" s="25" t="s">
-        <v>4147</v>
+        <v>4142</v>
       </c>
       <c r="I3125" s="24" t="s">
         <v>242</v>
       </c>
       <c r="J3125" s="54"/>
       <c r="M3125" s="24" t="s">
-        <v>4100</v>
+        <v>4095</v>
       </c>
       <c r="N3125" s="24" t="s">
-        <v>4148</v>
+        <v>4143</v>
       </c>
     </row>
     <row r="3126" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3126" s="38" t="s">
-        <v>4102</v>
+        <v>4097</v>
       </c>
       <c r="B3126" s="24" t="s">
-        <v>4149</v>
+        <v>4144</v>
       </c>
       <c r="H3126" s="25" t="s">
-        <v>4104</v>
+        <v>4099</v>
       </c>
       <c r="I3126" s="24" t="s">
-        <v>4150</v>
+        <v>4145</v>
       </c>
       <c r="J3126" s="54" t="s">
         <v>404</v>
@@ -80955,24 +80943,24 @@
         <v>1</v>
       </c>
       <c r="M3126" s="24" t="s">
-        <v>4100</v>
+        <v>4095</v>
       </c>
       <c r="N3126" s="24" t="s">
-        <v>4148</v>
+        <v>4143</v>
       </c>
     </row>
     <row r="3127" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3127" s="38" t="s">
-        <v>4106</v>
+        <v>4101</v>
       </c>
       <c r="B3127" s="24" t="s">
-        <v>4151</v>
+        <v>4146</v>
       </c>
       <c r="H3127" s="25" t="s">
-        <v>4108</v>
+        <v>4103</v>
       </c>
       <c r="I3127" s="24" t="s">
-        <v>4152</v>
+        <v>4147</v>
       </c>
       <c r="J3127" s="54" t="s">
         <v>404</v>
@@ -80984,10 +80972,10 @@
         <v>1</v>
       </c>
       <c r="M3127" s="24" t="s">
-        <v>4100</v>
+        <v>4095</v>
       </c>
       <c r="N3127" s="24" t="s">
-        <v>4148</v>
+        <v>4143</v>
       </c>
     </row>
     <row r="3128" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
@@ -81021,7 +81009,7 @@
         <v>273</v>
       </c>
       <c r="B3130" s="31" t="s">
-        <v>4153</v>
+        <v>4148</v>
       </c>
       <c r="C3130" s="31"/>
       <c r="D3130" s="31"/>
@@ -81029,10 +81017,10 @@
       <c r="F3130" s="31"/>
       <c r="G3130" s="31"/>
       <c r="H3130" s="52" t="s">
-        <v>4154</v>
+        <v>4149</v>
       </c>
       <c r="I3130" s="52" t="s">
-        <v>4154</v>
+        <v>4149</v>
       </c>
       <c r="J3130" s="31"/>
       <c r="K3130" s="31"/>
@@ -81062,7 +81050,7 @@
         <v>384</v>
       </c>
       <c r="I3131" s="52" t="s">
-        <v>4154</v>
+        <v>4149</v>
       </c>
       <c r="J3131" s="31"/>
       <c r="K3131" s="31"/>
@@ -81079,13 +81067,13 @@
         <v>305</v>
       </c>
       <c r="B3132" s="24" t="s">
-        <v>4155</v>
+        <v>4150</v>
       </c>
       <c r="H3132" s="25" t="s">
-        <v>4156</v>
+        <v>4151</v>
       </c>
       <c r="I3132" s="24" t="s">
-        <v>4157</v>
+        <v>4152</v>
       </c>
       <c r="J3132" s="24" t="s">
         <v>279</v>
@@ -81102,13 +81090,13 @@
         <v>305</v>
       </c>
       <c r="B3133" s="24" t="s">
-        <v>4158</v>
+        <v>4153</v>
       </c>
       <c r="H3133" s="25" t="s">
-        <v>4159</v>
+        <v>4154</v>
       </c>
       <c r="I3133" s="24" t="s">
-        <v>4160</v>
+        <v>4155</v>
       </c>
       <c r="J3133" s="24" t="s">
         <v>279</v>
@@ -81128,13 +81116,13 @@
         <v>305</v>
       </c>
       <c r="B3134" s="24" t="s">
-        <v>4161</v>
+        <v>4156</v>
       </c>
       <c r="H3134" s="25" t="s">
-        <v>4162</v>
+        <v>4157</v>
       </c>
       <c r="I3134" s="24" t="s">
-        <v>4163</v>
+        <v>4158</v>
       </c>
       <c r="J3134" s="24" t="s">
         <v>279</v>
